--- a/lesson_vo_manifest.xlsx
+++ b/lesson_vo_manifest.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K183"/>
+  <dimension ref="A1:K155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="I21" s="14" t="inlineStr">
         <is>
-          <t>Page 4, Page 5, Page 6, Page 7</t>
+          <t>Page 4</t>
         </is>
       </c>
       <c r="J21" s="12" t="n">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="I22" s="18" t="inlineStr">
         <is>
-          <t>Page 4, Page 5, Page 6, Page 7</t>
+          <t>Page 4</t>
         </is>
       </c>
       <c r="J22" s="16" t="n">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="I23" s="14" t="inlineStr">
         <is>
-          <t>Page 4, Page 5, Page 6, Page 7</t>
+          <t>Page 4</t>
         </is>
       </c>
       <c r="J23" s="12" t="n">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="I24" s="18" t="inlineStr">
         <is>
-          <t>Page 4, Page 5, Page 6, Page 7</t>
+          <t>Page 4</t>
         </is>
       </c>
       <c r="J24" s="16" t="n">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="I25" s="14" t="inlineStr">
         <is>
-          <t>Page 4, Page 5, Page 7</t>
+          <t>Page 4</t>
         </is>
       </c>
       <c r="J25" s="12" t="n">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="I26" s="18" t="inlineStr">
         <is>
-          <t>Page 4, Page 5, Page 7</t>
+          <t>Page 4</t>
         </is>
       </c>
       <c r="J26" s="16" t="n">
@@ -2117,27 +2117,27 @@
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>vo_t3s_b_pari</t>
+          <t>vo_t3s_b_myra</t>
         </is>
       </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
-          <t>उनमें से 17 परी को दे दिए।</t>
+          <t>उनमें से 17 मायरा को दे दिए।</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>story - 17 given to Pari</t>
+          <t>story - 17 given to Myra</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>next; Pari's picture comes in, then − 17; her picture lights on «परी»</t>
+          <t>next; Myra's picture comes in, then − 17; her picture lights on «मायरा»</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr"/>
       <c r="J35" s="12" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>Page 5, Page 6, Page 7, Page 8, Page 9</t>
+          <t>Page 5, Page 6</t>
         </is>
       </c>
       <c r="J41" s="12" t="n">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="I46" s="18" t="inlineStr">
         <is>
-          <t>Page 2, Page 5, Page 6, Page 7</t>
+          <t>Page 2</t>
         </is>
       </c>
       <c r="J46" s="16" t="n">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>Page 2, Page 5, Page 6, Page 7</t>
+          <t>Page 2</t>
         </is>
       </c>
       <c r="J47" s="12" t="n">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="I48" s="18" t="inlineStr">
         <is>
-          <t>Page 2, Page 5, Page 6, Page 7</t>
+          <t>Page 2</t>
         </is>
       </c>
       <c r="J48" s="16" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
-          <t>Page 2, Page 5, Page 6, Page 7</t>
+          <t>Page 2</t>
         </is>
       </c>
       <c r="J49" s="12" t="n">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="I50" s="18" t="inlineStr">
         <is>
-          <t>Page 2, Page 5, Page 7</t>
+          <t>Page 2</t>
         </is>
       </c>
       <c r="J50" s="16" t="n">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="I51" s="14" t="inlineStr">
         <is>
-          <t>Page 2, Page 5, Page 7</t>
+          <t>Page 2</t>
         </is>
       </c>
       <c r="J51" s="12" t="n">
@@ -2962,11 +2962,7 @@
           <t>one per one the child takes: «एक» … «सात» (the next tap waits for it)</t>
         </is>
       </c>
-      <c r="I52" s="18" t="inlineStr">
-        <is>
-          <t>Page 5, Page 7</t>
-        </is>
-      </c>
+      <c r="I52" s="18" t="inlineStr"/>
       <c r="J52" s="16" t="n">
         <v>1.45</v>
       </c>
@@ -3300,7 +3296,7 @@
       </c>
       <c r="H59" s="14" t="inlineStr">
         <is>
-          <t>T3's story row comes back; on «सत्रह» one of Madhav's rods opens into 10 cubes and 1 rod + 7 cubes fly into Pari's picture (his grey); his 13 beat</t>
+          <t>T3's story row comes back; on «सत्रह» one of Madhav's rods opens into 10 cubes and 1 rod + 7 cubes fly into Myra's picture (his grey); his 13 beat</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr"/>
@@ -3587,7 +3583,7 @@
       </c>
       <c r="I65" s="14" t="inlineStr">
         <is>
-          <t>Page 4, Page 6, Page 7, Page 8, Page 9</t>
+          <t>Page 4, Page 6</t>
         </is>
       </c>
       <c r="J65" s="12" t="n">
@@ -3638,7 +3634,7 @@
       </c>
       <c r="I66" s="18" t="inlineStr">
         <is>
-          <t>Page 6, Page 7, Page 8, Page 9</t>
+          <t>Page 6</t>
         </is>
       </c>
       <c r="J66" s="16" t="n">
@@ -3955,31 +3951,27 @@
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>vo_num_1</t>
+          <t>vo_g1_ones_left</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr">
         <is>
-          <t>एक।</t>
+          <t>इन 12 इकाई में से 7 इकाई हटाने पर बचीं, 5 इकाई।</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>ones left</t>
         </is>
       </c>
       <c r="H73" s="14" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
-        </is>
-      </c>
-      <c r="I73" s="14" t="inlineStr">
-        <is>
-          <t>Page 2, Page 4, Page 6, Page 7</t>
-        </is>
-      </c>
+          <t>when the ones are done; the ones column beats</t>
+        </is>
+      </c>
+      <c r="I73" s="14" t="inlineStr"/>
       <c r="J73" s="12" t="n">
-        <v>1.32</v>
+        <v>4.92</v>
       </c>
       <c r="K73" s="13" t="inlineStr">
         <is>
@@ -4006,31 +3998,27 @@
       </c>
       <c r="E74" s="17" t="inlineStr">
         <is>
-          <t>vo_num_2</t>
+          <t>vo_g1_rm_tens</t>
         </is>
       </c>
       <c r="F74" s="19" t="inlineStr">
         <is>
-          <t>दो।</t>
+          <t>अब दहाइयाँ घटाइए। 3 दहाई में से 2 दहाई हटाइए।</t>
         </is>
       </c>
       <c r="G74" s="18" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>take-away step - the tens</t>
         </is>
       </c>
       <c r="H74" s="18" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
-        </is>
-      </c>
-      <c r="I74" s="18" t="inlineStr">
-        <is>
-          <t>Page 2, Page 4, Page 6, Page 7</t>
-        </is>
-      </c>
+          <t>when the ones are done; the tens column beats</t>
+        </is>
+      </c>
+      <c r="I74" s="18" t="inlineStr"/>
       <c r="J74" s="16" t="n">
-        <v>1.05</v>
+        <v>5.49</v>
       </c>
       <c r="K74" s="17" t="inlineStr">
         <is>
@@ -4057,31 +4045,31 @@
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>vo_num_3</t>
+          <t>vo_idle_rm_o</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>तीन।</t>
+          <t>अब इकाई हटाइए।</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H75" s="14" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
         </is>
       </c>
       <c r="I75" s="14" t="inlineStr">
         <is>
-          <t>Page 2, Page 4, Page 6, Page 7</t>
+          <t>Page 4, Page 6, Page 7, Page 8, Page 9</t>
         </is>
       </c>
       <c r="J75" s="12" t="n">
-        <v>1.07</v>
+        <v>2.21</v>
       </c>
       <c r="K75" s="13" t="inlineStr">
         <is>
@@ -4108,31 +4096,31 @@
       </c>
       <c r="E76" s="17" t="inlineStr">
         <is>
-          <t>vo_num_4</t>
+          <t>vo_idle_rm_t</t>
         </is>
       </c>
       <c r="F76" s="19" t="inlineStr">
         <is>
-          <t>चार।</t>
+          <t>अब दहाई हटाइए।</t>
         </is>
       </c>
       <c r="G76" s="18" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H76" s="18" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
         </is>
       </c>
       <c r="I76" s="18" t="inlineStr">
         <is>
-          <t>Page 2, Page 4, Page 6, Page 7</t>
+          <t>Page 4, Page 6, Page 7, Page 8, Page 9</t>
         </is>
       </c>
       <c r="J76" s="16" t="n">
-        <v>1.17</v>
+        <v>2.27</v>
       </c>
       <c r="K76" s="17" t="inlineStr">
         <is>
@@ -4159,31 +4147,31 @@
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>vo_num_5</t>
+          <t>vo_rm_tens_more</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>पाँच।</t>
+          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>take-away mistake - 1st time</t>
         </is>
       </c>
       <c r="H77" s="14" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
+          <t>a ten too many taken: the tens go back, this line</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
-          <t>Page 2, Page 4, Page 7</t>
+          <t>Page 6, Page 7, Page 8, Page 9</t>
         </is>
       </c>
       <c r="J77" s="12" t="n">
-        <v>1.32</v>
+        <v>4.05</v>
       </c>
       <c r="K77" s="13" t="inlineStr">
         <is>
@@ -4210,31 +4198,31 @@
       </c>
       <c r="E78" s="17" t="inlineStr">
         <is>
-          <t>vo_num_6</t>
+          <t>vo_rm_guide</t>
         </is>
       </c>
       <c r="F78" s="19" t="inlineStr">
         <is>
-          <t>छः।</t>
+          <t>इनमें से इतने हटाइए।</t>
         </is>
       </c>
       <c r="G78" s="18" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>take-away mistake - 2nd time</t>
         </is>
       </c>
       <c r="H78" s="18" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
+          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
         </is>
       </c>
       <c r="I78" s="18" t="inlineStr">
         <is>
-          <t>Page 2, Page 4, Page 7</t>
+          <t>Page 6, Page 7, Page 8, Page 9</t>
         </is>
       </c>
       <c r="J78" s="16" t="n">
-        <v>1.19</v>
+        <v>2.09</v>
       </c>
       <c r="K78" s="17" t="inlineStr">
         <is>
@@ -4261,31 +4249,31 @@
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>vo_num_7</t>
+          <t>vo_ask_pick</t>
         </is>
       </c>
       <c r="F79" s="15" t="inlineStr">
         <is>
-          <t>सात।</t>
+          <t>अब कितने बचे? सही संख्या चुनिए।</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>the answer question</t>
         </is>
       </c>
       <c r="H79" s="14" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
+          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
         </is>
       </c>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>Page 4, Page 7</t>
+          <t>Page 6, Page 7</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
-        <v>1.45</v>
+        <v>3.2</v>
       </c>
       <c r="K79" s="13" t="inlineStr">
         <is>
@@ -4312,27 +4300,31 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>vo_g1_ones_left</t>
+          <t>vo_h_recount</t>
         </is>
       </c>
       <c r="F80" s="19" t="inlineStr">
         <is>
-          <t>इन 12 इकाई में से 7 इकाई हटाने पर बचीं, 5 इकाई।</t>
+          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
         </is>
       </c>
       <c r="G80" s="18" t="inlineStr">
         <is>
-          <t>ones left</t>
+          <t>Hint 1 (1st wrong answer)</t>
         </is>
       </c>
       <c r="H80" s="18" t="inlineStr">
         <is>
-          <t>when the ones are done; the ones column beats</t>
-        </is>
-      </c>
-      <c r="I80" s="18" t="inlineStr"/>
+          <t>the columns beat on «दहाई» / «इकाई»</t>
+        </is>
+      </c>
+      <c r="I80" s="18" t="inlineStr">
+        <is>
+          <t>Page 6, Page 7, Page 8, Page 9</t>
+        </is>
+      </c>
       <c r="J80" s="16" t="n">
-        <v>4.92</v>
+        <v>3.31</v>
       </c>
       <c r="K80" s="17" t="inlineStr">
         <is>
@@ -4359,27 +4351,27 @@
       </c>
       <c r="E81" s="13" t="inlineStr">
         <is>
-          <t>vo_g1_rm_tens</t>
+          <t>vo_g1_h2</t>
         </is>
       </c>
       <c r="F81" s="15" t="inlineStr">
         <is>
-          <t>अब दहाइयाँ घटाइए। 3 दहाई में से 2 दहाई हटाइए।</t>
+          <t>42 में से 27 घटाने पर, 1 दहाई और 5 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">
         <is>
-          <t>take-away step - the tens</t>
+          <t>Hint 2 (2nd wrong answer)</t>
         </is>
       </c>
       <c r="H81" s="14" t="inlineStr">
         <is>
-          <t>when the ones are done; the tens column beats</t>
+          <t>the numbers light; the tens and ones left beat on their words</t>
         </is>
       </c>
       <c r="I81" s="14" t="inlineStr"/>
       <c r="J81" s="12" t="n">
-        <v>5.49</v>
+        <v>5.72</v>
       </c>
       <c r="K81" s="13" t="inlineStr">
         <is>
@@ -4406,31 +4398,27 @@
       </c>
       <c r="E82" s="17" t="inlineStr">
         <is>
-          <t>vo_idle_rm_o</t>
+          <t>vo_g1_reveal</t>
         </is>
       </c>
       <c r="F82" s="19" t="inlineStr">
         <is>
-          <t>अब इकाई हटाइए।</t>
+          <t>42 में से 27 घटाने पर 15 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="G82" s="18" t="inlineStr">
         <is>
-          <t>inactivity reminder - taking away</t>
+          <t>Hint 3 (3rd wrong answer)</t>
         </is>
       </c>
       <c r="H82" s="18" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I82" s="18" t="inlineStr">
-        <is>
-          <t>Page 4, Page 6, Page 7, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>the right card / the right keys lit (one key at a time), the others off</t>
+        </is>
+      </c>
+      <c r="I82" s="18" t="inlineStr"/>
       <c r="J82" s="16" t="n">
-        <v>2.21</v>
+        <v>5.02</v>
       </c>
       <c r="K82" s="17" t="inlineStr">
         <is>
@@ -4457,31 +4445,27 @@
       </c>
       <c r="E83" s="13" t="inlineStr">
         <is>
-          <t>vo_idle_rm_t</t>
+          <t>vo_g1_correct</t>
         </is>
       </c>
       <c r="F83" s="15" t="inlineStr">
         <is>
-          <t>अब दहाई हटाइए।</t>
+          <t>शाबाश! 42 में से 27 घटाने पर हमें मिलीं 1 दहाई और 5 इकाई, यानी 15।</t>
         </is>
       </c>
       <c r="G83" s="14" t="inlineStr">
         <is>
-          <t>inactivity reminder - taking away</t>
+          <t>correct answer</t>
         </is>
       </c>
       <c r="H83" s="14" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I83" s="14" t="inlineStr">
-        <is>
-          <t>Page 4, Page 6, Page 7, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
+        </is>
+      </c>
+      <c r="I83" s="14" t="inlineStr"/>
       <c r="J83" s="12" t="n">
-        <v>2.27</v>
+        <v>7.35</v>
       </c>
       <c r="K83" s="13" t="inlineStr">
         <is>
@@ -4508,31 +4492,27 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>vo_rm_tens_more</t>
+          <t>vo_g1_eq</t>
         </is>
       </c>
       <c r="F84" s="19" t="inlineStr">
         <is>
-          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
+          <t>इसलिए 42 घटा 27 बराबर 15।</t>
         </is>
       </c>
       <c r="G84" s="18" t="inlineStr">
         <is>
-          <t>take-away mistake - 1st time</t>
+          <t>the equation read out</t>
         </is>
       </c>
       <c r="H84" s="18" t="inlineStr">
         <is>
-          <t>a ten too many taken: the tens go back, this line</t>
-        </is>
-      </c>
-      <c r="I84" s="18" t="inlineStr">
-        <is>
-          <t>Page 6, Page 7, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>after the correct line: each part lights as it is said</t>
+        </is>
+      </c>
+      <c r="I84" s="18" t="inlineStr"/>
       <c r="J84" s="16" t="n">
-        <v>4.05</v>
+        <v>4.26</v>
       </c>
       <c r="K84" s="17" t="inlineStr">
         <is>
@@ -4546,44 +4526,40 @@
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>Page 5</t>
+          <t>Page 6</t>
         </is>
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
-          <t>G1 · PV_SUB  (42 − 27)</t>
+          <t>G2 · PV_SUB  (53 − 14)</t>
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>vo_rm_guide</t>
+          <t>vo_g2_prompt</t>
         </is>
       </c>
       <c r="F85" s="15" t="inlineStr">
         <is>
-          <t>इनमें से इतने हटाइए।</t>
+          <t>53 में से 14 घटाइए।</t>
         </is>
       </c>
       <c r="G85" s="14" t="inlineStr">
         <is>
-          <t>take-away mistake - 2nd time</t>
+          <t>page instruction</t>
         </is>
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
-          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
-        </is>
-      </c>
-      <c r="I85" s="14" t="inlineStr">
-        <is>
-          <t>Page 6, Page 7, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>as the page opens (the speaker replays it)</t>
+        </is>
+      </c>
+      <c r="I85" s="14" t="inlineStr"/>
       <c r="J85" s="12" t="n">
-        <v>2.09</v>
+        <v>2.56</v>
       </c>
       <c r="K85" s="13" t="inlineStr">
         <is>
@@ -4597,44 +4573,40 @@
       </c>
       <c r="B86" s="17" t="inlineStr">
         <is>
-          <t>Page 5</t>
+          <t>Page 6</t>
         </is>
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>G1 · PV_SUB  (42 − 27)</t>
+          <t>G2 · PV_SUB  (53 − 14)</t>
         </is>
       </c>
       <c r="D86" s="16" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>vo_ask_pick</t>
+          <t>vo_g2_build</t>
         </is>
       </c>
       <c r="F86" s="19" t="inlineStr">
         <is>
-          <t>अब कितने बचे? सही संख्या चुनिए।</t>
+          <t>सबसे पहले ब्लॉक्स की सहायता से 53 बनाइए।</t>
         </is>
       </c>
       <c r="G86" s="18" t="inlineStr">
         <is>
-          <t>the answer question</t>
+          <t>build instruction</t>
         </is>
       </c>
       <c r="H86" s="18" t="inlineStr">
         <is>
-          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
-        </is>
-      </c>
-      <c r="I86" s="18" t="inlineStr">
-        <is>
-          <t>Page 6, Page 7</t>
-        </is>
-      </c>
+          <t>after the instruction; the + box comes in, the rod + pulses on its «… दहाई» (or the number), the cube + on «… इकाई»</t>
+        </is>
+      </c>
+      <c r="I86" s="18" t="inlineStr"/>
       <c r="J86" s="16" t="n">
-        <v>3.2</v>
+        <v>4.23</v>
       </c>
       <c r="K86" s="17" t="inlineStr">
         <is>
@@ -4648,44 +4620,44 @@
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>Page 5</t>
+          <t>Page 6</t>
         </is>
       </c>
       <c r="C87" s="14" t="inlineStr">
         <is>
-          <t>G1 · PV_SUB  (42 − 27)</t>
+          <t>G2 · PV_SUB  (53 − 14)</t>
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>vo_h_recount</t>
+          <t>vo_idle_build_t</t>
         </is>
       </c>
       <c r="F87" s="15" t="inlineStr">
         <is>
-          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
+          <t>अब दहाई बनाइए।</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
         <is>
-          <t>Hint 1 (1st wrong answer)</t>
+          <t>inactivity reminder - building</t>
         </is>
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
-          <t>the columns beat on «दहाई» / «इकाई»</t>
+          <t>after 7s with no tap at the build step, again every 7s while idle</t>
         </is>
       </c>
       <c r="I87" s="14" t="inlineStr">
         <is>
-          <t>Page 6, Page 7, Page 8, Page 9</t>
+          <t>Page 4, Page 5</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
-        <v>3.31</v>
+        <v>1.95</v>
       </c>
       <c r="K87" s="13" t="inlineStr">
         <is>
@@ -4699,40 +4671,44 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
+          <t>Page 6</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>G2 · PV_SUB  (53 − 14)</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="E88" s="17" t="inlineStr">
+        <is>
+          <t>vo_idle_build_o</t>
+        </is>
+      </c>
+      <c r="F88" s="19" t="inlineStr">
+        <is>
+          <t>अब इकाई बनाइए।</t>
+        </is>
+      </c>
+      <c r="G88" s="18" t="inlineStr">
+        <is>
+          <t>inactivity reminder - building</t>
+        </is>
+      </c>
+      <c r="H88" s="18" t="inlineStr">
+        <is>
+          <t>after 7s with no tap at the build step, again every 7s while idle</t>
+        </is>
+      </c>
+      <c r="I88" s="18" t="inlineStr">
+        <is>
           <t>Page 5</t>
         </is>
       </c>
-      <c r="C88" s="18" t="inlineStr">
-        <is>
-          <t>G1 · PV_SUB  (42 − 27)</t>
-        </is>
-      </c>
-      <c r="D88" s="16" t="n">
-        <v>26</v>
-      </c>
-      <c r="E88" s="17" t="inlineStr">
-        <is>
-          <t>vo_g1_h2</t>
-        </is>
-      </c>
-      <c r="F88" s="19" t="inlineStr">
-        <is>
-          <t>42 में से 27 घटाने पर, 1 दहाई और 5 इकाई बचती हैं।</t>
-        </is>
-      </c>
-      <c r="G88" s="18" t="inlineStr">
-        <is>
-          <t>Hint 2 (2nd wrong answer)</t>
-        </is>
-      </c>
-      <c r="H88" s="18" t="inlineStr">
-        <is>
-          <t>the numbers light; the tens and ones left beat on their words</t>
-        </is>
-      </c>
-      <c r="I88" s="18" t="inlineStr"/>
       <c r="J88" s="16" t="n">
-        <v>5.72</v>
+        <v>1.85</v>
       </c>
       <c r="K88" s="17" t="inlineStr">
         <is>
@@ -4746,40 +4722,40 @@
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>Page 5</t>
+          <t>Page 6</t>
         </is>
       </c>
       <c r="C89" s="14" t="inlineStr">
         <is>
-          <t>G1 · PV_SUB  (42 − 27)</t>
+          <t>G2 · PV_SUB  (53 − 14)</t>
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>vo_g1_reveal</t>
+          <t>vo_g2_sub</t>
         </is>
       </c>
       <c r="F89" s="15" t="inlineStr">
         <is>
-          <t>42 में से 27 घटाने पर 15 बचता है। तो सही संख्या यह है।</t>
+          <t>और अब इसमें से 14 घटाइए।</t>
         </is>
       </c>
       <c r="G89" s="14" t="inlineStr">
         <is>
-          <t>Hint 3 (3rd wrong answer)</t>
+          <t>what is taken away</t>
         </is>
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
-          <t>the right card / the right keys lit (one key at a time), the others off</t>
+          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
         </is>
       </c>
       <c r="I89" s="14" t="inlineStr"/>
       <c r="J89" s="12" t="n">
-        <v>5.02</v>
+        <v>2.32</v>
       </c>
       <c r="K89" s="13" t="inlineStr">
         <is>
@@ -4793,40 +4769,44 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>Page 5</t>
+          <t>Page 6</t>
         </is>
       </c>
       <c r="C90" s="18" t="inlineStr">
         <is>
-          <t>G1 · PV_SUB  (42 − 27)</t>
+          <t>G2 · PV_SUB  (53 − 14)</t>
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>vo_g1_correct</t>
+          <t>vo_idle_open</t>
         </is>
       </c>
       <c r="F90" s="19" t="inlineStr">
         <is>
-          <t>शाबाश! 42 में से 27 घटाने पर हमें मिलीं 1 दहाई और 5 इकाई, यानी 15।</t>
+          <t>अब 1 दहाई को इकाई में लाइए।</t>
         </is>
       </c>
       <c r="G90" s="18" t="inlineStr">
         <is>
-          <t>correct answer</t>
+          <t>inactivity reminder - open a ten</t>
         </is>
       </c>
       <c r="H90" s="18" t="inlineStr">
         <is>
-          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
-        </is>
-      </c>
-      <c r="I90" s="18" t="inlineStr"/>
+          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
+        </is>
+      </c>
+      <c r="I90" s="18" t="inlineStr">
+        <is>
+          <t>Page 5, Page 7, Page 8, Page 9</t>
+        </is>
+      </c>
       <c r="J90" s="16" t="n">
-        <v>7.35</v>
+        <v>3.16</v>
       </c>
       <c r="K90" s="17" t="inlineStr">
         <is>
@@ -4840,40 +4820,40 @@
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>Page 5</t>
+          <t>Page 6</t>
         </is>
       </c>
       <c r="C91" s="14" t="inlineStr">
         <is>
-          <t>G1 · PV_SUB  (42 − 27)</t>
+          <t>G2 · PV_SUB  (53 − 14)</t>
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>vo_g1_eq</t>
+          <t>vo_g2_rm_ones</t>
         </is>
       </c>
       <c r="F91" s="15" t="inlineStr">
         <is>
-          <t>इसलिए 42 घटा 27 बराबर 15।</t>
+          <t>इसमें से 4 इकाई को हटाइए।</t>
         </is>
       </c>
       <c r="G91" s="14" t="inlineStr">
         <is>
-          <t>the equation read out</t>
+          <t>take-away step - the ones</t>
         </is>
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
-          <t>after the correct line: each part lights as it is said</t>
+          <t>after the ten is opened; the ones column beats on «इकाई»</t>
         </is>
       </c>
       <c r="I91" s="14" t="inlineStr"/>
       <c r="J91" s="12" t="n">
-        <v>4.26</v>
+        <v>2.58</v>
       </c>
       <c r="K91" s="13" t="inlineStr">
         <is>
@@ -4896,31 +4876,31 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>vo_g2_prompt</t>
+          <t>vo_g2_rm_tens</t>
         </is>
       </c>
       <c r="F92" s="19" t="inlineStr">
         <is>
-          <t>53 में से 14 घटाइए।</t>
+          <t>अब दहाइयाँ घटाइए।</t>
         </is>
       </c>
       <c r="G92" s="18" t="inlineStr">
         <is>
-          <t>page instruction</t>
+          <t>take-away step - the tens</t>
         </is>
       </c>
       <c r="H92" s="18" t="inlineStr">
         <is>
-          <t>as the page opens (the speaker replays it)</t>
+          <t>when the ones are done; the tens column beats</t>
         </is>
       </c>
       <c r="I92" s="18" t="inlineStr"/>
       <c r="J92" s="16" t="n">
-        <v>2.56</v>
+        <v>2.16</v>
       </c>
       <c r="K92" s="17" t="inlineStr">
         <is>
@@ -4943,31 +4923,35 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>vo_g2_build</t>
+          <t>vo_idle_rm_o</t>
         </is>
       </c>
       <c r="F93" s="15" t="inlineStr">
         <is>
-          <t>सबसे पहले ब्लॉक्स की सहायता से 53 बनाइए।</t>
+          <t>अब इकाई हटाइए।</t>
         </is>
       </c>
       <c r="G93" s="14" t="inlineStr">
         <is>
-          <t>build instruction</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H93" s="14" t="inlineStr">
         <is>
-          <t>after the instruction; the + box comes in, the rod + pulses on its «… दहाई» (or the number), the cube + on «… इकाई»</t>
-        </is>
-      </c>
-      <c r="I93" s="14" t="inlineStr"/>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
+        </is>
+      </c>
+      <c r="I93" s="14" t="inlineStr">
+        <is>
+          <t>Page 4, Page 5, Page 7, Page 8, Page 9</t>
+        </is>
+      </c>
       <c r="J93" s="12" t="n">
-        <v>4.23</v>
+        <v>2.21</v>
       </c>
       <c r="K93" s="13" t="inlineStr">
         <is>
@@ -4990,26 +4974,26 @@
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>vo_idle_build_t</t>
+          <t>vo_idle_rm_t</t>
         </is>
       </c>
       <c r="F94" s="19" t="inlineStr">
         <is>
-          <t>अब दहाई बनाइए।</t>
+          <t>अब दहाई हटाइए।</t>
         </is>
       </c>
       <c r="G94" s="18" t="inlineStr">
         <is>
-          <t>inactivity reminder - building</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H94" s="18" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the build step, again every 7s while idle</t>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
         </is>
       </c>
       <c r="I94" s="18" t="inlineStr">
@@ -5018,7 +5002,7 @@
         </is>
       </c>
       <c r="J94" s="16" t="n">
-        <v>1.95</v>
+        <v>2.27</v>
       </c>
       <c r="K94" s="17" t="inlineStr">
         <is>
@@ -5041,26 +5025,26 @@
         </is>
       </c>
       <c r="D95" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>vo_idle_build_o</t>
+          <t>vo_rm_tens_more</t>
         </is>
       </c>
       <c r="F95" s="15" t="inlineStr">
         <is>
-          <t>अब इकाई बनाइए।</t>
+          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
         </is>
       </c>
       <c r="G95" s="14" t="inlineStr">
         <is>
-          <t>inactivity reminder - building</t>
+          <t>take-away mistake - 1st time</t>
         </is>
       </c>
       <c r="H95" s="14" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the build step, again every 7s while idle</t>
+          <t>a ten too many taken: the tens go back, this line</t>
         </is>
       </c>
       <c r="I95" s="14" t="inlineStr">
@@ -5069,7 +5053,7 @@
         </is>
       </c>
       <c r="J95" s="12" t="n">
-        <v>1.85</v>
+        <v>4.05</v>
       </c>
       <c r="K95" s="13" t="inlineStr">
         <is>
@@ -5092,31 +5076,35 @@
         </is>
       </c>
       <c r="D96" s="16" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>vo_g2_sub</t>
+          <t>vo_rm_guide</t>
         </is>
       </c>
       <c r="F96" s="19" t="inlineStr">
         <is>
-          <t>और अब इसमें से 14 घटाइए।</t>
+          <t>इनमें से इतने हटाइए।</t>
         </is>
       </c>
       <c r="G96" s="18" t="inlineStr">
         <is>
-          <t>what is taken away</t>
+          <t>take-away mistake - 2nd time</t>
         </is>
       </c>
       <c r="H96" s="18" t="inlineStr">
         <is>
-          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
-        </is>
-      </c>
-      <c r="I96" s="18" t="inlineStr"/>
+          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
+        </is>
+      </c>
+      <c r="I96" s="18" t="inlineStr">
+        <is>
+          <t>Page 5, Page 7, Page 8, Page 9</t>
+        </is>
+      </c>
       <c r="J96" s="16" t="n">
-        <v>2.32</v>
+        <v>2.09</v>
       </c>
       <c r="K96" s="17" t="inlineStr">
         <is>
@@ -5139,35 +5127,35 @@
         </is>
       </c>
       <c r="D97" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>vo_idle_open</t>
+          <t>vo_ask_pick</t>
         </is>
       </c>
       <c r="F97" s="15" t="inlineStr">
         <is>
-          <t>अब 1 दहाई को इकाई में लाइए।</t>
+          <t>अब कितने बचे? सही संख्या चुनिए।</t>
         </is>
       </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
-          <t>inactivity reminder - open a ten</t>
+          <t>the answer question</t>
         </is>
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
-          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
+          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
         </is>
       </c>
       <c r="I97" s="14" t="inlineStr">
         <is>
-          <t>Page 5, Page 7, Page 8, Page 9</t>
+          <t>Page 5, Page 7</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="K97" s="13" t="inlineStr">
         <is>
@@ -5190,31 +5178,35 @@
         </is>
       </c>
       <c r="D98" s="16" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t>vo_g2_rm_ones</t>
+          <t>vo_h_recount</t>
         </is>
       </c>
       <c r="F98" s="19" t="inlineStr">
         <is>
-          <t>इसमें से 4 इकाई को हटाइए।</t>
+          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
         </is>
       </c>
       <c r="G98" s="18" t="inlineStr">
         <is>
-          <t>take-away step - the ones</t>
+          <t>Hint 1 (1st wrong answer)</t>
         </is>
       </c>
       <c r="H98" s="18" t="inlineStr">
         <is>
-          <t>after the ten is opened; the ones column beats on «इकाई»</t>
-        </is>
-      </c>
-      <c r="I98" s="18" t="inlineStr"/>
+          <t>the columns beat on «दहाई» / «इकाई»</t>
+        </is>
+      </c>
+      <c r="I98" s="18" t="inlineStr">
+        <is>
+          <t>Page 5, Page 7, Page 8, Page 9</t>
+        </is>
+      </c>
       <c r="J98" s="16" t="n">
-        <v>2.58</v>
+        <v>3.31</v>
       </c>
       <c r="K98" s="17" t="inlineStr">
         <is>
@@ -5237,35 +5229,31 @@
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>vo_num_1</t>
+          <t>vo_g2_h2</t>
         </is>
       </c>
       <c r="F99" s="15" t="inlineStr">
         <is>
-          <t>एक।</t>
+          <t>53 में से 14 घटाने पर, 3 दहाई और 9 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="G99" s="14" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>Hint 2 (2nd wrong answer)</t>
         </is>
       </c>
       <c r="H99" s="14" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
-        </is>
-      </c>
-      <c r="I99" s="14" t="inlineStr">
-        <is>
-          <t>Page 2, Page 4, Page 5, Page 7</t>
-        </is>
-      </c>
+          <t>the numbers light; the tens and ones left beat on their words</t>
+        </is>
+      </c>
+      <c r="I99" s="14" t="inlineStr"/>
       <c r="J99" s="12" t="n">
-        <v>1.32</v>
+        <v>4.71</v>
       </c>
       <c r="K99" s="13" t="inlineStr">
         <is>
@@ -5288,35 +5276,31 @@
         </is>
       </c>
       <c r="D100" s="16" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>vo_num_2</t>
+          <t>vo_g2_reveal</t>
         </is>
       </c>
       <c r="F100" s="19" t="inlineStr">
         <is>
-          <t>दो।</t>
+          <t>53 में से 14 घटाने पर 39 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="G100" s="18" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>Hint 3 (3rd wrong answer)</t>
         </is>
       </c>
       <c r="H100" s="18" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
-        </is>
-      </c>
-      <c r="I100" s="18" t="inlineStr">
-        <is>
-          <t>Page 2, Page 4, Page 5, Page 7</t>
-        </is>
-      </c>
+          <t>the right card / the right keys lit (one key at a time), the others off</t>
+        </is>
+      </c>
+      <c r="I100" s="18" t="inlineStr"/>
       <c r="J100" s="16" t="n">
-        <v>1.05</v>
+        <v>5.8</v>
       </c>
       <c r="K100" s="17" t="inlineStr">
         <is>
@@ -5339,35 +5323,31 @@
         </is>
       </c>
       <c r="D101" s="12" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>vo_num_3</t>
+          <t>vo_g2_correct</t>
         </is>
       </c>
       <c r="F101" s="15" t="inlineStr">
         <is>
-          <t>तीन।</t>
+          <t>शाबाश! 53 घटा 14 बराबर 39।</t>
         </is>
       </c>
       <c r="G101" s="14" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>correct answer</t>
         </is>
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
-        </is>
-      </c>
-      <c r="I101" s="14" t="inlineStr">
-        <is>
-          <t>Page 2, Page 4, Page 5, Page 7</t>
-        </is>
-      </c>
+          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
+        </is>
+      </c>
+      <c r="I101" s="14" t="inlineStr"/>
       <c r="J101" s="12" t="n">
-        <v>1.07</v>
+        <v>4.48</v>
       </c>
       <c r="K101" s="13" t="inlineStr">
         <is>
@@ -5381,44 +5361,40 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>Page 6</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="C102" s="18" t="inlineStr">
         <is>
-          <t>G2 · PV_SUB  (53 − 14)</t>
+          <t>G3 · PV_SUB  (46 − 28)</t>
         </is>
       </c>
       <c r="D102" s="16" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t>vo_num_4</t>
+          <t>vo_g3_prompt</t>
         </is>
       </c>
       <c r="F102" s="19" t="inlineStr">
         <is>
-          <t>चार।</t>
+          <t>46 में से 28 घटाइए।</t>
         </is>
       </c>
       <c r="G102" s="18" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>page instruction</t>
         </is>
       </c>
       <c r="H102" s="18" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
-        </is>
-      </c>
-      <c r="I102" s="18" t="inlineStr">
-        <is>
-          <t>Page 2, Page 4, Page 5, Page 7</t>
-        </is>
-      </c>
+          <t>as the page opens (the speaker replays it)</t>
+        </is>
+      </c>
+      <c r="I102" s="18" t="inlineStr"/>
       <c r="J102" s="16" t="n">
-        <v>1.17</v>
+        <v>2.72</v>
       </c>
       <c r="K102" s="17" t="inlineStr">
         <is>
@@ -5432,40 +5408,40 @@
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>Page 6</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="C103" s="14" t="inlineStr">
         <is>
-          <t>G2 · PV_SUB  (53 − 14)</t>
+          <t>G3 · PV_SUB  (46 − 28)</t>
         </is>
       </c>
       <c r="D103" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>vo_g2_rm_tens</t>
+          <t>vo_g3_sub</t>
         </is>
       </c>
       <c r="F103" s="15" t="inlineStr">
         <is>
-          <t>अब दहाइयाँ घटाइए।</t>
+          <t>और अब इसमें से 28 घटाइए।</t>
         </is>
       </c>
       <c r="G103" s="14" t="inlineStr">
         <is>
-          <t>take-away step - the tens</t>
+          <t>what is taken away</t>
         </is>
       </c>
       <c r="H103" s="14" t="inlineStr">
         <is>
-          <t>when the ones are done; the tens column beats</t>
+          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
         </is>
       </c>
       <c r="I103" s="14" t="inlineStr"/>
       <c r="J103" s="12" t="n">
-        <v>2.16</v>
+        <v>2.67</v>
       </c>
       <c r="K103" s="13" t="inlineStr">
         <is>
@@ -5479,44 +5455,44 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>Page 6</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="C104" s="18" t="inlineStr">
         <is>
-          <t>G2 · PV_SUB  (53 − 14)</t>
+          <t>G3 · PV_SUB  (46 − 28)</t>
         </is>
       </c>
       <c r="D104" s="16" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>vo_idle_rm_o</t>
+          <t>vo_idle_open</t>
         </is>
       </c>
       <c r="F104" s="19" t="inlineStr">
         <is>
-          <t>अब इकाई हटाइए।</t>
+          <t>अब 1 दहाई को इकाई में लाइए।</t>
         </is>
       </c>
       <c r="G104" s="18" t="inlineStr">
         <is>
-          <t>inactivity reminder - taking away</t>
+          <t>inactivity reminder - open a ten</t>
         </is>
       </c>
       <c r="H104" s="18" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
+          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
         </is>
       </c>
       <c r="I104" s="18" t="inlineStr">
         <is>
-          <t>Page 4, Page 5, Page 7, Page 8, Page 9</t>
+          <t>Page 5, Page 6, Page 8, Page 9</t>
         </is>
       </c>
       <c r="J104" s="16" t="n">
-        <v>2.21</v>
+        <v>3.16</v>
       </c>
       <c r="K104" s="17" t="inlineStr">
         <is>
@@ -5530,44 +5506,40 @@
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>Page 6</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="C105" s="14" t="inlineStr">
         <is>
-          <t>G2 · PV_SUB  (53 − 14)</t>
+          <t>G3 · PV_SUB  (46 − 28)</t>
         </is>
       </c>
       <c r="D105" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>vo_idle_rm_t</t>
+          <t>vo_g3_rm_ones</t>
         </is>
       </c>
       <c r="F105" s="15" t="inlineStr">
         <is>
-          <t>अब दहाई हटाइए।</t>
+          <t>इसमें से 8 इकाई को हटाइए।</t>
         </is>
       </c>
       <c r="G105" s="14" t="inlineStr">
         <is>
-          <t>inactivity reminder - taking away</t>
+          <t>take-away step - the ones</t>
         </is>
       </c>
       <c r="H105" s="14" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I105" s="14" t="inlineStr">
-        <is>
-          <t>Page 4, Page 5, Page 7, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>after the ten is opened; the ones column beats on «इकाई»</t>
+        </is>
+      </c>
+      <c r="I105" s="14" t="inlineStr"/>
       <c r="J105" s="12" t="n">
-        <v>2.27</v>
+        <v>3.03</v>
       </c>
       <c r="K105" s="13" t="inlineStr">
         <is>
@@ -5581,44 +5553,40 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>Page 6</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="C106" s="18" t="inlineStr">
         <is>
-          <t>G2 · PV_SUB  (53 − 14)</t>
+          <t>G3 · PV_SUB  (46 − 28)</t>
         </is>
       </c>
       <c r="D106" s="16" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>vo_rm_tens_more</t>
+          <t>vo_g3_rm_tens</t>
         </is>
       </c>
       <c r="F106" s="19" t="inlineStr">
         <is>
-          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
+          <t>अब दहाइयाँ हटाइए।</t>
         </is>
       </c>
       <c r="G106" s="18" t="inlineStr">
         <is>
-          <t>take-away mistake - 1st time</t>
+          <t>take-away step - the tens</t>
         </is>
       </c>
       <c r="H106" s="18" t="inlineStr">
         <is>
-          <t>a ten too many taken: the tens go back, this line</t>
-        </is>
-      </c>
-      <c r="I106" s="18" t="inlineStr">
-        <is>
-          <t>Page 5, Page 7, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>when the ones are done; the tens column beats</t>
+        </is>
+      </c>
+      <c r="I106" s="18" t="inlineStr"/>
       <c r="J106" s="16" t="n">
-        <v>4.05</v>
+        <v>2.47</v>
       </c>
       <c r="K106" s="17" t="inlineStr">
         <is>
@@ -5632,44 +5600,44 @@
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>Page 6</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>G2 · PV_SUB  (53 − 14)</t>
+          <t>G3 · PV_SUB  (46 − 28)</t>
         </is>
       </c>
       <c r="D107" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>vo_rm_guide</t>
+          <t>vo_idle_rm_o</t>
         </is>
       </c>
       <c r="F107" s="15" t="inlineStr">
         <is>
-          <t>इनमें से इतने हटाइए।</t>
+          <t>अब इकाई हटाइए।</t>
         </is>
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
-          <t>take-away mistake - 2nd time</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H107" s="14" t="inlineStr">
         <is>
-          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
         </is>
       </c>
       <c r="I107" s="14" t="inlineStr">
         <is>
-          <t>Page 5, Page 7, Page 8, Page 9</t>
+          <t>Page 4, Page 5, Page 6, Page 8, Page 9</t>
         </is>
       </c>
       <c r="J107" s="12" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="K107" s="13" t="inlineStr">
         <is>
@@ -5683,44 +5651,44 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>Page 6</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="C108" s="18" t="inlineStr">
         <is>
-          <t>G2 · PV_SUB  (53 − 14)</t>
+          <t>G3 · PV_SUB  (46 − 28)</t>
         </is>
       </c>
       <c r="D108" s="16" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>vo_ask_pick</t>
+          <t>vo_idle_rm_t</t>
         </is>
       </c>
       <c r="F108" s="19" t="inlineStr">
         <is>
-          <t>अब कितने बचे? सही संख्या चुनिए।</t>
+          <t>अब दहाई हटाइए।</t>
         </is>
       </c>
       <c r="G108" s="18" t="inlineStr">
         <is>
-          <t>the answer question</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H108" s="18" t="inlineStr">
         <is>
-          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
         </is>
       </c>
       <c r="I108" s="18" t="inlineStr">
         <is>
-          <t>Page 5, Page 7</t>
+          <t>Page 4, Page 5, Page 6, Page 8, Page 9</t>
         </is>
       </c>
       <c r="J108" s="16" t="n">
-        <v>3.2</v>
+        <v>2.27</v>
       </c>
       <c r="K108" s="17" t="inlineStr">
         <is>
@@ -5734,44 +5702,44 @@
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>Page 6</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="C109" s="14" t="inlineStr">
         <is>
-          <t>G2 · PV_SUB  (53 − 14)</t>
+          <t>G3 · PV_SUB  (46 − 28)</t>
         </is>
       </c>
       <c r="D109" s="12" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>vo_h_recount</t>
+          <t>vo_rm_tens_more</t>
         </is>
       </c>
       <c r="F109" s="15" t="inlineStr">
         <is>
-          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
+          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
         <is>
-          <t>Hint 1 (1st wrong answer)</t>
+          <t>take-away mistake - 1st time</t>
         </is>
       </c>
       <c r="H109" s="14" t="inlineStr">
         <is>
-          <t>the columns beat on «दहाई» / «इकाई»</t>
+          <t>a ten too many taken: the tens go back, this line</t>
         </is>
       </c>
       <c r="I109" s="14" t="inlineStr">
         <is>
-          <t>Page 5, Page 7, Page 8, Page 9</t>
+          <t>Page 5, Page 6, Page 8, Page 9</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
-        <v>3.31</v>
+        <v>4.05</v>
       </c>
       <c r="K109" s="13" t="inlineStr">
         <is>
@@ -5785,40 +5753,44 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>Page 6</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="C110" s="18" t="inlineStr">
         <is>
-          <t>G2 · PV_SUB  (53 − 14)</t>
+          <t>G3 · PV_SUB  (46 − 28)</t>
         </is>
       </c>
       <c r="D110" s="16" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t>vo_g2_h2</t>
+          <t>vo_rm_guide</t>
         </is>
       </c>
       <c r="F110" s="19" t="inlineStr">
         <is>
-          <t>53 में से 14 घटाने पर, 3 दहाई और 9 इकाई बचती हैं।</t>
+          <t>इनमें से इतने हटाइए।</t>
         </is>
       </c>
       <c r="G110" s="18" t="inlineStr">
         <is>
-          <t>Hint 2 (2nd wrong answer)</t>
+          <t>take-away mistake - 2nd time</t>
         </is>
       </c>
       <c r="H110" s="18" t="inlineStr">
         <is>
-          <t>the numbers light; the tens and ones left beat on their words</t>
-        </is>
-      </c>
-      <c r="I110" s="18" t="inlineStr"/>
+          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
+        </is>
+      </c>
+      <c r="I110" s="18" t="inlineStr">
+        <is>
+          <t>Page 5, Page 6, Page 8, Page 9</t>
+        </is>
+      </c>
       <c r="J110" s="16" t="n">
-        <v>4.71</v>
+        <v>2.09</v>
       </c>
       <c r="K110" s="17" t="inlineStr">
         <is>
@@ -5832,40 +5804,44 @@
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>Page 6</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="C111" s="14" t="inlineStr">
         <is>
-          <t>G2 · PV_SUB  (53 − 14)</t>
+          <t>G3 · PV_SUB  (46 − 28)</t>
         </is>
       </c>
       <c r="D111" s="12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>vo_g2_reveal</t>
+          <t>vo_ask_pick</t>
         </is>
       </c>
       <c r="F111" s="15" t="inlineStr">
         <is>
-          <t>53 में से 14 घटाने पर 39 बचता है। तो सही संख्या यह है।</t>
+          <t>अब कितने बचे? सही संख्या चुनिए।</t>
         </is>
       </c>
       <c r="G111" s="14" t="inlineStr">
         <is>
-          <t>Hint 3 (3rd wrong answer)</t>
+          <t>the answer question</t>
         </is>
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
-          <t>the right card / the right keys lit (one key at a time), the others off</t>
-        </is>
-      </c>
-      <c r="I111" s="14" t="inlineStr"/>
+          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
+        </is>
+      </c>
+      <c r="I111" s="14" t="inlineStr">
+        <is>
+          <t>Page 5, Page 6</t>
+        </is>
+      </c>
       <c r="J111" s="12" t="n">
-        <v>5.8</v>
+        <v>3.2</v>
       </c>
       <c r="K111" s="13" t="inlineStr">
         <is>
@@ -5879,40 +5855,44 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>Page 6</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="C112" s="18" t="inlineStr">
         <is>
-          <t>G2 · PV_SUB  (53 − 14)</t>
+          <t>G3 · PV_SUB  (46 − 28)</t>
         </is>
       </c>
       <c r="D112" s="16" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t>vo_g2_correct</t>
+          <t>vo_h_recount</t>
         </is>
       </c>
       <c r="F112" s="19" t="inlineStr">
         <is>
-          <t>शाबाश! 53 घटा 14 बराबर 39।</t>
+          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
         </is>
       </c>
       <c r="G112" s="18" t="inlineStr">
         <is>
-          <t>correct answer</t>
+          <t>Hint 1 (1st wrong answer)</t>
         </is>
       </c>
       <c r="H112" s="18" t="inlineStr">
         <is>
-          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
-        </is>
-      </c>
-      <c r="I112" s="18" t="inlineStr"/>
+          <t>the columns beat on «दहाई» / «इकाई»</t>
+        </is>
+      </c>
+      <c r="I112" s="18" t="inlineStr">
+        <is>
+          <t>Page 5, Page 6, Page 8, Page 9</t>
+        </is>
+      </c>
       <c r="J112" s="16" t="n">
-        <v>4.48</v>
+        <v>3.31</v>
       </c>
       <c r="K112" s="17" t="inlineStr">
         <is>
@@ -5935,31 +5915,31 @@
         </is>
       </c>
       <c r="D113" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>vo_g3_prompt</t>
+          <t>vo_g3_h2</t>
         </is>
       </c>
       <c r="F113" s="15" t="inlineStr">
         <is>
-          <t>46 में से 28 घटाइए।</t>
+          <t>46 में से 28 घटाने पर, 1 दहाई और 8 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
-          <t>page instruction</t>
+          <t>Hint 2 (2nd wrong answer)</t>
         </is>
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
-          <t>as the page opens (the speaker replays it)</t>
+          <t>the numbers light; the tens and ones left beat on their words</t>
         </is>
       </c>
       <c r="I113" s="14" t="inlineStr"/>
       <c r="J113" s="12" t="n">
-        <v>2.72</v>
+        <v>5.55</v>
       </c>
       <c r="K113" s="13" t="inlineStr">
         <is>
@@ -5982,31 +5962,31 @@
         </is>
       </c>
       <c r="D114" s="16" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t>vo_g3_build</t>
+          <t>vo_g3_reveal</t>
         </is>
       </c>
       <c r="F114" s="19" t="inlineStr">
         <is>
-          <t>सबसे पहले ब्लॉक्स से 46 बनाइए।</t>
+          <t>46 में से 28 घटाने पर 18 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="G114" s="18" t="inlineStr">
         <is>
-          <t>build instruction</t>
+          <t>Hint 3 (3rd wrong answer)</t>
         </is>
       </c>
       <c r="H114" s="18" t="inlineStr">
         <is>
-          <t>after the instruction; the + box comes in, the rod + pulses on its «… दहाई» (or the number), the cube + on «… इकाई»</t>
+          <t>the right card / the right keys lit (one key at a time), the others off</t>
         </is>
       </c>
       <c r="I114" s="18" t="inlineStr"/>
       <c r="J114" s="16" t="n">
-        <v>3.92</v>
+        <v>5.75</v>
       </c>
       <c r="K114" s="17" t="inlineStr">
         <is>
@@ -6029,35 +6009,31 @@
         </is>
       </c>
       <c r="D115" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>vo_idle_build_t</t>
+          <t>vo_g3_correct</t>
         </is>
       </c>
       <c r="F115" s="15" t="inlineStr">
         <is>
-          <t>अब दहाई बनाइए।</t>
+          <t>शाबाश! 46 घटा 28 बराबर 18।</t>
         </is>
       </c>
       <c r="G115" s="14" t="inlineStr">
         <is>
-          <t>inactivity reminder - building</t>
+          <t>correct answer</t>
         </is>
       </c>
       <c r="H115" s="14" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the build step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I115" s="14" t="inlineStr">
-        <is>
-          <t>Page 4, Page 5, Page 6, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
+        </is>
+      </c>
+      <c r="I115" s="14" t="inlineStr"/>
       <c r="J115" s="12" t="n">
-        <v>1.95</v>
+        <v>4.99</v>
       </c>
       <c r="K115" s="13" t="inlineStr">
         <is>
@@ -6066,53 +6042,49 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="16" t="n">
+      <c r="A116" s="8" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="17" t="inlineStr">
-        <is>
-          <t>Page 7</t>
-        </is>
-      </c>
-      <c r="C116" s="18" t="inlineStr">
-        <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
-        </is>
-      </c>
-      <c r="D116" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E116" s="17" t="inlineStr">
-        <is>
-          <t>vo_idle_build_o</t>
-        </is>
-      </c>
-      <c r="F116" s="19" t="inlineStr">
-        <is>
-          <t>अब इकाई बनाइए।</t>
-        </is>
-      </c>
-      <c r="G116" s="18" t="inlineStr">
-        <is>
-          <t>inactivity reminder - building</t>
-        </is>
-      </c>
-      <c r="H116" s="18" t="inlineStr">
-        <is>
-          <t>after 7s with no tap at the build step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I116" s="18" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 8, Page 9</t>
-        </is>
-      </c>
-      <c r="J116" s="16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="K116" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
+      <c r="B116" s="9" t="inlineStr">
+        <is>
+          <t>Transition 3</t>
+        </is>
+      </c>
+      <c r="C116" s="10" t="inlineStr">
+        <is>
+          <t>before page 8</t>
+        </is>
+      </c>
+      <c r="D116" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E116" s="9" t="inlineStr">
+        <is>
+          <t>vo_pt_practice</t>
+        </is>
+      </c>
+      <c r="F116" s="11" t="inlineStr">
+        <is>
+          <t>वाह! अब आपकी बारी।</t>
+        </is>
+      </c>
+      <c r="G116" s="10" t="inlineStr">
+        <is>
+          <t>transition line</t>
+        </is>
+      </c>
+      <c r="H116" s="10" t="inlineStr">
+        <is>
+          <t>Swiftee rises talking; «अब आपकी बारी!» wipes in as it is said</t>
+        </is>
+      </c>
+      <c r="I116" s="10" t="inlineStr"/>
+      <c r="J116" s="8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="K116" s="9" t="inlineStr">
+        <is>
+          <t>Copied (HI02H11, recorded voice)</t>
         </is>
       </c>
     </row>
@@ -6122,40 +6094,40 @@
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D117" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>vo_g3_sub</t>
+          <t>vo_p1_prompt</t>
         </is>
       </c>
       <c r="F117" s="15" t="inlineStr">
         <is>
-          <t>और अब इसमें से 28 घटाइए।</t>
+          <t>74 में से 58 घटाइए।</t>
         </is>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
-          <t>what is taken away</t>
+          <t>page instruction</t>
         </is>
       </c>
       <c r="H117" s="14" t="inlineStr">
         <is>
-          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
+          <t>as the page opens (the speaker replays it)</t>
         </is>
       </c>
       <c r="I117" s="14" t="inlineStr"/>
       <c r="J117" s="12" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="K117" s="13" t="inlineStr">
         <is>
@@ -6169,44 +6141,40 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C118" s="18" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D118" s="16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t>vo_idle_open</t>
+          <t>vo_p1_sub</t>
         </is>
       </c>
       <c r="F118" s="19" t="inlineStr">
         <is>
-          <t>अब 1 दहाई को इकाई में लाइए।</t>
+          <t>और अब इसमें से 58 घटाते हैं।</t>
         </is>
       </c>
       <c r="G118" s="18" t="inlineStr">
         <is>
-          <t>inactivity reminder - open a ten</t>
+          <t>what is taken away</t>
         </is>
       </c>
       <c r="H118" s="18" t="inlineStr">
         <is>
-          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
-        </is>
-      </c>
-      <c r="I118" s="18" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
+        </is>
+      </c>
+      <c r="I118" s="18" t="inlineStr"/>
       <c r="J118" s="16" t="n">
-        <v>3.16</v>
+        <v>3.69</v>
       </c>
       <c r="K118" s="17" t="inlineStr">
         <is>
@@ -6220,40 +6188,44 @@
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C119" s="14" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D119" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E119" s="13" t="inlineStr">
         <is>
-          <t>vo_g3_rm_ones</t>
+          <t>vo_idle_open</t>
         </is>
       </c>
       <c r="F119" s="15" t="inlineStr">
         <is>
-          <t>इसमें से 8 इकाई को हटाइए।</t>
+          <t>अब 1 दहाई को इकाई में लाइए।</t>
         </is>
       </c>
       <c r="G119" s="14" t="inlineStr">
         <is>
-          <t>take-away step - the ones</t>
+          <t>inactivity reminder - open a ten</t>
         </is>
       </c>
       <c r="H119" s="14" t="inlineStr">
         <is>
-          <t>after the ten is opened; the ones column beats on «इकाई»</t>
-        </is>
-      </c>
-      <c r="I119" s="14" t="inlineStr"/>
+          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
+        </is>
+      </c>
+      <c r="I119" s="14" t="inlineStr">
+        <is>
+          <t>Page 5, Page 6, Page 7, Page 9</t>
+        </is>
+      </c>
       <c r="J119" s="12" t="n">
-        <v>3.03</v>
+        <v>3.16</v>
       </c>
       <c r="K119" s="13" t="inlineStr">
         <is>
@@ -6267,44 +6239,40 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C120" s="18" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D120" s="16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t>vo_num_1</t>
+          <t>vo_p1_rm_ones</t>
         </is>
       </c>
       <c r="F120" s="19" t="inlineStr">
         <is>
-          <t>एक।</t>
+          <t>14 इकाई में से 8 इकाई हटाइए।</t>
         </is>
       </c>
       <c r="G120" s="18" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>take-away step - the ones</t>
         </is>
       </c>
       <c r="H120" s="18" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
-        </is>
-      </c>
-      <c r="I120" s="18" t="inlineStr">
-        <is>
-          <t>Page 2, Page 4, Page 5, Page 6</t>
-        </is>
-      </c>
+          <t>after the ten is opened; the ones column beats on «इकाई»</t>
+        </is>
+      </c>
+      <c r="I120" s="18" t="inlineStr"/>
       <c r="J120" s="16" t="n">
-        <v>1.32</v>
+        <v>3.33</v>
       </c>
       <c r="K120" s="17" t="inlineStr">
         <is>
@@ -6318,44 +6286,40 @@
       </c>
       <c r="B121" s="13" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D121" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>vo_num_2</t>
+          <t>vo_p1_rm_tens</t>
         </is>
       </c>
       <c r="F121" s="15" t="inlineStr">
         <is>
-          <t>दो।</t>
+          <t>अब दहाइयाँ घटाइए।</t>
         </is>
       </c>
       <c r="G121" s="14" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>take-away step - the tens</t>
         </is>
       </c>
       <c r="H121" s="14" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
-        </is>
-      </c>
-      <c r="I121" s="14" t="inlineStr">
-        <is>
-          <t>Page 2, Page 4, Page 5, Page 6</t>
-        </is>
-      </c>
+          <t>when the ones are done; the tens column beats</t>
+        </is>
+      </c>
+      <c r="I121" s="14" t="inlineStr"/>
       <c r="J121" s="12" t="n">
-        <v>1.05</v>
+        <v>2.63</v>
       </c>
       <c r="K121" s="13" t="inlineStr">
         <is>
@@ -6369,44 +6333,44 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D122" s="16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t>vo_num_3</t>
+          <t>vo_idle_rm_o</t>
         </is>
       </c>
       <c r="F122" s="19" t="inlineStr">
         <is>
-          <t>तीन।</t>
+          <t>अब इकाई हटाइए।</t>
         </is>
       </c>
       <c r="G122" s="18" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H122" s="18" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
         </is>
       </c>
       <c r="I122" s="18" t="inlineStr">
         <is>
-          <t>Page 2, Page 4, Page 5, Page 6</t>
+          <t>Page 4, Page 5, Page 6, Page 7, Page 9</t>
         </is>
       </c>
       <c r="J122" s="16" t="n">
-        <v>1.07</v>
+        <v>2.21</v>
       </c>
       <c r="K122" s="17" t="inlineStr">
         <is>
@@ -6420,44 +6384,44 @@
       </c>
       <c r="B123" s="13" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C123" s="14" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D123" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>vo_num_4</t>
+          <t>vo_idle_rm_t</t>
         </is>
       </c>
       <c r="F123" s="15" t="inlineStr">
         <is>
-          <t>चार।</t>
+          <t>अब दहाई हटाइए।</t>
         </is>
       </c>
       <c r="G123" s="14" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H123" s="14" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
         </is>
       </c>
       <c r="I123" s="14" t="inlineStr">
         <is>
-          <t>Page 2, Page 4, Page 5, Page 6</t>
+          <t>Page 4, Page 5, Page 6, Page 7, Page 9</t>
         </is>
       </c>
       <c r="J123" s="12" t="n">
-        <v>1.17</v>
+        <v>2.27</v>
       </c>
       <c r="K123" s="13" t="inlineStr">
         <is>
@@ -6471,44 +6435,44 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C124" s="18" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D124" s="16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t>vo_num_5</t>
+          <t>vo_rm_tens_more</t>
         </is>
       </c>
       <c r="F124" s="19" t="inlineStr">
         <is>
-          <t>पाँच।</t>
+          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
         </is>
       </c>
       <c r="G124" s="18" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>take-away mistake - 1st time</t>
         </is>
       </c>
       <c r="H124" s="18" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
+          <t>a ten too many taken: the tens go back, this line</t>
         </is>
       </c>
       <c r="I124" s="18" t="inlineStr">
         <is>
-          <t>Page 2, Page 4, Page 5</t>
+          <t>Page 5, Page 6, Page 7, Page 9</t>
         </is>
       </c>
       <c r="J124" s="16" t="n">
-        <v>1.32</v>
+        <v>4.05</v>
       </c>
       <c r="K124" s="17" t="inlineStr">
         <is>
@@ -6522,44 +6486,44 @@
       </c>
       <c r="B125" s="13" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C125" s="14" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D125" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>vo_num_6</t>
+          <t>vo_rm_guide</t>
         </is>
       </c>
       <c r="F125" s="15" t="inlineStr">
         <is>
-          <t>छः।</t>
+          <t>इनमें से इतने हटाइए।</t>
         </is>
       </c>
       <c r="G125" s="14" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>take-away mistake - 2nd time</t>
         </is>
       </c>
       <c r="H125" s="14" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
+          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
         </is>
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>Page 2, Page 4, Page 5</t>
+          <t>Page 5, Page 6, Page 7, Page 9</t>
         </is>
       </c>
       <c r="J125" s="12" t="n">
-        <v>1.19</v>
+        <v>2.09</v>
       </c>
       <c r="K125" s="13" t="inlineStr">
         <is>
@@ -6573,44 +6537,44 @@
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C126" s="18" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D126" s="16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t>vo_num_7</t>
+          <t>vo_p1_ask</t>
         </is>
       </c>
       <c r="F126" s="19" t="inlineStr">
         <is>
-          <t>सात।</t>
+          <t>अब कितने बचे? नीचे डिब्बे पर टैप करके सही संख्या लिखिए।</t>
         </is>
       </c>
       <c r="G126" s="18" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>the answer question</t>
         </is>
       </c>
       <c r="H126" s="18" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
+          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
         </is>
       </c>
       <c r="I126" s="18" t="inlineStr">
         <is>
-          <t>Page 4, Page 5</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="J126" s="16" t="n">
-        <v>1.45</v>
+        <v>4.39</v>
       </c>
       <c r="K126" s="17" t="inlineStr">
         <is>
@@ -6624,40 +6588,44 @@
       </c>
       <c r="B127" s="13" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C127" s="14" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D127" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>vo_num_8</t>
+          <t>vo_h_recount</t>
         </is>
       </c>
       <c r="F127" s="15" t="inlineStr">
         <is>
-          <t>आठ।</t>
+          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
         </is>
       </c>
       <c r="G127" s="14" t="inlineStr">
         <is>
-          <t>the count</t>
+          <t>Hint 1 (1st wrong answer)</t>
         </is>
       </c>
       <c r="H127" s="14" t="inlineStr">
         <is>
-          <t>one per one the child takes away: «एक», «दो» … (the next tap waits for it)</t>
-        </is>
-      </c>
-      <c r="I127" s="14" t="inlineStr"/>
+          <t>the columns beat on «दहाई» / «इकाई»</t>
+        </is>
+      </c>
+      <c r="I127" s="14" t="inlineStr">
+        <is>
+          <t>Page 5, Page 6, Page 7, Page 9</t>
+        </is>
+      </c>
       <c r="J127" s="12" t="n">
-        <v>1.08</v>
+        <v>3.31</v>
       </c>
       <c r="K127" s="13" t="inlineStr">
         <is>
@@ -6671,40 +6639,40 @@
       </c>
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C128" s="18" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D128" s="16" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t>vo_g3_rm_tens</t>
+          <t>vo_p1_h2</t>
         </is>
       </c>
       <c r="F128" s="19" t="inlineStr">
         <is>
-          <t>अब दहाइयाँ हटाइए।</t>
+          <t>74 में से 58 घटाने पर, 1 दहाई और 6 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="G128" s="18" t="inlineStr">
         <is>
-          <t>take-away step - the tens</t>
+          <t>Hint 2 (2nd wrong answer)</t>
         </is>
       </c>
       <c r="H128" s="18" t="inlineStr">
         <is>
-          <t>when the ones are done; the tens column beats</t>
+          <t>the numbers light; the tens and ones left beat on their words</t>
         </is>
       </c>
       <c r="I128" s="18" t="inlineStr"/>
       <c r="J128" s="16" t="n">
-        <v>2.47</v>
+        <v>5.45</v>
       </c>
       <c r="K128" s="17" t="inlineStr">
         <is>
@@ -6718,44 +6686,40 @@
       </c>
       <c r="B129" s="13" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C129" s="14" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D129" s="12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>vo_idle_rm_o</t>
+          <t>vo_p1_reveal</t>
         </is>
       </c>
       <c r="F129" s="15" t="inlineStr">
         <is>
-          <t>अब इकाई हटाइए।</t>
+          <t>74 में से 58 घटाने पर 16 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
-          <t>inactivity reminder - taking away</t>
+          <t>Hint 3 (3rd wrong answer)</t>
         </is>
       </c>
       <c r="H129" s="14" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I129" s="14" t="inlineStr">
-        <is>
-          <t>Page 4, Page 5, Page 6, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>the right card / the right keys lit (one key at a time), the others off</t>
+        </is>
+      </c>
+      <c r="I129" s="14" t="inlineStr"/>
       <c r="J129" s="12" t="n">
-        <v>2.21</v>
+        <v>5.69</v>
       </c>
       <c r="K129" s="13" t="inlineStr">
         <is>
@@ -6769,44 +6733,40 @@
       </c>
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C130" s="18" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D130" s="16" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t>vo_idle_rm_t</t>
+          <t>vo_p1_correct</t>
         </is>
       </c>
       <c r="F130" s="19" t="inlineStr">
         <is>
-          <t>अब दहाई हटाइए।</t>
+          <t>शाबाश! 74 में से 58 घटाने पर हमें मिला 16।</t>
         </is>
       </c>
       <c r="G130" s="18" t="inlineStr">
         <is>
-          <t>inactivity reminder - taking away</t>
+          <t>correct answer</t>
         </is>
       </c>
       <c r="H130" s="18" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I130" s="18" t="inlineStr">
-        <is>
-          <t>Page 4, Page 5, Page 6, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
+        </is>
+      </c>
+      <c r="I130" s="18" t="inlineStr"/>
       <c r="J130" s="16" t="n">
-        <v>2.27</v>
+        <v>5.01</v>
       </c>
       <c r="K130" s="17" t="inlineStr">
         <is>
@@ -6820,44 +6780,40 @@
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C131" s="14" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D131" s="12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>vo_rm_tens_more</t>
+          <t>vo_p2_prompt</t>
         </is>
       </c>
       <c r="F131" s="15" t="inlineStr">
         <is>
-          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
+          <t>61 में से 35 घटाइए।</t>
         </is>
       </c>
       <c r="G131" s="14" t="inlineStr">
         <is>
-          <t>take-away mistake - 1st time</t>
+          <t>page instruction</t>
         </is>
       </c>
       <c r="H131" s="14" t="inlineStr">
         <is>
-          <t>a ten too many taken: the tens go back, this line</t>
-        </is>
-      </c>
-      <c r="I131" s="14" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>as the page opens (the speaker replays it)</t>
+        </is>
+      </c>
+      <c r="I131" s="14" t="inlineStr"/>
       <c r="J131" s="12" t="n">
-        <v>4.05</v>
+        <v>2.48</v>
       </c>
       <c r="K131" s="13" t="inlineStr">
         <is>
@@ -6871,44 +6827,40 @@
       </c>
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C132" s="18" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D132" s="16" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t>vo_rm_guide</t>
+          <t>vo_p2_sub</t>
         </is>
       </c>
       <c r="F132" s="19" t="inlineStr">
         <is>
-          <t>इनमें से इतने हटाइए।</t>
+          <t>और अब इसमें से 35 घटाते हैं।</t>
         </is>
       </c>
       <c r="G132" s="18" t="inlineStr">
         <is>
-          <t>take-away mistake - 2nd time</t>
+          <t>what is taken away</t>
         </is>
       </c>
       <c r="H132" s="18" t="inlineStr">
         <is>
-          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
-        </is>
-      </c>
-      <c r="I132" s="18" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
+        </is>
+      </c>
+      <c r="I132" s="18" t="inlineStr"/>
       <c r="J132" s="16" t="n">
-        <v>2.09</v>
+        <v>2.86</v>
       </c>
       <c r="K132" s="17" t="inlineStr">
         <is>
@@ -6922,44 +6874,44 @@
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C133" s="14" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D133" s="12" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>vo_ask_pick</t>
+          <t>vo_idle_open</t>
         </is>
       </c>
       <c r="F133" s="15" t="inlineStr">
         <is>
-          <t>अब कितने बचे? सही संख्या चुनिए।</t>
+          <t>अब 1 दहाई को इकाई में लाइए।</t>
         </is>
       </c>
       <c r="G133" s="14" t="inlineStr">
         <is>
-          <t>the answer question</t>
+          <t>inactivity reminder - open a ten</t>
         </is>
       </c>
       <c r="H133" s="14" t="inlineStr">
         <is>
-          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
+          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
         </is>
       </c>
       <c r="I133" s="14" t="inlineStr">
         <is>
-          <t>Page 5, Page 6</t>
+          <t>Page 5, Page 6, Page 7, Page 8</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
-        <v>3.2</v>
+        <v>3.16</v>
       </c>
       <c r="K133" s="13" t="inlineStr">
         <is>
@@ -6973,44 +6925,40 @@
       </c>
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C134" s="18" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D134" s="16" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="E134" s="17" t="inlineStr">
         <is>
-          <t>vo_h_recount</t>
+          <t>vo_p2_rm_ones</t>
         </is>
       </c>
       <c r="F134" s="19" t="inlineStr">
         <is>
-          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
+          <t>इकाई हटाइए।</t>
         </is>
       </c>
       <c r="G134" s="18" t="inlineStr">
         <is>
-          <t>Hint 1 (1st wrong answer)</t>
+          <t>take-away step - the ones</t>
         </is>
       </c>
       <c r="H134" s="18" t="inlineStr">
         <is>
-          <t>the columns beat on «दहाई» / «इकाई»</t>
-        </is>
-      </c>
-      <c r="I134" s="18" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>after the ten is opened; the ones column beats on «इकाई»</t>
+        </is>
+      </c>
+      <c r="I134" s="18" t="inlineStr"/>
       <c r="J134" s="16" t="n">
-        <v>3.31</v>
+        <v>1.81</v>
       </c>
       <c r="K134" s="17" t="inlineStr">
         <is>
@@ -7024,40 +6972,40 @@
       </c>
       <c r="B135" s="13" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C135" s="14" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D135" s="12" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>vo_g3_h2</t>
+          <t>vo_p2_rm_tens</t>
         </is>
       </c>
       <c r="F135" s="15" t="inlineStr">
         <is>
-          <t>46 में से 28 घटाने पर, 1 दहाई और 8 इकाई बचती हैं।</t>
+          <t>अब दहाइयाँ हटाइए।</t>
         </is>
       </c>
       <c r="G135" s="14" t="inlineStr">
         <is>
-          <t>Hint 2 (2nd wrong answer)</t>
+          <t>take-away step - the tens</t>
         </is>
       </c>
       <c r="H135" s="14" t="inlineStr">
         <is>
-          <t>the numbers light; the tens and ones left beat on their words</t>
+          <t>when the ones are done; the tens column beats</t>
         </is>
       </c>
       <c r="I135" s="14" t="inlineStr"/>
       <c r="J135" s="12" t="n">
-        <v>5.55</v>
+        <v>1.95</v>
       </c>
       <c r="K135" s="13" t="inlineStr">
         <is>
@@ -7071,40 +7019,44 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C136" s="18" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D136" s="16" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E136" s="17" t="inlineStr">
         <is>
-          <t>vo_g3_reveal</t>
+          <t>vo_idle_rm_o</t>
         </is>
       </c>
       <c r="F136" s="19" t="inlineStr">
         <is>
-          <t>46 में से 28 घटाने पर 18 बचता है। तो सही संख्या यह है।</t>
+          <t>अब इकाई हटाइए।</t>
         </is>
       </c>
       <c r="G136" s="18" t="inlineStr">
         <is>
-          <t>Hint 3 (3rd wrong answer)</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H136" s="18" t="inlineStr">
         <is>
-          <t>the right card / the right keys lit (one key at a time), the others off</t>
-        </is>
-      </c>
-      <c r="I136" s="18" t="inlineStr"/>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
+        </is>
+      </c>
+      <c r="I136" s="18" t="inlineStr">
+        <is>
+          <t>Page 4, Page 5, Page 6, Page 7, Page 8</t>
+        </is>
+      </c>
       <c r="J136" s="16" t="n">
-        <v>5.75</v>
+        <v>2.21</v>
       </c>
       <c r="K136" s="17" t="inlineStr">
         <is>
@@ -7118,40 +7070,44 @@
       </c>
       <c r="B137" s="13" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C137" s="14" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D137" s="12" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>vo_g3_correct</t>
+          <t>vo_idle_rm_t</t>
         </is>
       </c>
       <c r="F137" s="15" t="inlineStr">
         <is>
-          <t>शाबाश! 46 घटा 28 बराबर 18।</t>
+          <t>अब दहाई हटाइए।</t>
         </is>
       </c>
       <c r="G137" s="14" t="inlineStr">
         <is>
-          <t>correct answer</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H137" s="14" t="inlineStr">
         <is>
-          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
-        </is>
-      </c>
-      <c r="I137" s="14" t="inlineStr"/>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
+        </is>
+      </c>
+      <c r="I137" s="14" t="inlineStr">
+        <is>
+          <t>Page 4, Page 5, Page 6, Page 7, Page 8</t>
+        </is>
+      </c>
       <c r="J137" s="12" t="n">
-        <v>4.99</v>
+        <v>2.27</v>
       </c>
       <c r="K137" s="13" t="inlineStr">
         <is>
@@ -7160,49 +7116,53 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="8" t="n">
+      <c r="A138" s="16" t="n">
         <v>134</v>
       </c>
-      <c r="B138" s="9" t="inlineStr">
-        <is>
-          <t>Transition 3</t>
-        </is>
-      </c>
-      <c r="C138" s="10" t="inlineStr">
-        <is>
-          <t>before page 8</t>
-        </is>
-      </c>
-      <c r="D138" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" s="9" t="inlineStr">
-        <is>
-          <t>vo_pt_practice</t>
-        </is>
-      </c>
-      <c r="F138" s="11" t="inlineStr">
-        <is>
-          <t>वाह! अब आपकी बारी।</t>
-        </is>
-      </c>
-      <c r="G138" s="10" t="inlineStr">
-        <is>
-          <t>transition line</t>
-        </is>
-      </c>
-      <c r="H138" s="10" t="inlineStr">
-        <is>
-          <t>Swiftee rises talking; «अब आपकी बारी!» wipes in as it is said</t>
-        </is>
-      </c>
-      <c r="I138" s="10" t="inlineStr"/>
-      <c r="J138" s="8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="K138" s="9" t="inlineStr">
-        <is>
-          <t>Copied (HI02H11, recorded voice)</t>
+      <c r="B138" s="17" t="inlineStr">
+        <is>
+          <t>Page 9</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="inlineStr">
+        <is>
+          <t>P2 · PV_SUB  (61 − 35)</t>
+        </is>
+      </c>
+      <c r="D138" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="E138" s="17" t="inlineStr">
+        <is>
+          <t>vo_rm_tens_more</t>
+        </is>
+      </c>
+      <c r="F138" s="19" t="inlineStr">
+        <is>
+          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
+        </is>
+      </c>
+      <c r="G138" s="18" t="inlineStr">
+        <is>
+          <t>take-away mistake - 1st time</t>
+        </is>
+      </c>
+      <c r="H138" s="18" t="inlineStr">
+        <is>
+          <t>a ten too many taken: the tens go back, this line</t>
+        </is>
+      </c>
+      <c r="I138" s="18" t="inlineStr">
+        <is>
+          <t>Page 5, Page 6, Page 7, Page 8</t>
+        </is>
+      </c>
+      <c r="J138" s="16" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="K138" s="17" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
         </is>
       </c>
     </row>
@@ -7212,40 +7172,44 @@
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C139" s="14" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D139" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>vo_p1_prompt</t>
+          <t>vo_rm_guide</t>
         </is>
       </c>
       <c r="F139" s="15" t="inlineStr">
         <is>
-          <t>74 में से 58 घटाइए।</t>
+          <t>इनमें से इतने हटाइए।</t>
         </is>
       </c>
       <c r="G139" s="14" t="inlineStr">
         <is>
-          <t>page instruction</t>
+          <t>take-away mistake - 2nd time</t>
         </is>
       </c>
       <c r="H139" s="14" t="inlineStr">
         <is>
-          <t>as the page opens (the speaker replays it)</t>
-        </is>
-      </c>
-      <c r="I139" s="14" t="inlineStr"/>
+          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
+        </is>
+      </c>
+      <c r="I139" s="14" t="inlineStr">
+        <is>
+          <t>Page 5, Page 6, Page 7, Page 8</t>
+        </is>
+      </c>
       <c r="J139" s="12" t="n">
-        <v>2.5</v>
+        <v>2.09</v>
       </c>
       <c r="K139" s="13" t="inlineStr">
         <is>
@@ -7259,40 +7223,44 @@
       </c>
       <c r="B140" s="17" t="inlineStr">
         <is>
+          <t>Page 9</t>
+        </is>
+      </c>
+      <c r="C140" s="18" t="inlineStr">
+        <is>
+          <t>P2 · PV_SUB  (61 − 35)</t>
+        </is>
+      </c>
+      <c r="D140" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E140" s="17" t="inlineStr">
+        <is>
+          <t>vo_p1_ask</t>
+        </is>
+      </c>
+      <c r="F140" s="19" t="inlineStr">
+        <is>
+          <t>अब कितने बचे? नीचे डिब्बे पर टैप करके सही संख्या लिखिए।</t>
+        </is>
+      </c>
+      <c r="G140" s="18" t="inlineStr">
+        <is>
+          <t>the answer question</t>
+        </is>
+      </c>
+      <c r="H140" s="18" t="inlineStr">
+        <is>
+          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
+        </is>
+      </c>
+      <c r="I140" s="18" t="inlineStr">
+        <is>
           <t>Page 8</t>
         </is>
       </c>
-      <c r="C140" s="18" t="inlineStr">
-        <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
-        </is>
-      </c>
-      <c r="D140" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E140" s="17" t="inlineStr">
-        <is>
-          <t>vo_p1_build</t>
-        </is>
-      </c>
-      <c r="F140" s="19" t="inlineStr">
-        <is>
-          <t>सबसे पहले ब्लॉक्स से 74 बनाइए।</t>
-        </is>
-      </c>
-      <c r="G140" s="18" t="inlineStr">
-        <is>
-          <t>build instruction</t>
-        </is>
-      </c>
-      <c r="H140" s="18" t="inlineStr">
-        <is>
-          <t>after the instruction; the + box comes in, the rod + pulses on its «… दहाई» (or the number), the cube + on «… इकाई»</t>
-        </is>
-      </c>
-      <c r="I140" s="18" t="inlineStr"/>
       <c r="J140" s="16" t="n">
-        <v>3.45</v>
+        <v>4.39</v>
       </c>
       <c r="K140" s="17" t="inlineStr">
         <is>
@@ -7306,44 +7274,44 @@
       </c>
       <c r="B141" s="13" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C141" s="14" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D141" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>vo_idle_build_t</t>
+          <t>vo_h_recount</t>
         </is>
       </c>
       <c r="F141" s="15" t="inlineStr">
         <is>
-          <t>अब दहाई बनाइए।</t>
+          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
         </is>
       </c>
       <c r="G141" s="14" t="inlineStr">
         <is>
-          <t>inactivity reminder - building</t>
+          <t>Hint 1 (1st wrong answer)</t>
         </is>
       </c>
       <c r="H141" s="14" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the build step, again every 7s while idle</t>
+          <t>the columns beat on «दहाई» / «इकाई»</t>
         </is>
       </c>
       <c r="I141" s="14" t="inlineStr">
         <is>
-          <t>Page 4, Page 5, Page 6, Page 7, Page 9</t>
+          <t>Page 5, Page 6, Page 7, Page 8</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
-        <v>1.95</v>
+        <v>3.31</v>
       </c>
       <c r="K141" s="13" t="inlineStr">
         <is>
@@ -7357,44 +7325,40 @@
       </c>
       <c r="B142" s="17" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C142" s="18" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D142" s="16" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E142" s="17" t="inlineStr">
         <is>
-          <t>vo_idle_build_o</t>
+          <t>vo_p2_h2</t>
         </is>
       </c>
       <c r="F142" s="19" t="inlineStr">
         <is>
-          <t>अब इकाई बनाइए।</t>
+          <t>61 में से 35 घटाने पर, 2 दहाई और 6 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="G142" s="18" t="inlineStr">
         <is>
-          <t>inactivity reminder - building</t>
+          <t>Hint 2 (2nd wrong answer)</t>
         </is>
       </c>
       <c r="H142" s="18" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the build step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I142" s="18" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 7, Page 9</t>
-        </is>
-      </c>
+          <t>the numbers light; the tens and ones left beat on their words</t>
+        </is>
+      </c>
+      <c r="I142" s="18" t="inlineStr"/>
       <c r="J142" s="16" t="n">
-        <v>1.85</v>
+        <v>5.81</v>
       </c>
       <c r="K142" s="17" t="inlineStr">
         <is>
@@ -7408,40 +7372,40 @@
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C143" s="14" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D143" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>vo_p1_sub</t>
+          <t>vo_p2_reveal</t>
         </is>
       </c>
       <c r="F143" s="15" t="inlineStr">
         <is>
-          <t>और अब इसमें से 58 घटाते हैं।</t>
+          <t>61 में से 35 घटाने पर 26 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="G143" s="14" t="inlineStr">
         <is>
-          <t>what is taken away</t>
+          <t>Hint 3 (3rd wrong answer)</t>
         </is>
       </c>
       <c r="H143" s="14" t="inlineStr">
         <is>
-          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
+          <t>the right card / the right keys lit (one key at a time), the others off</t>
         </is>
       </c>
       <c r="I143" s="14" t="inlineStr"/>
       <c r="J143" s="12" t="n">
-        <v>3.69</v>
+        <v>4.64</v>
       </c>
       <c r="K143" s="13" t="inlineStr">
         <is>
@@ -7455,44 +7419,40 @@
       </c>
       <c r="B144" s="17" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C144" s="18" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D144" s="16" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E144" s="17" t="inlineStr">
         <is>
-          <t>vo_idle_open</t>
+          <t>vo_p2_correct</t>
         </is>
       </c>
       <c r="F144" s="19" t="inlineStr">
         <is>
-          <t>अब 1 दहाई को इकाई में लाइए।</t>
+          <t>शाबाश! 61 में से 35 घटाने पर हमें मिला 26।</t>
         </is>
       </c>
       <c r="G144" s="18" t="inlineStr">
         <is>
-          <t>inactivity reminder - open a ten</t>
+          <t>correct answer</t>
         </is>
       </c>
       <c r="H144" s="18" t="inlineStr">
         <is>
-          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
-        </is>
-      </c>
-      <c r="I144" s="18" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 7, Page 9</t>
-        </is>
-      </c>
+          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
+        </is>
+      </c>
+      <c r="I144" s="18" t="inlineStr"/>
       <c r="J144" s="16" t="n">
-        <v>3.16</v>
+        <v>5.21</v>
       </c>
       <c r="K144" s="17" t="inlineStr">
         <is>
@@ -7506,40 +7466,40 @@
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="C145" s="14" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>P3 · MENTAL_SUB  (84 − 46)</t>
         </is>
       </c>
       <c r="D145" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>vo_p1_rm_ones</t>
+          <t>vo_p3_prompt</t>
         </is>
       </c>
       <c r="F145" s="15" t="inlineStr">
         <is>
-          <t>14 इकाई में से 8 इकाई हटाइए।</t>
+          <t>84 में से 46 घटाइए और सही संख्या चुनिए।</t>
         </is>
       </c>
       <c r="G145" s="14" t="inlineStr">
         <is>
-          <t>take-away step - the ones</t>
+          <t>page instruction</t>
         </is>
       </c>
       <c r="H145" s="14" t="inlineStr">
         <is>
-          <t>after the ten is opened; the ones column beats on «इकाई»</t>
+          <t>as the page opens (the speaker replays it)</t>
         </is>
       </c>
       <c r="I145" s="14" t="inlineStr"/>
       <c r="J145" s="12" t="n">
-        <v>3.33</v>
+        <v>4.51</v>
       </c>
       <c r="K145" s="13" t="inlineStr">
         <is>
@@ -7553,40 +7513,44 @@
       </c>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="C146" s="18" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>P3 · MENTAL_SUB  (84 − 46)</t>
         </is>
       </c>
       <c r="D146" s="16" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E146" s="17" t="inlineStr">
         <is>
-          <t>vo_p1_rm_tens</t>
+          <t>vo_h_order</t>
         </is>
       </c>
       <c r="F146" s="19" t="inlineStr">
         <is>
-          <t>अब दहाइयाँ घटाइए।</t>
+          <t>संख्याओं में से पहले इकाई घटाइए, फिर दहाई घटाइए।</t>
         </is>
       </c>
       <c r="G146" s="18" t="inlineStr">
         <is>
-          <t>take-away step - the tens</t>
+          <t>Hint 1 (1st wrong answer)</t>
         </is>
       </c>
       <c r="H146" s="18" t="inlineStr">
         <is>
-          <t>when the ones are done; the tens column beats</t>
-        </is>
-      </c>
-      <c r="I146" s="18" t="inlineStr"/>
+          <t>the ones digits light on «इकाई», the tens digits on «दहाई»</t>
+        </is>
+      </c>
+      <c r="I146" s="18" t="inlineStr">
+        <is>
+          <t>Page 11</t>
+        </is>
+      </c>
       <c r="J146" s="16" t="n">
-        <v>2.63</v>
+        <v>4.45</v>
       </c>
       <c r="K146" s="17" t="inlineStr">
         <is>
@@ -7600,44 +7564,40 @@
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="C147" s="14" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>P3 · MENTAL_SUB  (84 − 46)</t>
         </is>
       </c>
       <c r="D147" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>vo_idle_rm_o</t>
+          <t>vo_p3_h2</t>
         </is>
       </c>
       <c r="F147" s="15" t="inlineStr">
         <is>
-          <t>अब इकाई हटाइए।</t>
+          <t>84 में से 46 घटाने पर, 3 दहाई और 8 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="G147" s="14" t="inlineStr">
         <is>
-          <t>inactivity reminder - taking away</t>
+          <t>Hint 2 (2nd wrong answer)</t>
         </is>
       </c>
       <c r="H147" s="14" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I147" s="14" t="inlineStr">
-        <is>
-          <t>Page 4, Page 5, Page 6, Page 7, Page 9</t>
-        </is>
-      </c>
+          <t>the table comes in with the first number's blocks; the second number is taken away as it is said</t>
+        </is>
+      </c>
+      <c r="I147" s="14" t="inlineStr"/>
       <c r="J147" s="12" t="n">
-        <v>2.21</v>
+        <v>5.47</v>
       </c>
       <c r="K147" s="13" t="inlineStr">
         <is>
@@ -7651,44 +7611,40 @@
       </c>
       <c r="B148" s="17" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="C148" s="18" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>P3 · MENTAL_SUB  (84 − 46)</t>
         </is>
       </c>
       <c r="D148" s="16" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E148" s="17" t="inlineStr">
         <is>
-          <t>vo_idle_rm_t</t>
+          <t>vo_p3_reveal</t>
         </is>
       </c>
       <c r="F148" s="19" t="inlineStr">
         <is>
-          <t>अब दहाई हटाइए।</t>
+          <t>84 में से 46 घटाने पर 38 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="G148" s="18" t="inlineStr">
         <is>
-          <t>inactivity reminder - taking away</t>
+          <t>Hint 3 (3rd wrong answer)</t>
         </is>
       </c>
       <c r="H148" s="18" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I148" s="18" t="inlineStr">
-        <is>
-          <t>Page 4, Page 5, Page 6, Page 7, Page 9</t>
-        </is>
-      </c>
+          <t>the right card / the right keys lit (one key at a time), the others off</t>
+        </is>
+      </c>
+      <c r="I148" s="18" t="inlineStr"/>
       <c r="J148" s="16" t="n">
-        <v>2.27</v>
+        <v>5.52</v>
       </c>
       <c r="K148" s="17" t="inlineStr">
         <is>
@@ -7702,44 +7658,40 @@
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="C149" s="14" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>P3 · MENTAL_SUB  (84 − 46)</t>
         </is>
       </c>
       <c r="D149" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>vo_rm_tens_more</t>
+          <t>vo_p3_correct</t>
         </is>
       </c>
       <c r="F149" s="15" t="inlineStr">
         <is>
-          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
+          <t>शाबाश! आपने सही संख्या चुन ली। 84 घटा 46 बराबर 38।</t>
         </is>
       </c>
       <c r="G149" s="14" t="inlineStr">
         <is>
-          <t>take-away mistake - 1st time</t>
+          <t>correct answer</t>
         </is>
       </c>
       <c r="H149" s="14" t="inlineStr">
         <is>
-          <t>a ten too many taken: the tens go back, this line</t>
-        </is>
-      </c>
-      <c r="I149" s="14" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 7, Page 9</t>
-        </is>
-      </c>
+          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
+        </is>
+      </c>
+      <c r="I149" s="14" t="inlineStr"/>
       <c r="J149" s="12" t="n">
-        <v>4.05</v>
+        <v>6.91</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -7753,44 +7705,40 @@
       </c>
       <c r="B150" s="17" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 11</t>
         </is>
       </c>
       <c r="C150" s="18" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>P4 · MENTAL_SUB  (91 − 14)</t>
         </is>
       </c>
       <c r="D150" s="16" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E150" s="17" t="inlineStr">
         <is>
-          <t>vo_rm_guide</t>
+          <t>vo_p4_prompt</t>
         </is>
       </c>
       <c r="F150" s="19" t="inlineStr">
         <is>
-          <t>इनमें से इतने हटाइए।</t>
+          <t>91 में से 14 घटाइए और सही संख्या चुनिए।</t>
         </is>
       </c>
       <c r="G150" s="18" t="inlineStr">
         <is>
-          <t>take-away mistake - 2nd time</t>
+          <t>page instruction</t>
         </is>
       </c>
       <c r="H150" s="18" t="inlineStr">
         <is>
-          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
-        </is>
-      </c>
-      <c r="I150" s="18" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 7, Page 9</t>
-        </is>
-      </c>
+          <t>as the page opens (the speaker replays it)</t>
+        </is>
+      </c>
+      <c r="I150" s="18" t="inlineStr"/>
       <c r="J150" s="16" t="n">
-        <v>2.09</v>
+        <v>3.57</v>
       </c>
       <c r="K150" s="17" t="inlineStr">
         <is>
@@ -7804,44 +7752,44 @@
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 11</t>
         </is>
       </c>
       <c r="C151" s="14" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>P4 · MENTAL_SUB  (91 − 14)</t>
         </is>
       </c>
       <c r="D151" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E151" s="13" t="inlineStr">
         <is>
-          <t>vo_p1_ask</t>
+          <t>vo_h_order</t>
         </is>
       </c>
       <c r="F151" s="15" t="inlineStr">
         <is>
-          <t>अब कितने बचे? नीचे डिब्बे पर टैप करके सही संख्या लिखिए।</t>
+          <t>संख्याओं में से पहले इकाई घटाइए, फिर दहाई घटाइए।</t>
         </is>
       </c>
       <c r="G151" s="14" t="inlineStr">
         <is>
-          <t>the answer question</t>
+          <t>Hint 1 (1st wrong answer)</t>
         </is>
       </c>
       <c r="H151" s="14" t="inlineStr">
         <is>
-          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
+          <t>the ones digits light on «इकाई», the tens digits on «दहाई»</t>
         </is>
       </c>
       <c r="I151" s="14" t="inlineStr">
         <is>
-          <t>Page 9</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
-        <v>4.39</v>
+        <v>4.45</v>
       </c>
       <c r="K151" s="13" t="inlineStr">
         <is>
@@ -7855,44 +7803,40 @@
       </c>
       <c r="B152" s="17" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 11</t>
         </is>
       </c>
       <c r="C152" s="18" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>P4 · MENTAL_SUB  (91 − 14)</t>
         </is>
       </c>
       <c r="D152" s="16" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="E152" s="17" t="inlineStr">
         <is>
-          <t>vo_h_recount</t>
+          <t>vo_p4_h2</t>
         </is>
       </c>
       <c r="F152" s="19" t="inlineStr">
         <is>
-          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
+          <t>91 में से 14 घटाने पर, 7 दहाई और 7 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="G152" s="18" t="inlineStr">
         <is>
-          <t>Hint 1 (1st wrong answer)</t>
+          <t>Hint 2 (2nd wrong answer)</t>
         </is>
       </c>
       <c r="H152" s="18" t="inlineStr">
         <is>
-          <t>the columns beat on «दहाई» / «इकाई»</t>
-        </is>
-      </c>
-      <c r="I152" s="18" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 7, Page 9</t>
-        </is>
-      </c>
+          <t>the table comes in with the first number's blocks; the second number is taken away as it is said</t>
+        </is>
+      </c>
+      <c r="I152" s="18" t="inlineStr"/>
       <c r="J152" s="16" t="n">
-        <v>3.31</v>
+        <v>5.17</v>
       </c>
       <c r="K152" s="17" t="inlineStr">
         <is>
@@ -7906,40 +7850,40 @@
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 11</t>
         </is>
       </c>
       <c r="C153" s="14" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>P4 · MENTAL_SUB  (91 − 14)</t>
         </is>
       </c>
       <c r="D153" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>vo_p1_h2</t>
+          <t>vo_p4_reveal</t>
         </is>
       </c>
       <c r="F153" s="15" t="inlineStr">
         <is>
-          <t>74 में से 58 घटाने पर, 1 दहाई और 6 इकाई बचती हैं।</t>
+          <t>91 में से 14 घटाने पर 77 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="G153" s="14" t="inlineStr">
         <is>
-          <t>Hint 2 (2nd wrong answer)</t>
+          <t>Hint 3 (3rd wrong answer)</t>
         </is>
       </c>
       <c r="H153" s="14" t="inlineStr">
         <is>
-          <t>the numbers light; the tens and ones left beat on their words</t>
+          <t>the right card / the right keys lit (one key at a time), the others off</t>
         </is>
       </c>
       <c r="I153" s="14" t="inlineStr"/>
       <c r="J153" s="12" t="n">
-        <v>5.45</v>
+        <v>6.49</v>
       </c>
       <c r="K153" s="13" t="inlineStr">
         <is>
@@ -7953,40 +7897,40 @@
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 11</t>
         </is>
       </c>
       <c r="C154" s="18" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>P4 · MENTAL_SUB  (91 − 14)</t>
         </is>
       </c>
       <c r="D154" s="16" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E154" s="17" t="inlineStr">
         <is>
-          <t>vo_p1_reveal</t>
+          <t>vo_p4_correct</t>
         </is>
       </c>
       <c r="F154" s="19" t="inlineStr">
         <is>
-          <t>74 में से 58 घटाने पर 16 बचता है। तो सही संख्या यह है।</t>
+          <t>शाबाश! आपने सही संख्या चुन ली। 91 घटा 14 बराबर 77।</t>
         </is>
       </c>
       <c r="G154" s="18" t="inlineStr">
         <is>
-          <t>Hint 3 (3rd wrong answer)</t>
+          <t>correct answer</t>
         </is>
       </c>
       <c r="H154" s="18" t="inlineStr">
         <is>
-          <t>the right card / the right keys lit (one key at a time), the others off</t>
+          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
         </is>
       </c>
       <c r="I154" s="18" t="inlineStr"/>
       <c r="J154" s="16" t="n">
-        <v>5.69</v>
+        <v>7.04</v>
       </c>
       <c r="K154" s="17" t="inlineStr">
         <is>
@@ -7995,1407 +7939,47 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="12" t="n">
+      <c r="A155" s="20" t="n">
         <v>151</v>
       </c>
-      <c r="B155" s="13" t="inlineStr">
-        <is>
-          <t>Page 8</t>
-        </is>
-      </c>
-      <c r="C155" s="14" t="inlineStr">
-        <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
-        </is>
-      </c>
-      <c r="D155" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="E155" s="13" t="inlineStr">
-        <is>
-          <t>vo_p1_correct</t>
-        </is>
-      </c>
-      <c r="F155" s="15" t="inlineStr">
-        <is>
-          <t>शाबाश! 74 में से 58 घटाने पर हमें मिला 16।</t>
-        </is>
-      </c>
-      <c r="G155" s="14" t="inlineStr">
-        <is>
-          <t>correct answer</t>
-        </is>
-      </c>
-      <c r="H155" s="14" t="inlineStr">
-        <is>
-          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
-        </is>
-      </c>
-      <c r="I155" s="14" t="inlineStr"/>
-      <c r="J155" s="12" t="n">
-        <v>5.01</v>
-      </c>
-      <c r="K155" s="13" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="16" t="n">
-        <v>152</v>
-      </c>
-      <c r="B156" s="17" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C156" s="18" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D156" s="16" t="n">
+      <c r="B155" s="21" t="inlineStr">
+        <is>
+          <t>Celebration</t>
+        </is>
+      </c>
+      <c r="C155" s="22" t="inlineStr">
+        <is>
+          <t>CEL · CELEBRATION</t>
+        </is>
+      </c>
+      <c r="D155" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E156" s="17" t="inlineStr">
-        <is>
-          <t>vo_p2_prompt</t>
-        </is>
-      </c>
-      <c r="F156" s="19" t="inlineStr">
-        <is>
-          <t>61 में से 35 घटाइए।</t>
-        </is>
-      </c>
-      <c r="G156" s="18" t="inlineStr">
-        <is>
-          <t>page instruction</t>
-        </is>
-      </c>
-      <c r="H156" s="18" t="inlineStr">
-        <is>
-          <t>as the page opens (the speaker replays it)</t>
-        </is>
-      </c>
-      <c r="I156" s="18" t="inlineStr"/>
-      <c r="J156" s="16" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="K156" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="12" t="n">
-        <v>153</v>
-      </c>
-      <c r="B157" s="13" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C157" s="14" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D157" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E157" s="13" t="inlineStr">
-        <is>
-          <t>vo_p2_build</t>
-        </is>
-      </c>
-      <c r="F157" s="15" t="inlineStr">
-        <is>
-          <t>सबसे पहले ब्लॉक्स से 61 बनाइए।</t>
-        </is>
-      </c>
-      <c r="G157" s="14" t="inlineStr">
-        <is>
-          <t>build instruction</t>
-        </is>
-      </c>
-      <c r="H157" s="14" t="inlineStr">
-        <is>
-          <t>after the instruction; the + box comes in, the rod + pulses on its «… दहाई» (or the number), the cube + on «… इकाई»</t>
-        </is>
-      </c>
-      <c r="I157" s="14" t="inlineStr"/>
-      <c r="J157" s="12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K157" s="13" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="16" t="n">
-        <v>154</v>
-      </c>
-      <c r="B158" s="17" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C158" s="18" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D158" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E158" s="17" t="inlineStr">
-        <is>
-          <t>vo_idle_build_t</t>
-        </is>
-      </c>
-      <c r="F158" s="19" t="inlineStr">
-        <is>
-          <t>अब दहाई बनाइए।</t>
-        </is>
-      </c>
-      <c r="G158" s="18" t="inlineStr">
-        <is>
-          <t>inactivity reminder - building</t>
-        </is>
-      </c>
-      <c r="H158" s="18" t="inlineStr">
-        <is>
-          <t>after 7s with no tap at the build step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I158" s="18" t="inlineStr">
-        <is>
-          <t>Page 4, Page 5, Page 6, Page 7, Page 8</t>
-        </is>
-      </c>
-      <c r="J158" s="16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="K158" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="12" t="n">
-        <v>155</v>
-      </c>
-      <c r="B159" s="13" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C159" s="14" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D159" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E159" s="13" t="inlineStr">
-        <is>
-          <t>vo_idle_build_o</t>
-        </is>
-      </c>
-      <c r="F159" s="15" t="inlineStr">
-        <is>
-          <t>अब इकाई बनाइए।</t>
-        </is>
-      </c>
-      <c r="G159" s="14" t="inlineStr">
-        <is>
-          <t>inactivity reminder - building</t>
-        </is>
-      </c>
-      <c r="H159" s="14" t="inlineStr">
-        <is>
-          <t>after 7s with no tap at the build step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I159" s="14" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 7, Page 8</t>
-        </is>
-      </c>
-      <c r="J159" s="12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="K159" s="13" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="16" t="n">
-        <v>156</v>
-      </c>
-      <c r="B160" s="17" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C160" s="18" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D160" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E160" s="17" t="inlineStr">
-        <is>
-          <t>vo_p2_sub</t>
-        </is>
-      </c>
-      <c r="F160" s="19" t="inlineStr">
-        <is>
-          <t>और अब इसमें से 35 घटाते हैं।</t>
-        </is>
-      </c>
-      <c r="G160" s="18" t="inlineStr">
-        <is>
-          <t>what is taken away</t>
-        </is>
-      </c>
-      <c r="H160" s="18" t="inlineStr">
-        <is>
-          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
-        </is>
-      </c>
-      <c r="I160" s="18" t="inlineStr"/>
-      <c r="J160" s="16" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="K160" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="12" t="n">
-        <v>157</v>
-      </c>
-      <c r="B161" s="13" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C161" s="14" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D161" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E161" s="13" t="inlineStr">
-        <is>
-          <t>vo_idle_open</t>
-        </is>
-      </c>
-      <c r="F161" s="15" t="inlineStr">
-        <is>
-          <t>अब 1 दहाई को इकाई में लाइए।</t>
-        </is>
-      </c>
-      <c r="G161" s="14" t="inlineStr">
-        <is>
-          <t>inactivity reminder - open a ten</t>
-        </is>
-      </c>
-      <c r="H161" s="14" t="inlineStr">
-        <is>
-          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
-        </is>
-      </c>
-      <c r="I161" s="14" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 7, Page 8</t>
-        </is>
-      </c>
-      <c r="J161" s="12" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="K161" s="13" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="16" t="n">
-        <v>158</v>
-      </c>
-      <c r="B162" s="17" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C162" s="18" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D162" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="E162" s="17" t="inlineStr">
-        <is>
-          <t>vo_p2_rm_ones</t>
-        </is>
-      </c>
-      <c r="F162" s="19" t="inlineStr">
-        <is>
-          <t>इकाई हटाइए।</t>
-        </is>
-      </c>
-      <c r="G162" s="18" t="inlineStr">
-        <is>
-          <t>take-away step - the ones</t>
-        </is>
-      </c>
-      <c r="H162" s="18" t="inlineStr">
-        <is>
-          <t>after the ten is opened; the ones column beats on «इकाई»</t>
-        </is>
-      </c>
-      <c r="I162" s="18" t="inlineStr"/>
-      <c r="J162" s="16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="K162" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="12" t="n">
-        <v>159</v>
-      </c>
-      <c r="B163" s="13" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C163" s="14" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D163" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="E163" s="13" t="inlineStr">
-        <is>
-          <t>vo_p2_rm_tens</t>
-        </is>
-      </c>
-      <c r="F163" s="15" t="inlineStr">
-        <is>
-          <t>अब दहाइयाँ हटाइए।</t>
-        </is>
-      </c>
-      <c r="G163" s="14" t="inlineStr">
-        <is>
-          <t>take-away step - the tens</t>
-        </is>
-      </c>
-      <c r="H163" s="14" t="inlineStr">
-        <is>
-          <t>when the ones are done; the tens column beats</t>
-        </is>
-      </c>
-      <c r="I163" s="14" t="inlineStr"/>
-      <c r="J163" s="12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="K163" s="13" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="16" t="n">
-        <v>160</v>
-      </c>
-      <c r="B164" s="17" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C164" s="18" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D164" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="E164" s="17" t="inlineStr">
-        <is>
-          <t>vo_idle_rm_o</t>
-        </is>
-      </c>
-      <c r="F164" s="19" t="inlineStr">
-        <is>
-          <t>अब इकाई हटाइए।</t>
-        </is>
-      </c>
-      <c r="G164" s="18" t="inlineStr">
-        <is>
-          <t>inactivity reminder - taking away</t>
-        </is>
-      </c>
-      <c r="H164" s="18" t="inlineStr">
-        <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I164" s="18" t="inlineStr">
-        <is>
-          <t>Page 4, Page 5, Page 6, Page 7, Page 8</t>
-        </is>
-      </c>
-      <c r="J164" s="16" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="K164" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="12" t="n">
-        <v>161</v>
-      </c>
-      <c r="B165" s="13" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C165" s="14" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D165" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E165" s="13" t="inlineStr">
-        <is>
-          <t>vo_idle_rm_t</t>
-        </is>
-      </c>
-      <c r="F165" s="15" t="inlineStr">
-        <is>
-          <t>अब दहाई हटाइए।</t>
-        </is>
-      </c>
-      <c r="G165" s="14" t="inlineStr">
-        <is>
-          <t>inactivity reminder - taking away</t>
-        </is>
-      </c>
-      <c r="H165" s="14" t="inlineStr">
-        <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I165" s="14" t="inlineStr">
-        <is>
-          <t>Page 4, Page 5, Page 6, Page 7, Page 8</t>
-        </is>
-      </c>
-      <c r="J165" s="12" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="K165" s="13" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="16" t="n">
-        <v>162</v>
-      </c>
-      <c r="B166" s="17" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C166" s="18" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D166" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="E166" s="17" t="inlineStr">
-        <is>
-          <t>vo_rm_tens_more</t>
-        </is>
-      </c>
-      <c r="F166" s="19" t="inlineStr">
-        <is>
-          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
-        </is>
-      </c>
-      <c r="G166" s="18" t="inlineStr">
-        <is>
-          <t>take-away mistake - 1st time</t>
-        </is>
-      </c>
-      <c r="H166" s="18" t="inlineStr">
-        <is>
-          <t>a ten too many taken: the tens go back, this line</t>
-        </is>
-      </c>
-      <c r="I166" s="18" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 7, Page 8</t>
-        </is>
-      </c>
-      <c r="J166" s="16" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="K166" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="12" t="n">
-        <v>163</v>
-      </c>
-      <c r="B167" s="13" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C167" s="14" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D167" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="E167" s="13" t="inlineStr">
-        <is>
-          <t>vo_rm_guide</t>
-        </is>
-      </c>
-      <c r="F167" s="15" t="inlineStr">
-        <is>
-          <t>इनमें से इतने हटाइए।</t>
-        </is>
-      </c>
-      <c r="G167" s="14" t="inlineStr">
-        <is>
-          <t>take-away mistake - 2nd time</t>
-        </is>
-      </c>
-      <c r="H167" s="14" t="inlineStr">
-        <is>
-          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
-        </is>
-      </c>
-      <c r="I167" s="14" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 7, Page 8</t>
-        </is>
-      </c>
-      <c r="J167" s="12" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="K167" s="13" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="16" t="n">
-        <v>164</v>
-      </c>
-      <c r="B168" s="17" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C168" s="18" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D168" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="E168" s="17" t="inlineStr">
-        <is>
-          <t>vo_p1_ask</t>
-        </is>
-      </c>
-      <c r="F168" s="19" t="inlineStr">
-        <is>
-          <t>अब कितने बचे? नीचे डिब्बे पर टैप करके सही संख्या लिखिए।</t>
-        </is>
-      </c>
-      <c r="G168" s="18" t="inlineStr">
-        <is>
-          <t>the answer question</t>
-        </is>
-      </c>
-      <c r="H168" s="18" t="inlineStr">
-        <is>
-          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
-        </is>
-      </c>
-      <c r="I168" s="18" t="inlineStr">
-        <is>
-          <t>Page 8</t>
-        </is>
-      </c>
-      <c r="J168" s="16" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="K168" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="12" t="n">
-        <v>165</v>
-      </c>
-      <c r="B169" s="13" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C169" s="14" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D169" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="E169" s="13" t="inlineStr">
-        <is>
-          <t>vo_h_recount</t>
-        </is>
-      </c>
-      <c r="F169" s="15" t="inlineStr">
-        <is>
-          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
-        </is>
-      </c>
-      <c r="G169" s="14" t="inlineStr">
-        <is>
-          <t>Hint 1 (1st wrong answer)</t>
-        </is>
-      </c>
-      <c r="H169" s="14" t="inlineStr">
-        <is>
-          <t>the columns beat on «दहाई» / «इकाई»</t>
-        </is>
-      </c>
-      <c r="I169" s="14" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 7, Page 8</t>
-        </is>
-      </c>
-      <c r="J169" s="12" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="K169" s="13" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="16" t="n">
-        <v>166</v>
-      </c>
-      <c r="B170" s="17" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C170" s="18" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D170" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="E170" s="17" t="inlineStr">
-        <is>
-          <t>vo_p2_h2</t>
-        </is>
-      </c>
-      <c r="F170" s="19" t="inlineStr">
-        <is>
-          <t>61 में से 35 घटाने पर, 2 दहाई और 6 इकाई बचती हैं।</t>
-        </is>
-      </c>
-      <c r="G170" s="18" t="inlineStr">
-        <is>
-          <t>Hint 2 (2nd wrong answer)</t>
-        </is>
-      </c>
-      <c r="H170" s="18" t="inlineStr">
-        <is>
-          <t>the numbers light; the tens and ones left beat on their words</t>
-        </is>
-      </c>
-      <c r="I170" s="18" t="inlineStr"/>
-      <c r="J170" s="16" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="K170" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="12" t="n">
-        <v>167</v>
-      </c>
-      <c r="B171" s="13" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C171" s="14" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D171" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="E171" s="13" t="inlineStr">
-        <is>
-          <t>vo_p2_reveal</t>
-        </is>
-      </c>
-      <c r="F171" s="15" t="inlineStr">
-        <is>
-          <t>61 में से 35 घटाने पर 26 बचता है। तो सही संख्या यह है।</t>
-        </is>
-      </c>
-      <c r="G171" s="14" t="inlineStr">
-        <is>
-          <t>Hint 3 (3rd wrong answer)</t>
-        </is>
-      </c>
-      <c r="H171" s="14" t="inlineStr">
-        <is>
-          <t>the right card / the right keys lit (one key at a time), the others off</t>
-        </is>
-      </c>
-      <c r="I171" s="14" t="inlineStr"/>
-      <c r="J171" s="12" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="K171" s="13" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="16" t="n">
-        <v>168</v>
-      </c>
-      <c r="B172" s="17" t="inlineStr">
-        <is>
-          <t>Page 9</t>
-        </is>
-      </c>
-      <c r="C172" s="18" t="inlineStr">
-        <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
-        </is>
-      </c>
-      <c r="D172" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="E172" s="17" t="inlineStr">
-        <is>
-          <t>vo_p2_correct</t>
-        </is>
-      </c>
-      <c r="F172" s="19" t="inlineStr">
-        <is>
-          <t>शाबाश! 61 में से 35 घटाने पर हमें मिला 26।</t>
-        </is>
-      </c>
-      <c r="G172" s="18" t="inlineStr">
-        <is>
-          <t>correct answer</t>
-        </is>
-      </c>
-      <c r="H172" s="18" t="inlineStr">
-        <is>
-          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
-        </is>
-      </c>
-      <c r="I172" s="18" t="inlineStr"/>
-      <c r="J172" s="16" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="K172" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="12" t="n">
-        <v>169</v>
-      </c>
-      <c r="B173" s="13" t="inlineStr">
-        <is>
-          <t>Page 10</t>
-        </is>
-      </c>
-      <c r="C173" s="14" t="inlineStr">
-        <is>
-          <t>P3 · MENTAL_SUB  (84 − 46)</t>
-        </is>
-      </c>
-      <c r="D173" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E173" s="13" t="inlineStr">
-        <is>
-          <t>vo_p3_prompt</t>
-        </is>
-      </c>
-      <c r="F173" s="15" t="inlineStr">
-        <is>
-          <t>84 में से 46 घटाइए और सही संख्या चुनिए।</t>
-        </is>
-      </c>
-      <c r="G173" s="14" t="inlineStr">
-        <is>
-          <t>page instruction</t>
-        </is>
-      </c>
-      <c r="H173" s="14" t="inlineStr">
-        <is>
-          <t>as the page opens (the speaker replays it)</t>
-        </is>
-      </c>
-      <c r="I173" s="14" t="inlineStr"/>
-      <c r="J173" s="12" t="n">
-        <v>4.51</v>
-      </c>
-      <c r="K173" s="13" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="16" t="n">
-        <v>170</v>
-      </c>
-      <c r="B174" s="17" t="inlineStr">
-        <is>
-          <t>Page 10</t>
-        </is>
-      </c>
-      <c r="C174" s="18" t="inlineStr">
-        <is>
-          <t>P3 · MENTAL_SUB  (84 − 46)</t>
-        </is>
-      </c>
-      <c r="D174" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E174" s="17" t="inlineStr">
-        <is>
-          <t>vo_h_order</t>
-        </is>
-      </c>
-      <c r="F174" s="19" t="inlineStr">
-        <is>
-          <t>संख्याओं में से पहले इकाई घटाइए, फिर दहाई घटाइए।</t>
-        </is>
-      </c>
-      <c r="G174" s="18" t="inlineStr">
-        <is>
-          <t>Hint 1 (1st wrong answer)</t>
-        </is>
-      </c>
-      <c r="H174" s="18" t="inlineStr">
-        <is>
-          <t>the ones digits light on «इकाई», the tens digits on «दहाई»</t>
-        </is>
-      </c>
-      <c r="I174" s="18" t="inlineStr">
-        <is>
-          <t>Page 11</t>
-        </is>
-      </c>
-      <c r="J174" s="16" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="K174" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" s="12" t="n">
-        <v>171</v>
-      </c>
-      <c r="B175" s="13" t="inlineStr">
-        <is>
-          <t>Page 10</t>
-        </is>
-      </c>
-      <c r="C175" s="14" t="inlineStr">
-        <is>
-          <t>P3 · MENTAL_SUB  (84 − 46)</t>
-        </is>
-      </c>
-      <c r="D175" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E175" s="13" t="inlineStr">
-        <is>
-          <t>vo_p3_h2</t>
-        </is>
-      </c>
-      <c r="F175" s="15" t="inlineStr">
-        <is>
-          <t>84 में से 46 घटाने पर, 3 दहाई और 8 इकाई बचती हैं।</t>
-        </is>
-      </c>
-      <c r="G175" s="14" t="inlineStr">
-        <is>
-          <t>Hint 2 (2nd wrong answer)</t>
-        </is>
-      </c>
-      <c r="H175" s="14" t="inlineStr">
-        <is>
-          <t>the table comes in with the first number's blocks; the second number is taken away as it is said</t>
-        </is>
-      </c>
-      <c r="I175" s="14" t="inlineStr"/>
-      <c r="J175" s="12" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="K175" s="13" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="16" t="n">
-        <v>172</v>
-      </c>
-      <c r="B176" s="17" t="inlineStr">
-        <is>
-          <t>Page 10</t>
-        </is>
-      </c>
-      <c r="C176" s="18" t="inlineStr">
-        <is>
-          <t>P3 · MENTAL_SUB  (84 − 46)</t>
-        </is>
-      </c>
-      <c r="D176" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="E176" s="17" t="inlineStr">
-        <is>
-          <t>vo_p3_reveal</t>
-        </is>
-      </c>
-      <c r="F176" s="19" t="inlineStr">
-        <is>
-          <t>84 में से 46 घटाने पर 38 बचता है। तो सही संख्या यह है।</t>
-        </is>
-      </c>
-      <c r="G176" s="18" t="inlineStr">
-        <is>
-          <t>Hint 3 (3rd wrong answer)</t>
-        </is>
-      </c>
-      <c r="H176" s="18" t="inlineStr">
-        <is>
-          <t>the right card / the right keys lit (one key at a time), the others off</t>
-        </is>
-      </c>
-      <c r="I176" s="18" t="inlineStr"/>
-      <c r="J176" s="16" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="K176" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="12" t="n">
-        <v>173</v>
-      </c>
-      <c r="B177" s="13" t="inlineStr">
-        <is>
-          <t>Page 10</t>
-        </is>
-      </c>
-      <c r="C177" s="14" t="inlineStr">
-        <is>
-          <t>P3 · MENTAL_SUB  (84 − 46)</t>
-        </is>
-      </c>
-      <c r="D177" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="E177" s="13" t="inlineStr">
-        <is>
-          <t>vo_p3_correct</t>
-        </is>
-      </c>
-      <c r="F177" s="15" t="inlineStr">
-        <is>
-          <t>शाबाश! आपने सही संख्या चुन ली। 84 घटा 46 बराबर 38।</t>
-        </is>
-      </c>
-      <c r="G177" s="14" t="inlineStr">
-        <is>
-          <t>correct answer</t>
-        </is>
-      </c>
-      <c r="H177" s="14" t="inlineStr">
-        <is>
-          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
-        </is>
-      </c>
-      <c r="I177" s="14" t="inlineStr"/>
-      <c r="J177" s="12" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="K177" s="13" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="16" t="n">
-        <v>174</v>
-      </c>
-      <c r="B178" s="17" t="inlineStr">
-        <is>
-          <t>Page 11</t>
-        </is>
-      </c>
-      <c r="C178" s="18" t="inlineStr">
-        <is>
-          <t>P4 · MENTAL_SUB  (91 − 14)</t>
-        </is>
-      </c>
-      <c r="D178" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E178" s="17" t="inlineStr">
-        <is>
-          <t>vo_p4_prompt</t>
-        </is>
-      </c>
-      <c r="F178" s="19" t="inlineStr">
-        <is>
-          <t>91 में से 14 घटाइए और सही संख्या चुनिए।</t>
-        </is>
-      </c>
-      <c r="G178" s="18" t="inlineStr">
-        <is>
-          <t>page instruction</t>
-        </is>
-      </c>
-      <c r="H178" s="18" t="inlineStr">
-        <is>
-          <t>as the page opens (the speaker replays it)</t>
-        </is>
-      </c>
-      <c r="I178" s="18" t="inlineStr"/>
-      <c r="J178" s="16" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="K178" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="12" t="n">
-        <v>175</v>
-      </c>
-      <c r="B179" s="13" t="inlineStr">
-        <is>
-          <t>Page 11</t>
-        </is>
-      </c>
-      <c r="C179" s="14" t="inlineStr">
-        <is>
-          <t>P4 · MENTAL_SUB  (91 − 14)</t>
-        </is>
-      </c>
-      <c r="D179" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E179" s="13" t="inlineStr">
-        <is>
-          <t>vo_h_order</t>
-        </is>
-      </c>
-      <c r="F179" s="15" t="inlineStr">
-        <is>
-          <t>संख्याओं में से पहले इकाई घटाइए, फिर दहाई घटाइए।</t>
-        </is>
-      </c>
-      <c r="G179" s="14" t="inlineStr">
-        <is>
-          <t>Hint 1 (1st wrong answer)</t>
-        </is>
-      </c>
-      <c r="H179" s="14" t="inlineStr">
-        <is>
-          <t>the ones digits light on «इकाई», the tens digits on «दहाई»</t>
-        </is>
-      </c>
-      <c r="I179" s="14" t="inlineStr">
-        <is>
-          <t>Page 10</t>
-        </is>
-      </c>
-      <c r="J179" s="12" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="K179" s="13" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" s="16" t="n">
-        <v>176</v>
-      </c>
-      <c r="B180" s="17" t="inlineStr">
-        <is>
-          <t>Page 11</t>
-        </is>
-      </c>
-      <c r="C180" s="18" t="inlineStr">
-        <is>
-          <t>P4 · MENTAL_SUB  (91 − 14)</t>
-        </is>
-      </c>
-      <c r="D180" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E180" s="17" t="inlineStr">
-        <is>
-          <t>vo_p4_h2</t>
-        </is>
-      </c>
-      <c r="F180" s="19" t="inlineStr">
-        <is>
-          <t>91 में से 14 घटाने पर, 7 दहाई और 7 इकाई बचती हैं।</t>
-        </is>
-      </c>
-      <c r="G180" s="18" t="inlineStr">
-        <is>
-          <t>Hint 2 (2nd wrong answer)</t>
-        </is>
-      </c>
-      <c r="H180" s="18" t="inlineStr">
-        <is>
-          <t>the table comes in with the first number's blocks; the second number is taken away as it is said</t>
-        </is>
-      </c>
-      <c r="I180" s="18" t="inlineStr"/>
-      <c r="J180" s="16" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="K180" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="12" t="n">
-        <v>177</v>
-      </c>
-      <c r="B181" s="13" t="inlineStr">
-        <is>
-          <t>Page 11</t>
-        </is>
-      </c>
-      <c r="C181" s="14" t="inlineStr">
-        <is>
-          <t>P4 · MENTAL_SUB  (91 − 14)</t>
-        </is>
-      </c>
-      <c r="D181" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E181" s="13" t="inlineStr">
-        <is>
-          <t>vo_p4_reveal</t>
-        </is>
-      </c>
-      <c r="F181" s="15" t="inlineStr">
-        <is>
-          <t>91 में से 14 घटाने पर 77 बचता है। तो सही संख्या यह है।</t>
-        </is>
-      </c>
-      <c r="G181" s="14" t="inlineStr">
-        <is>
-          <t>Hint 3 (3rd wrong answer)</t>
-        </is>
-      </c>
-      <c r="H181" s="14" t="inlineStr">
-        <is>
-          <t>the right card / the right keys lit (one key at a time), the others off</t>
-        </is>
-      </c>
-      <c r="I181" s="14" t="inlineStr"/>
-      <c r="J181" s="12" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="K181" s="13" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="16" t="n">
-        <v>178</v>
-      </c>
-      <c r="B182" s="17" t="inlineStr">
-        <is>
-          <t>Page 11</t>
-        </is>
-      </c>
-      <c r="C182" s="18" t="inlineStr">
-        <is>
-          <t>P4 · MENTAL_SUB  (91 − 14)</t>
-        </is>
-      </c>
-      <c r="D182" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E182" s="17" t="inlineStr">
-        <is>
-          <t>vo_p4_correct</t>
-        </is>
-      </c>
-      <c r="F182" s="19" t="inlineStr">
-        <is>
-          <t>शाबाश! आपने सही संख्या चुन ली। 91 घटा 14 बराबर 77।</t>
-        </is>
-      </c>
-      <c r="G182" s="18" t="inlineStr">
-        <is>
-          <t>correct answer</t>
-        </is>
-      </c>
-      <c r="H182" s="18" t="inlineStr">
-        <is>
-          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
-        </is>
-      </c>
-      <c r="I182" s="18" t="inlineStr"/>
-      <c r="J182" s="16" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="K182" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="20" t="n">
-        <v>179</v>
-      </c>
-      <c r="B183" s="21" t="inlineStr">
-        <is>
-          <t>Celebration</t>
-        </is>
-      </c>
-      <c r="C183" s="22" t="inlineStr">
-        <is>
-          <t>CEL · CELEBRATION</t>
-        </is>
-      </c>
-      <c r="D183" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E183" s="21" t="inlineStr">
+      <c r="E155" s="21" t="inlineStr">
         <is>
           <t>vo_cel</t>
         </is>
       </c>
-      <c r="F183" s="23" t="inlineStr">
+      <c r="F155" s="23" t="inlineStr">
         <is>
           <t>शाबाश! आपने दहाई खोलकर घटाना सीख लिया!</t>
         </is>
       </c>
-      <c r="G183" s="22" t="inlineStr">
+      <c r="G155" s="22" t="inlineStr">
         <is>
           <t>celebration</t>
         </is>
       </c>
-      <c r="H183" s="22" t="inlineStr">
+      <c r="H155" s="22" t="inlineStr">
         <is>
           <t>the celebration screen: Swiftee jumps on «शाबाश», then says the line lip-synced</t>
         </is>
       </c>
-      <c r="I183" s="22" t="inlineStr"/>
-      <c r="J183" s="20" t="n">
+      <c r="I155" s="22" t="inlineStr"/>
+      <c r="J155" s="20" t="n">
         <v>3.93</v>
       </c>
-      <c r="K183" s="21" t="inlineStr">
+      <c r="K155" s="21" t="inlineStr">
         <is>
           <t>TTS (Gemini, Kore)</t>
         </is>
@@ -9412,7 +7996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G120"/>
+  <dimension ref="A1:G116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9434,7 +8018,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>116 recordings. Record each once; the file name is the Audio ID + .ogg, in assets/voiceover/.</t>
+          <t>112 recordings. Record each once; the file name is the Audio ID + .ogg, in assets/voiceover/.</t>
         </is>
       </c>
     </row>
@@ -10024,7 +8608,7 @@
       </c>
       <c r="E21" s="27" t="inlineStr">
         <is>
-          <t>Page 2, Page 4, Page 5, Page 6, Page 7</t>
+          <t>Page 2, Page 4</t>
         </is>
       </c>
       <c r="F21" s="24" t="n">
@@ -10057,7 +8641,7 @@
       </c>
       <c r="E22" s="27" t="inlineStr">
         <is>
-          <t>Page 2, Page 4, Page 5, Page 6, Page 7</t>
+          <t>Page 2, Page 4</t>
         </is>
       </c>
       <c r="F22" s="24" t="n">
@@ -10090,7 +8674,7 @@
       </c>
       <c r="E23" s="27" t="inlineStr">
         <is>
-          <t>Page 2, Page 4, Page 5, Page 6, Page 7</t>
+          <t>Page 2, Page 4</t>
         </is>
       </c>
       <c r="F23" s="24" t="n">
@@ -10123,7 +8707,7 @@
       </c>
       <c r="E24" s="27" t="inlineStr">
         <is>
-          <t>Page 2, Page 4, Page 5, Page 6, Page 7</t>
+          <t>Page 2, Page 4</t>
         </is>
       </c>
       <c r="F24" s="24" t="n">
@@ -10156,7 +8740,7 @@
       </c>
       <c r="E25" s="27" t="inlineStr">
         <is>
-          <t>Page 2, Page 4, Page 5, Page 7</t>
+          <t>Page 2, Page 4</t>
         </is>
       </c>
       <c r="F25" s="24" t="n">
@@ -10189,7 +8773,7 @@
       </c>
       <c r="E26" s="27" t="inlineStr">
         <is>
-          <t>Page 2, Page 4, Page 5, Page 7</t>
+          <t>Page 2, Page 4</t>
         </is>
       </c>
       <c r="F26" s="24" t="n">
@@ -10471,17 +9055,17 @@
       </c>
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>vo_t3s_b_pari</t>
+          <t>vo_t3s_b_myra</t>
         </is>
       </c>
       <c r="C35" s="25" t="inlineStr">
         <is>
-          <t>vo_t3s_b_pari.ogg</t>
+          <t>vo_t3s_b_myra.ogg</t>
         </is>
       </c>
       <c r="D35" s="26" t="inlineStr">
         <is>
-          <t>उनमें से 17 परी को दे दिए।</t>
+          <t>उनमें से 17 मायरा को दे दिए।</t>
         </is>
       </c>
       <c r="E35" s="27" t="inlineStr">
@@ -10490,7 +9074,7 @@
         </is>
       </c>
       <c r="F35" s="24" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
@@ -10684,7 +9268,7 @@
       </c>
       <c r="E41" s="27" t="inlineStr">
         <is>
-          <t>Page 4, Page 5, Page 6, Page 7, Page 8, Page 9</t>
+          <t>Page 4, Page 5, Page 6</t>
         </is>
       </c>
       <c r="F41" s="24" t="n">
@@ -10849,7 +9433,7 @@
       </c>
       <c r="E46" s="27" t="inlineStr">
         <is>
-          <t>Page 4, Page 5, Page 7</t>
+          <t>Page 4</t>
         </is>
       </c>
       <c r="F46" s="24" t="n">
@@ -11278,7 +9862,7 @@
       </c>
       <c r="E59" s="27" t="inlineStr">
         <is>
-          <t>Page 5, Page 6, Page 7, Page 8, Page 9</t>
+          <t>Page 5, Page 6</t>
         </is>
       </c>
       <c r="F59" s="24" t="n">
@@ -12121,17 +10705,17 @@
       </c>
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_build</t>
+          <t>vo_g3_sub</t>
         </is>
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_build.ogg</t>
+          <t>vo_g3_sub.ogg</t>
         </is>
       </c>
       <c r="D85" s="26" t="inlineStr">
         <is>
-          <t>सबसे पहले ब्लॉक्स से 46 बनाइए।</t>
+          <t>और अब इसमें से 28 घटाइए।</t>
         </is>
       </c>
       <c r="E85" s="27" t="inlineStr">
@@ -12140,7 +10724,7 @@
         </is>
       </c>
       <c r="F85" s="24" t="n">
-        <v>3.92</v>
+        <v>2.67</v>
       </c>
       <c r="G85" s="25" t="inlineStr">
         <is>
@@ -12154,17 +10738,17 @@
       </c>
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_sub</t>
+          <t>vo_g3_rm_ones</t>
         </is>
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_sub.ogg</t>
+          <t>vo_g3_rm_ones.ogg</t>
         </is>
       </c>
       <c r="D86" s="26" t="inlineStr">
         <is>
-          <t>और अब इसमें से 28 घटाइए।</t>
+          <t>इसमें से 8 इकाई को हटाइए।</t>
         </is>
       </c>
       <c r="E86" s="27" t="inlineStr">
@@ -12173,7 +10757,7 @@
         </is>
       </c>
       <c r="F86" s="24" t="n">
-        <v>2.67</v>
+        <v>3.03</v>
       </c>
       <c r="G86" s="25" t="inlineStr">
         <is>
@@ -12187,17 +10771,17 @@
       </c>
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_rm_ones</t>
+          <t>vo_g3_rm_tens</t>
         </is>
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_rm_ones.ogg</t>
+          <t>vo_g3_rm_tens.ogg</t>
         </is>
       </c>
       <c r="D87" s="26" t="inlineStr">
         <is>
-          <t>इसमें से 8 इकाई को हटाइए।</t>
+          <t>अब दहाइयाँ हटाइए।</t>
         </is>
       </c>
       <c r="E87" s="27" t="inlineStr">
@@ -12206,7 +10790,7 @@
         </is>
       </c>
       <c r="F87" s="24" t="n">
-        <v>3.03</v>
+        <v>2.47</v>
       </c>
       <c r="G87" s="25" t="inlineStr">
         <is>
@@ -12220,17 +10804,17 @@
       </c>
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>vo_num_8</t>
+          <t>vo_g3_h2</t>
         </is>
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>vo_num_8.ogg</t>
+          <t>vo_g3_h2.ogg</t>
         </is>
       </c>
       <c r="D88" s="26" t="inlineStr">
         <is>
-          <t>आठ।</t>
+          <t>46 में से 28 घटाने पर, 1 दहाई और 8 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="E88" s="27" t="inlineStr">
@@ -12239,7 +10823,7 @@
         </is>
       </c>
       <c r="F88" s="24" t="n">
-        <v>1.08</v>
+        <v>5.55</v>
       </c>
       <c r="G88" s="25" t="inlineStr">
         <is>
@@ -12253,17 +10837,17 @@
       </c>
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_rm_tens</t>
+          <t>vo_g3_reveal</t>
         </is>
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_rm_tens.ogg</t>
+          <t>vo_g3_reveal.ogg</t>
         </is>
       </c>
       <c r="D89" s="26" t="inlineStr">
         <is>
-          <t>अब दहाइयाँ हटाइए।</t>
+          <t>46 में से 28 घटाने पर 18 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="E89" s="27" t="inlineStr">
@@ -12272,7 +10856,7 @@
         </is>
       </c>
       <c r="F89" s="24" t="n">
-        <v>2.47</v>
+        <v>5.75</v>
       </c>
       <c r="G89" s="25" t="inlineStr">
         <is>
@@ -12286,17 +10870,17 @@
       </c>
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_h2</t>
+          <t>vo_g3_correct</t>
         </is>
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_h2.ogg</t>
+          <t>vo_g3_correct.ogg</t>
         </is>
       </c>
       <c r="D90" s="26" t="inlineStr">
         <is>
-          <t>46 में से 28 घटाने पर, 1 दहाई और 8 इकाई बचती हैं।</t>
+          <t>शाबाश! 46 घटा 28 बराबर 18।</t>
         </is>
       </c>
       <c r="E90" s="27" t="inlineStr">
@@ -12305,7 +10889,7 @@
         </is>
       </c>
       <c r="F90" s="24" t="n">
-        <v>5.55</v>
+        <v>4.99</v>
       </c>
       <c r="G90" s="25" t="inlineStr">
         <is>
@@ -12319,30 +10903,30 @@
       </c>
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_reveal</t>
+          <t>vo_pt_practice</t>
         </is>
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_reveal.ogg</t>
+          <t>vo_pt_practice.ogg</t>
         </is>
       </c>
       <c r="D91" s="26" t="inlineStr">
         <is>
-          <t>46 में से 28 घटाने पर 18 बचता है। तो सही संख्या यह है।</t>
+          <t>वाह! अब आपकी बारी।</t>
         </is>
       </c>
       <c r="E91" s="27" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Transition 3</t>
         </is>
       </c>
       <c r="F91" s="24" t="n">
-        <v>5.75</v>
+        <v>1.87</v>
       </c>
       <c r="G91" s="25" t="inlineStr">
         <is>
-          <t>TTS (Gemini, Kore)</t>
+          <t>Copied (HI02H11, recorded voice)</t>
         </is>
       </c>
     </row>
@@ -12352,26 +10936,26 @@
       </c>
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_correct</t>
+          <t>vo_p1_prompt</t>
         </is>
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_correct.ogg</t>
+          <t>vo_p1_prompt.ogg</t>
         </is>
       </c>
       <c r="D92" s="26" t="inlineStr">
         <is>
-          <t>शाबाश! 46 घटा 28 बराबर 18।</t>
+          <t>74 में से 58 घटाइए।</t>
         </is>
       </c>
       <c r="E92" s="27" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="F92" s="24" t="n">
-        <v>4.99</v>
+        <v>2.5</v>
       </c>
       <c r="G92" s="25" t="inlineStr">
         <is>
@@ -12385,30 +10969,30 @@
       </c>
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>vo_pt_practice</t>
+          <t>vo_p1_sub</t>
         </is>
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>vo_pt_practice.ogg</t>
+          <t>vo_p1_sub.ogg</t>
         </is>
       </c>
       <c r="D93" s="26" t="inlineStr">
         <is>
-          <t>वाह! अब आपकी बारी।</t>
+          <t>और अब इसमें से 58 घटाते हैं।</t>
         </is>
       </c>
       <c r="E93" s="27" t="inlineStr">
         <is>
-          <t>Transition 3</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="F93" s="24" t="n">
-        <v>1.87</v>
+        <v>3.69</v>
       </c>
       <c r="G93" s="25" t="inlineStr">
         <is>
-          <t>Copied (HI02H11, recorded voice)</t>
+          <t>TTS (Gemini, Kore)</t>
         </is>
       </c>
     </row>
@@ -12418,17 +11002,17 @@
       </c>
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_prompt</t>
+          <t>vo_p1_rm_ones</t>
         </is>
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_prompt.ogg</t>
+          <t>vo_p1_rm_ones.ogg</t>
         </is>
       </c>
       <c r="D94" s="26" t="inlineStr">
         <is>
-          <t>74 में से 58 घटाइए।</t>
+          <t>14 इकाई में से 8 इकाई हटाइए।</t>
         </is>
       </c>
       <c r="E94" s="27" t="inlineStr">
@@ -12437,7 +11021,7 @@
         </is>
       </c>
       <c r="F94" s="24" t="n">
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="G94" s="25" t="inlineStr">
         <is>
@@ -12451,17 +11035,17 @@
       </c>
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_build</t>
+          <t>vo_p1_rm_tens</t>
         </is>
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_build.ogg</t>
+          <t>vo_p1_rm_tens.ogg</t>
         </is>
       </c>
       <c r="D95" s="26" t="inlineStr">
         <is>
-          <t>सबसे पहले ब्लॉक्स से 74 बनाइए।</t>
+          <t>अब दहाइयाँ घटाइए।</t>
         </is>
       </c>
       <c r="E95" s="27" t="inlineStr">
@@ -12470,7 +11054,7 @@
         </is>
       </c>
       <c r="F95" s="24" t="n">
-        <v>3.45</v>
+        <v>2.63</v>
       </c>
       <c r="G95" s="25" t="inlineStr">
         <is>
@@ -12484,26 +11068,26 @@
       </c>
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_sub</t>
+          <t>vo_p1_ask</t>
         </is>
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_sub.ogg</t>
+          <t>vo_p1_ask.ogg</t>
         </is>
       </c>
       <c r="D96" s="26" t="inlineStr">
         <is>
-          <t>और अब इसमें से 58 घटाते हैं।</t>
+          <t>अब कितने बचे? नीचे डिब्बे पर टैप करके सही संख्या लिखिए।</t>
         </is>
       </c>
       <c r="E96" s="27" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 8, Page 9</t>
         </is>
       </c>
       <c r="F96" s="24" t="n">
-        <v>3.69</v>
+        <v>4.39</v>
       </c>
       <c r="G96" s="25" t="inlineStr">
         <is>
@@ -12517,17 +11101,17 @@
       </c>
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_rm_ones</t>
+          <t>vo_p1_h2</t>
         </is>
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_rm_ones.ogg</t>
+          <t>vo_p1_h2.ogg</t>
         </is>
       </c>
       <c r="D97" s="26" t="inlineStr">
         <is>
-          <t>14 इकाई में से 8 इकाई हटाइए।</t>
+          <t>74 में से 58 घटाने पर, 1 दहाई और 6 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="E97" s="27" t="inlineStr">
@@ -12536,7 +11120,7 @@
         </is>
       </c>
       <c r="F97" s="24" t="n">
-        <v>3.33</v>
+        <v>5.45</v>
       </c>
       <c r="G97" s="25" t="inlineStr">
         <is>
@@ -12550,17 +11134,17 @@
       </c>
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_rm_tens</t>
+          <t>vo_p1_reveal</t>
         </is>
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_rm_tens.ogg</t>
+          <t>vo_p1_reveal.ogg</t>
         </is>
       </c>
       <c r="D98" s="26" t="inlineStr">
         <is>
-          <t>अब दहाइयाँ घटाइए।</t>
+          <t>74 में से 58 घटाने पर 16 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="E98" s="27" t="inlineStr">
@@ -12569,7 +11153,7 @@
         </is>
       </c>
       <c r="F98" s="24" t="n">
-        <v>2.63</v>
+        <v>5.69</v>
       </c>
       <c r="G98" s="25" t="inlineStr">
         <is>
@@ -12583,26 +11167,26 @@
       </c>
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_ask</t>
+          <t>vo_p1_correct</t>
         </is>
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_ask.ogg</t>
+          <t>vo_p1_correct.ogg</t>
         </is>
       </c>
       <c r="D99" s="26" t="inlineStr">
         <is>
-          <t>अब कितने बचे? नीचे डिब्बे पर टैप करके सही संख्या लिखिए।</t>
+          <t>शाबाश! 74 में से 58 घटाने पर हमें मिला 16।</t>
         </is>
       </c>
       <c r="E99" s="27" t="inlineStr">
         <is>
-          <t>Page 8, Page 9</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="F99" s="24" t="n">
-        <v>4.39</v>
+        <v>5.01</v>
       </c>
       <c r="G99" s="25" t="inlineStr">
         <is>
@@ -12616,26 +11200,26 @@
       </c>
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_h2</t>
+          <t>vo_p2_prompt</t>
         </is>
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_h2.ogg</t>
+          <t>vo_p2_prompt.ogg</t>
         </is>
       </c>
       <c r="D100" s="26" t="inlineStr">
         <is>
-          <t>74 में से 58 घटाने पर, 1 दहाई और 6 इकाई बचती हैं।</t>
+          <t>61 में से 35 घटाइए।</t>
         </is>
       </c>
       <c r="E100" s="27" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="F100" s="24" t="n">
-        <v>5.45</v>
+        <v>2.48</v>
       </c>
       <c r="G100" s="25" t="inlineStr">
         <is>
@@ -12649,26 +11233,26 @@
       </c>
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_reveal</t>
+          <t>vo_p2_sub</t>
         </is>
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_reveal.ogg</t>
+          <t>vo_p2_sub.ogg</t>
         </is>
       </c>
       <c r="D101" s="26" t="inlineStr">
         <is>
-          <t>74 में से 58 घटाने पर 16 बचता है। तो सही संख्या यह है।</t>
+          <t>और अब इसमें से 35 घटाते हैं।</t>
         </is>
       </c>
       <c r="E101" s="27" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="F101" s="24" t="n">
-        <v>5.69</v>
+        <v>2.86</v>
       </c>
       <c r="G101" s="25" t="inlineStr">
         <is>
@@ -12682,26 +11266,26 @@
       </c>
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_correct</t>
+          <t>vo_p2_rm_ones</t>
         </is>
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_correct.ogg</t>
+          <t>vo_p2_rm_ones.ogg</t>
         </is>
       </c>
       <c r="D102" s="26" t="inlineStr">
         <is>
-          <t>शाबाश! 74 में से 58 घटाने पर हमें मिला 16।</t>
+          <t>इकाई हटाइए।</t>
         </is>
       </c>
       <c r="E102" s="27" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="F102" s="24" t="n">
-        <v>5.01</v>
+        <v>1.81</v>
       </c>
       <c r="G102" s="25" t="inlineStr">
         <is>
@@ -12715,17 +11299,17 @@
       </c>
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_prompt</t>
+          <t>vo_p2_rm_tens</t>
         </is>
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_prompt.ogg</t>
+          <t>vo_p2_rm_tens.ogg</t>
         </is>
       </c>
       <c r="D103" s="26" t="inlineStr">
         <is>
-          <t>61 में से 35 घटाइए।</t>
+          <t>अब दहाइयाँ हटाइए।</t>
         </is>
       </c>
       <c r="E103" s="27" t="inlineStr">
@@ -12734,7 +11318,7 @@
         </is>
       </c>
       <c r="F103" s="24" t="n">
-        <v>2.48</v>
+        <v>1.95</v>
       </c>
       <c r="G103" s="25" t="inlineStr">
         <is>
@@ -12748,17 +11332,17 @@
       </c>
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_build</t>
+          <t>vo_p2_h2</t>
         </is>
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_build.ogg</t>
+          <t>vo_p2_h2.ogg</t>
         </is>
       </c>
       <c r="D104" s="26" t="inlineStr">
         <is>
-          <t>सबसे पहले ब्लॉक्स से 61 बनाइए।</t>
+          <t>61 में से 35 घटाने पर, 2 दहाई और 6 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="E104" s="27" t="inlineStr">
@@ -12767,7 +11351,7 @@
         </is>
       </c>
       <c r="F104" s="24" t="n">
-        <v>3.3</v>
+        <v>5.81</v>
       </c>
       <c r="G104" s="25" t="inlineStr">
         <is>
@@ -12781,17 +11365,17 @@
       </c>
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_sub</t>
+          <t>vo_p2_reveal</t>
         </is>
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_sub.ogg</t>
+          <t>vo_p2_reveal.ogg</t>
         </is>
       </c>
       <c r="D105" s="26" t="inlineStr">
         <is>
-          <t>और अब इसमें से 35 घटाते हैं।</t>
+          <t>61 में से 35 घटाने पर 26 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="E105" s="27" t="inlineStr">
@@ -12800,7 +11384,7 @@
         </is>
       </c>
       <c r="F105" s="24" t="n">
-        <v>2.86</v>
+        <v>4.64</v>
       </c>
       <c r="G105" s="25" t="inlineStr">
         <is>
@@ -12814,17 +11398,17 @@
       </c>
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_rm_ones</t>
+          <t>vo_p2_correct</t>
         </is>
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_rm_ones.ogg</t>
+          <t>vo_p2_correct.ogg</t>
         </is>
       </c>
       <c r="D106" s="26" t="inlineStr">
         <is>
-          <t>इकाई हटाइए।</t>
+          <t>शाबाश! 61 में से 35 घटाने पर हमें मिला 26।</t>
         </is>
       </c>
       <c r="E106" s="27" t="inlineStr">
@@ -12833,7 +11417,7 @@
         </is>
       </c>
       <c r="F106" s="24" t="n">
-        <v>1.81</v>
+        <v>5.21</v>
       </c>
       <c r="G106" s="25" t="inlineStr">
         <is>
@@ -12847,26 +11431,26 @@
       </c>
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_rm_tens</t>
+          <t>vo_p3_prompt</t>
         </is>
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_rm_tens.ogg</t>
+          <t>vo_p3_prompt.ogg</t>
         </is>
       </c>
       <c r="D107" s="26" t="inlineStr">
         <is>
-          <t>अब दहाइयाँ हटाइए।</t>
+          <t>84 में से 46 घटाइए और सही संख्या चुनिए।</t>
         </is>
       </c>
       <c r="E107" s="27" t="inlineStr">
         <is>
-          <t>Page 9</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="F107" s="24" t="n">
-        <v>1.95</v>
+        <v>4.51</v>
       </c>
       <c r="G107" s="25" t="inlineStr">
         <is>
@@ -12880,26 +11464,26 @@
       </c>
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_h2</t>
+          <t>vo_h_order</t>
         </is>
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_h2.ogg</t>
+          <t>vo_h_order.ogg</t>
         </is>
       </c>
       <c r="D108" s="26" t="inlineStr">
         <is>
-          <t>61 में से 35 घटाने पर, 2 दहाई और 6 इकाई बचती हैं।</t>
+          <t>संख्याओं में से पहले इकाई घटाइए, फिर दहाई घटाइए।</t>
         </is>
       </c>
       <c r="E108" s="27" t="inlineStr">
         <is>
-          <t>Page 9</t>
+          <t>Page 10, Page 11</t>
         </is>
       </c>
       <c r="F108" s="24" t="n">
-        <v>5.81</v>
+        <v>4.45</v>
       </c>
       <c r="G108" s="25" t="inlineStr">
         <is>
@@ -12913,26 +11497,26 @@
       </c>
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_reveal</t>
+          <t>vo_p3_h2</t>
         </is>
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_reveal.ogg</t>
+          <t>vo_p3_h2.ogg</t>
         </is>
       </c>
       <c r="D109" s="26" t="inlineStr">
         <is>
-          <t>61 में से 35 घटाने पर 26 बचता है। तो सही संख्या यह है।</t>
+          <t>84 में से 46 घटाने पर, 3 दहाई और 8 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="E109" s="27" t="inlineStr">
         <is>
-          <t>Page 9</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="F109" s="24" t="n">
-        <v>4.64</v>
+        <v>5.47</v>
       </c>
       <c r="G109" s="25" t="inlineStr">
         <is>
@@ -12946,26 +11530,26 @@
       </c>
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_correct</t>
+          <t>vo_p3_reveal</t>
         </is>
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_correct.ogg</t>
+          <t>vo_p3_reveal.ogg</t>
         </is>
       </c>
       <c r="D110" s="26" t="inlineStr">
         <is>
-          <t>शाबाश! 61 में से 35 घटाने पर हमें मिला 26।</t>
+          <t>84 में से 46 घटाने पर 38 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="E110" s="27" t="inlineStr">
         <is>
-          <t>Page 9</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="F110" s="24" t="n">
-        <v>5.21</v>
+        <v>5.52</v>
       </c>
       <c r="G110" s="25" t="inlineStr">
         <is>
@@ -12979,17 +11563,17 @@
       </c>
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_prompt</t>
+          <t>vo_p3_correct</t>
         </is>
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_prompt.ogg</t>
+          <t>vo_p3_correct.ogg</t>
         </is>
       </c>
       <c r="D111" s="26" t="inlineStr">
         <is>
-          <t>84 में से 46 घटाइए और सही संख्या चुनिए।</t>
+          <t>शाबाश! आपने सही संख्या चुन ली। 84 घटा 46 बराबर 38।</t>
         </is>
       </c>
       <c r="E111" s="27" t="inlineStr">
@@ -12998,7 +11582,7 @@
         </is>
       </c>
       <c r="F111" s="24" t="n">
-        <v>4.51</v>
+        <v>6.91</v>
       </c>
       <c r="G111" s="25" t="inlineStr">
         <is>
@@ -13012,26 +11596,26 @@
       </c>
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>vo_h_order</t>
+          <t>vo_p4_prompt</t>
         </is>
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>vo_h_order.ogg</t>
+          <t>vo_p4_prompt.ogg</t>
         </is>
       </c>
       <c r="D112" s="26" t="inlineStr">
         <is>
-          <t>संख्याओं में से पहले इकाई घटाइए, फिर दहाई घटाइए।</t>
+          <t>91 में से 14 घटाइए और सही संख्या चुनिए।</t>
         </is>
       </c>
       <c r="E112" s="27" t="inlineStr">
         <is>
-          <t>Page 10, Page 11</t>
+          <t>Page 11</t>
         </is>
       </c>
       <c r="F112" s="24" t="n">
-        <v>4.45</v>
+        <v>3.57</v>
       </c>
       <c r="G112" s="25" t="inlineStr">
         <is>
@@ -13045,26 +11629,26 @@
       </c>
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_h2</t>
+          <t>vo_p4_h2</t>
         </is>
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_h2.ogg</t>
+          <t>vo_p4_h2.ogg</t>
         </is>
       </c>
       <c r="D113" s="26" t="inlineStr">
         <is>
-          <t>84 में से 46 घटाने पर, 3 दहाई और 8 इकाई बचती हैं।</t>
+          <t>91 में से 14 घटाने पर, 7 दहाई और 7 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="E113" s="27" t="inlineStr">
         <is>
-          <t>Page 10</t>
+          <t>Page 11</t>
         </is>
       </c>
       <c r="F113" s="24" t="n">
-        <v>5.47</v>
+        <v>5.17</v>
       </c>
       <c r="G113" s="25" t="inlineStr">
         <is>
@@ -13078,26 +11662,26 @@
       </c>
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_reveal</t>
+          <t>vo_p4_reveal</t>
         </is>
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_reveal.ogg</t>
+          <t>vo_p4_reveal.ogg</t>
         </is>
       </c>
       <c r="D114" s="26" t="inlineStr">
         <is>
-          <t>84 में से 46 घटाने पर 38 बचता है। तो सही संख्या यह है।</t>
+          <t>91 में से 14 घटाने पर 77 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="E114" s="27" t="inlineStr">
         <is>
-          <t>Page 10</t>
+          <t>Page 11</t>
         </is>
       </c>
       <c r="F114" s="24" t="n">
-        <v>5.52</v>
+        <v>6.49</v>
       </c>
       <c r="G114" s="25" t="inlineStr">
         <is>
@@ -13111,26 +11695,26 @@
       </c>
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_correct</t>
+          <t>vo_p4_correct</t>
         </is>
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_correct.ogg</t>
+          <t>vo_p4_correct.ogg</t>
         </is>
       </c>
       <c r="D115" s="26" t="inlineStr">
         <is>
-          <t>शाबाश! आपने सही संख्या चुन ली। 84 घटा 46 बराबर 38।</t>
+          <t>शाबाश! आपने सही संख्या चुन ली। 91 घटा 14 बराबर 77।</t>
         </is>
       </c>
       <c r="E115" s="27" t="inlineStr">
         <is>
-          <t>Page 10</t>
+          <t>Page 11</t>
         </is>
       </c>
       <c r="F115" s="24" t="n">
-        <v>6.91</v>
+        <v>7.04</v>
       </c>
       <c r="G115" s="25" t="inlineStr">
         <is>
@@ -13144,160 +11728,28 @@
       </c>
       <c r="B116" s="25" t="inlineStr">
         <is>
-          <t>vo_p4_prompt</t>
+          <t>vo_cel</t>
         </is>
       </c>
       <c r="C116" s="25" t="inlineStr">
         <is>
-          <t>vo_p4_prompt.ogg</t>
+          <t>vo_cel.ogg</t>
         </is>
       </c>
       <c r="D116" s="26" t="inlineStr">
         <is>
-          <t>91 में से 14 घटाइए और सही संख्या चुनिए।</t>
+          <t>शाबाश! आपने दहाई खोलकर घटाना सीख लिया!</t>
         </is>
       </c>
       <c r="E116" s="27" t="inlineStr">
         <is>
-          <t>Page 11</t>
+          <t>Celebration</t>
         </is>
       </c>
       <c r="F116" s="24" t="n">
-        <v>3.57</v>
+        <v>3.93</v>
       </c>
       <c r="G116" s="25" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="24" t="n">
-        <v>113</v>
-      </c>
-      <c r="B117" s="25" t="inlineStr">
-        <is>
-          <t>vo_p4_h2</t>
-        </is>
-      </c>
-      <c r="C117" s="25" t="inlineStr">
-        <is>
-          <t>vo_p4_h2.ogg</t>
-        </is>
-      </c>
-      <c r="D117" s="26" t="inlineStr">
-        <is>
-          <t>91 में से 14 घटाने पर, 7 दहाई और 7 इकाई बचती हैं।</t>
-        </is>
-      </c>
-      <c r="E117" s="27" t="inlineStr">
-        <is>
-          <t>Page 11</t>
-        </is>
-      </c>
-      <c r="F117" s="24" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="G117" s="25" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="24" t="n">
-        <v>114</v>
-      </c>
-      <c r="B118" s="25" t="inlineStr">
-        <is>
-          <t>vo_p4_reveal</t>
-        </is>
-      </c>
-      <c r="C118" s="25" t="inlineStr">
-        <is>
-          <t>vo_p4_reveal.ogg</t>
-        </is>
-      </c>
-      <c r="D118" s="26" t="inlineStr">
-        <is>
-          <t>91 में से 14 घटाने पर 77 बचता है। तो सही संख्या यह है।</t>
-        </is>
-      </c>
-      <c r="E118" s="27" t="inlineStr">
-        <is>
-          <t>Page 11</t>
-        </is>
-      </c>
-      <c r="F118" s="24" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="G118" s="25" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="24" t="n">
-        <v>115</v>
-      </c>
-      <c r="B119" s="25" t="inlineStr">
-        <is>
-          <t>vo_p4_correct</t>
-        </is>
-      </c>
-      <c r="C119" s="25" t="inlineStr">
-        <is>
-          <t>vo_p4_correct.ogg</t>
-        </is>
-      </c>
-      <c r="D119" s="26" t="inlineStr">
-        <is>
-          <t>शाबाश! आपने सही संख्या चुन ली। 91 घटा 14 बराबर 77।</t>
-        </is>
-      </c>
-      <c r="E119" s="27" t="inlineStr">
-        <is>
-          <t>Page 11</t>
-        </is>
-      </c>
-      <c r="F119" s="24" t="n">
-        <v>7.04</v>
-      </c>
-      <c r="G119" s="25" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="24" t="n">
-        <v>116</v>
-      </c>
-      <c r="B120" s="25" t="inlineStr">
-        <is>
-          <t>vo_cel</t>
-        </is>
-      </c>
-      <c r="C120" s="25" t="inlineStr">
-        <is>
-          <t>vo_cel.ogg</t>
-        </is>
-      </c>
-      <c r="D120" s="26" t="inlineStr">
-        <is>
-          <t>शाबाश! आपने दहाई खोलकर घटाना सीख लिया!</t>
-        </is>
-      </c>
-      <c r="E120" s="27" t="inlineStr">
-        <is>
-          <t>Celebration</t>
-        </is>
-      </c>
-      <c r="F120" s="24" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="G120" s="25" t="inlineStr">
         <is>
           <t>TTS (Gemini, Kore)</t>
         </is>
@@ -13675,7 +12127,7 @@
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>179 rows, 116 distinct recordings (see 'Recording list'). In the card but not heard in this build (not listed): vo_rm_ones_less, vo_rm_ones_more.</t>
+          <t>151 rows, 112 distinct recordings (see 'Recording list'). In the card but not heard in this build (not listed): vo_rm_ones_less, vo_rm_ones_more.</t>
         </is>
       </c>
     </row>

--- a/lesson_vo_manifest.xlsx
+++ b/lesson_vo_manifest.xlsx
@@ -577,7 +577,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K155"/>
+  <dimension ref="A1:K162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -4492,27 +4492,27 @@
       </c>
       <c r="E84" s="17" t="inlineStr">
         <is>
-          <t>vo_g1_eq</t>
+          <t>vo_g1_correct_late</t>
         </is>
       </c>
       <c r="F84" s="19" t="inlineStr">
         <is>
-          <t>इसलिए 42 घटा 27 बराबर 15।</t>
+          <t>42 में से 27 घटाने पर हमें मिलीं 1 दहाई और 5 इकाई, यानी 15।</t>
         </is>
       </c>
       <c r="G84" s="18" t="inlineStr">
         <is>
-          <t>the equation read out</t>
+          <t>correct answer after a wrong one</t>
         </is>
       </c>
       <c r="H84" s="18" t="inlineStr">
         <is>
-          <t>after the correct line: each part lights as it is said</t>
+          <t>the same as the correct line, without «शाबाश» (only a first-try answer gets it)</t>
         </is>
       </c>
       <c r="I84" s="18" t="inlineStr"/>
       <c r="J84" s="16" t="n">
-        <v>4.26</v>
+        <v>6.47</v>
       </c>
       <c r="K84" s="17" t="inlineStr">
         <is>
@@ -4526,40 +4526,40 @@
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>Page 6</t>
+          <t>Page 5</t>
         </is>
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
-          <t>G2 · PV_SUB  (53 − 14)</t>
+          <t>G1 · PV_SUB  (42 − 27)</t>
         </is>
       </c>
       <c r="D85" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E85" s="13" t="inlineStr">
         <is>
-          <t>vo_g2_prompt</t>
+          <t>vo_g1_eq</t>
         </is>
       </c>
       <c r="F85" s="15" t="inlineStr">
         <is>
-          <t>53 में से 14 घटाइए।</t>
+          <t>इसलिए 42 घटा 27 बराबर 15।</t>
         </is>
       </c>
       <c r="G85" s="14" t="inlineStr">
         <is>
-          <t>page instruction</t>
+          <t>the equation read out</t>
         </is>
       </c>
       <c r="H85" s="14" t="inlineStr">
         <is>
-          <t>as the page opens (the speaker replays it)</t>
+          <t>after the correct line: each part lights as it is said</t>
         </is>
       </c>
       <c r="I85" s="14" t="inlineStr"/>
       <c r="J85" s="12" t="n">
-        <v>2.56</v>
+        <v>4.26</v>
       </c>
       <c r="K85" s="13" t="inlineStr">
         <is>
@@ -4582,31 +4582,31 @@
         </is>
       </c>
       <c r="D86" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" s="17" t="inlineStr">
         <is>
-          <t>vo_g2_build</t>
+          <t>vo_g2_prompt</t>
         </is>
       </c>
       <c r="F86" s="19" t="inlineStr">
         <is>
-          <t>सबसे पहले ब्लॉक्स की सहायता से 53 बनाइए।</t>
+          <t>53 में से 14 घटाइए।</t>
         </is>
       </c>
       <c r="G86" s="18" t="inlineStr">
         <is>
-          <t>build instruction</t>
+          <t>page instruction</t>
         </is>
       </c>
       <c r="H86" s="18" t="inlineStr">
         <is>
-          <t>after the instruction; the + box comes in, the rod + pulses on its «… दहाई» (or the number), the cube + on «… इकाई»</t>
+          <t>as the page opens (the speaker replays it)</t>
         </is>
       </c>
       <c r="I86" s="18" t="inlineStr"/>
       <c r="J86" s="16" t="n">
-        <v>4.23</v>
+        <v>2.56</v>
       </c>
       <c r="K86" s="17" t="inlineStr">
         <is>
@@ -4629,35 +4629,31 @@
         </is>
       </c>
       <c r="D87" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>vo_idle_build_t</t>
+          <t>vo_g2_build</t>
         </is>
       </c>
       <c r="F87" s="15" t="inlineStr">
         <is>
-          <t>अब दहाई बनाइए।</t>
+          <t>सबसे पहले ब्लॉक्स की सहायता से 53 बनाइए।</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
         <is>
-          <t>inactivity reminder - building</t>
+          <t>build instruction</t>
         </is>
       </c>
       <c r="H87" s="14" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the build step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I87" s="14" t="inlineStr">
-        <is>
-          <t>Page 4, Page 5</t>
-        </is>
-      </c>
+          <t>after the instruction; the + box comes in, the rod + pulses on its «… दहाई» (or the number), the cube + on «… इकाई»</t>
+        </is>
+      </c>
+      <c r="I87" s="14" t="inlineStr"/>
       <c r="J87" s="12" t="n">
-        <v>1.95</v>
+        <v>4.23</v>
       </c>
       <c r="K87" s="13" t="inlineStr">
         <is>
@@ -4680,16 +4676,16 @@
         </is>
       </c>
       <c r="D88" s="16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E88" s="17" t="inlineStr">
         <is>
-          <t>vo_idle_build_o</t>
+          <t>vo_idle_build_t</t>
         </is>
       </c>
       <c r="F88" s="19" t="inlineStr">
         <is>
-          <t>अब इकाई बनाइए।</t>
+          <t>अब दहाई बनाइए।</t>
         </is>
       </c>
       <c r="G88" s="18" t="inlineStr">
@@ -4704,11 +4700,11 @@
       </c>
       <c r="I88" s="18" t="inlineStr">
         <is>
-          <t>Page 5</t>
+          <t>Page 4, Page 5</t>
         </is>
       </c>
       <c r="J88" s="16" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="K88" s="17" t="inlineStr">
         <is>
@@ -4731,31 +4727,35 @@
         </is>
       </c>
       <c r="D89" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>vo_g2_sub</t>
+          <t>vo_idle_build_o</t>
         </is>
       </c>
       <c r="F89" s="15" t="inlineStr">
         <is>
-          <t>और अब इसमें से 14 घटाइए।</t>
+          <t>अब इकाई बनाइए।</t>
         </is>
       </c>
       <c r="G89" s="14" t="inlineStr">
         <is>
-          <t>what is taken away</t>
+          <t>inactivity reminder - building</t>
         </is>
       </c>
       <c r="H89" s="14" t="inlineStr">
         <is>
-          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
-        </is>
-      </c>
-      <c r="I89" s="14" t="inlineStr"/>
+          <t>after 7s with no tap at the build step, again every 7s while idle</t>
+        </is>
+      </c>
+      <c r="I89" s="14" t="inlineStr">
+        <is>
+          <t>Page 5</t>
+        </is>
+      </c>
       <c r="J89" s="12" t="n">
-        <v>2.32</v>
+        <v>1.85</v>
       </c>
       <c r="K89" s="13" t="inlineStr">
         <is>
@@ -4778,35 +4778,31 @@
         </is>
       </c>
       <c r="D90" s="16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E90" s="17" t="inlineStr">
         <is>
-          <t>vo_idle_open</t>
+          <t>vo_g2_sub</t>
         </is>
       </c>
       <c r="F90" s="19" t="inlineStr">
         <is>
-          <t>अब 1 दहाई को इकाई में लाइए।</t>
+          <t>और अब इसमें से 14 घटाइए।</t>
         </is>
       </c>
       <c r="G90" s="18" t="inlineStr">
         <is>
-          <t>inactivity reminder - open a ten</t>
+          <t>what is taken away</t>
         </is>
       </c>
       <c r="H90" s="18" t="inlineStr">
         <is>
-          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
-        </is>
-      </c>
-      <c r="I90" s="18" t="inlineStr">
-        <is>
-          <t>Page 5, Page 7, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
+        </is>
+      </c>
+      <c r="I90" s="18" t="inlineStr"/>
       <c r="J90" s="16" t="n">
-        <v>3.16</v>
+        <v>2.32</v>
       </c>
       <c r="K90" s="17" t="inlineStr">
         <is>
@@ -4829,31 +4825,35 @@
         </is>
       </c>
       <c r="D91" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>vo_g2_rm_ones</t>
+          <t>vo_idle_open</t>
         </is>
       </c>
       <c r="F91" s="15" t="inlineStr">
         <is>
-          <t>इसमें से 4 इकाई को हटाइए।</t>
+          <t>अब 1 दहाई को इकाई में लाइए।</t>
         </is>
       </c>
       <c r="G91" s="14" t="inlineStr">
         <is>
-          <t>take-away step - the ones</t>
+          <t>inactivity reminder - open a ten</t>
         </is>
       </c>
       <c r="H91" s="14" t="inlineStr">
         <is>
-          <t>after the ten is opened; the ones column beats on «इकाई»</t>
-        </is>
-      </c>
-      <c r="I91" s="14" t="inlineStr"/>
+          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
+        </is>
+      </c>
+      <c r="I91" s="14" t="inlineStr">
+        <is>
+          <t>Page 5, Page 7, Page 8, Page 9</t>
+        </is>
+      </c>
       <c r="J91" s="12" t="n">
-        <v>2.58</v>
+        <v>3.16</v>
       </c>
       <c r="K91" s="13" t="inlineStr">
         <is>
@@ -4876,31 +4876,31 @@
         </is>
       </c>
       <c r="D92" s="16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E92" s="17" t="inlineStr">
         <is>
-          <t>vo_g2_rm_tens</t>
+          <t>vo_g2_rm_ones</t>
         </is>
       </c>
       <c r="F92" s="19" t="inlineStr">
         <is>
-          <t>अब दहाइयाँ घटाइए।</t>
+          <t>इसमें से 4 इकाई को हटाइए।</t>
         </is>
       </c>
       <c r="G92" s="18" t="inlineStr">
         <is>
-          <t>take-away step - the tens</t>
+          <t>take-away step - the ones</t>
         </is>
       </c>
       <c r="H92" s="18" t="inlineStr">
         <is>
-          <t>when the ones are done; the tens column beats</t>
+          <t>after the ten is opened; the ones column beats on «इकाई»</t>
         </is>
       </c>
       <c r="I92" s="18" t="inlineStr"/>
       <c r="J92" s="16" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="K92" s="17" t="inlineStr">
         <is>
@@ -4923,35 +4923,31 @@
         </is>
       </c>
       <c r="D93" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E93" s="13" t="inlineStr">
         <is>
-          <t>vo_idle_rm_o</t>
+          <t>vo_g2_rm_tens</t>
         </is>
       </c>
       <c r="F93" s="15" t="inlineStr">
         <is>
-          <t>अब इकाई हटाइए।</t>
+          <t>अब दहाइयाँ घटाइए।</t>
         </is>
       </c>
       <c r="G93" s="14" t="inlineStr">
         <is>
-          <t>inactivity reminder - taking away</t>
+          <t>take-away step - the tens</t>
         </is>
       </c>
       <c r="H93" s="14" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I93" s="14" t="inlineStr">
-        <is>
-          <t>Page 4, Page 5, Page 7, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>when the ones are done; the tens column beats</t>
+        </is>
+      </c>
+      <c r="I93" s="14" t="inlineStr"/>
       <c r="J93" s="12" t="n">
-        <v>2.21</v>
+        <v>2.16</v>
       </c>
       <c r="K93" s="13" t="inlineStr">
         <is>
@@ -4974,16 +4970,16 @@
         </is>
       </c>
       <c r="D94" s="16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E94" s="17" t="inlineStr">
         <is>
-          <t>vo_idle_rm_t</t>
+          <t>vo_idle_rm_o</t>
         </is>
       </c>
       <c r="F94" s="19" t="inlineStr">
         <is>
-          <t>अब दहाई हटाइए।</t>
+          <t>अब इकाई हटाइए।</t>
         </is>
       </c>
       <c r="G94" s="18" t="inlineStr">
@@ -5002,7 +4998,7 @@
         </is>
       </c>
       <c r="J94" s="16" t="n">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="K94" s="17" t="inlineStr">
         <is>
@@ -5025,35 +5021,35 @@
         </is>
       </c>
       <c r="D95" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E95" s="13" t="inlineStr">
         <is>
-          <t>vo_rm_tens_more</t>
+          <t>vo_idle_rm_t</t>
         </is>
       </c>
       <c r="F95" s="15" t="inlineStr">
         <is>
-          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
+          <t>अब दहाई हटाइए।</t>
         </is>
       </c>
       <c r="G95" s="14" t="inlineStr">
         <is>
-          <t>take-away mistake - 1st time</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H95" s="14" t="inlineStr">
         <is>
-          <t>a ten too many taken: the tens go back, this line</t>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
         </is>
       </c>
       <c r="I95" s="14" t="inlineStr">
         <is>
-          <t>Page 5, Page 7, Page 8, Page 9</t>
+          <t>Page 4, Page 5, Page 7, Page 8, Page 9</t>
         </is>
       </c>
       <c r="J95" s="12" t="n">
-        <v>4.05</v>
+        <v>2.27</v>
       </c>
       <c r="K95" s="13" t="inlineStr">
         <is>
@@ -5076,26 +5072,26 @@
         </is>
       </c>
       <c r="D96" s="16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E96" s="17" t="inlineStr">
         <is>
-          <t>vo_rm_guide</t>
+          <t>vo_rm_tens_more</t>
         </is>
       </c>
       <c r="F96" s="19" t="inlineStr">
         <is>
-          <t>इनमें से इतने हटाइए।</t>
+          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
         </is>
       </c>
       <c r="G96" s="18" t="inlineStr">
         <is>
-          <t>take-away mistake - 2nd time</t>
+          <t>take-away mistake - 1st time</t>
         </is>
       </c>
       <c r="H96" s="18" t="inlineStr">
         <is>
-          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
+          <t>a ten too many taken: the tens go back, this line</t>
         </is>
       </c>
       <c r="I96" s="18" t="inlineStr">
@@ -5104,7 +5100,7 @@
         </is>
       </c>
       <c r="J96" s="16" t="n">
-        <v>2.09</v>
+        <v>4.05</v>
       </c>
       <c r="K96" s="17" t="inlineStr">
         <is>
@@ -5127,35 +5123,35 @@
         </is>
       </c>
       <c r="D97" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>vo_ask_pick</t>
+          <t>vo_rm_guide</t>
         </is>
       </c>
       <c r="F97" s="15" t="inlineStr">
         <is>
-          <t>अब कितने बचे? सही संख्या चुनिए।</t>
+          <t>इनमें से इतने हटाइए।</t>
         </is>
       </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
-          <t>the answer question</t>
+          <t>take-away mistake - 2nd time</t>
         </is>
       </c>
       <c r="H97" s="14" t="inlineStr">
         <is>
-          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
+          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
         </is>
       </c>
       <c r="I97" s="14" t="inlineStr">
         <is>
-          <t>Page 5, Page 7</t>
+          <t>Page 5, Page 7, Page 8, Page 9</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
-        <v>3.2</v>
+        <v>2.09</v>
       </c>
       <c r="K97" s="13" t="inlineStr">
         <is>
@@ -5178,35 +5174,35 @@
         </is>
       </c>
       <c r="D98" s="16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E98" s="17" t="inlineStr">
         <is>
-          <t>vo_h_recount</t>
+          <t>vo_ask_pick</t>
         </is>
       </c>
       <c r="F98" s="19" t="inlineStr">
         <is>
-          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
+          <t>अब कितने बचे? सही संख्या चुनिए।</t>
         </is>
       </c>
       <c r="G98" s="18" t="inlineStr">
         <is>
-          <t>Hint 1 (1st wrong answer)</t>
+          <t>the answer question</t>
         </is>
       </c>
       <c r="H98" s="18" t="inlineStr">
         <is>
-          <t>the columns beat on «दहाई» / «इकाई»</t>
+          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
         </is>
       </c>
       <c r="I98" s="18" t="inlineStr">
         <is>
-          <t>Page 5, Page 7, Page 8, Page 9</t>
+          <t>Page 5, Page 7</t>
         </is>
       </c>
       <c r="J98" s="16" t="n">
-        <v>3.31</v>
+        <v>3.2</v>
       </c>
       <c r="K98" s="17" t="inlineStr">
         <is>
@@ -5229,31 +5225,35 @@
         </is>
       </c>
       <c r="D99" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>vo_g2_h2</t>
+          <t>vo_h_recount</t>
         </is>
       </c>
       <c r="F99" s="15" t="inlineStr">
         <is>
-          <t>53 में से 14 घटाने पर, 3 दहाई और 9 इकाई बचती हैं।</t>
+          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
         </is>
       </c>
       <c r="G99" s="14" t="inlineStr">
         <is>
-          <t>Hint 2 (2nd wrong answer)</t>
+          <t>Hint 1 (1st wrong answer)</t>
         </is>
       </c>
       <c r="H99" s="14" t="inlineStr">
         <is>
-          <t>the numbers light; the tens and ones left beat on their words</t>
-        </is>
-      </c>
-      <c r="I99" s="14" t="inlineStr"/>
+          <t>the columns beat on «दहाई» / «इकाई»</t>
+        </is>
+      </c>
+      <c r="I99" s="14" t="inlineStr">
+        <is>
+          <t>Page 5, Page 7, Page 8, Page 9</t>
+        </is>
+      </c>
       <c r="J99" s="12" t="n">
-        <v>4.71</v>
+        <v>3.31</v>
       </c>
       <c r="K99" s="13" t="inlineStr">
         <is>
@@ -5276,31 +5276,31 @@
         </is>
       </c>
       <c r="D100" s="16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>vo_g2_reveal</t>
+          <t>vo_g2_h2</t>
         </is>
       </c>
       <c r="F100" s="19" t="inlineStr">
         <is>
-          <t>53 में से 14 घटाने पर 39 बचता है। तो सही संख्या यह है।</t>
+          <t>53 में से 14 घटाने पर, 3 दहाई और 9 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="G100" s="18" t="inlineStr">
         <is>
-          <t>Hint 3 (3rd wrong answer)</t>
+          <t>Hint 2 (2nd wrong answer)</t>
         </is>
       </c>
       <c r="H100" s="18" t="inlineStr">
         <is>
-          <t>the right card / the right keys lit (one key at a time), the others off</t>
+          <t>the numbers light; the tens and ones left beat on their words</t>
         </is>
       </c>
       <c r="I100" s="18" t="inlineStr"/>
       <c r="J100" s="16" t="n">
-        <v>5.8</v>
+        <v>4.71</v>
       </c>
       <c r="K100" s="17" t="inlineStr">
         <is>
@@ -5323,31 +5323,31 @@
         </is>
       </c>
       <c r="D101" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>vo_g2_correct</t>
+          <t>vo_g2_reveal</t>
         </is>
       </c>
       <c r="F101" s="15" t="inlineStr">
         <is>
-          <t>शाबाश! 53 घटा 14 बराबर 39।</t>
+          <t>53 में से 14 घटाने पर 39 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="G101" s="14" t="inlineStr">
         <is>
-          <t>correct answer</t>
+          <t>Hint 3 (3rd wrong answer)</t>
         </is>
       </c>
       <c r="H101" s="14" t="inlineStr">
         <is>
-          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
+          <t>the right card / the right keys lit (one key at a time), the others off</t>
         </is>
       </c>
       <c r="I101" s="14" t="inlineStr"/>
       <c r="J101" s="12" t="n">
-        <v>4.48</v>
+        <v>5.8</v>
       </c>
       <c r="K101" s="13" t="inlineStr">
         <is>
@@ -5361,40 +5361,40 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 6</t>
         </is>
       </c>
       <c r="C102" s="18" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>G2 · PV_SUB  (53 − 14)</t>
         </is>
       </c>
       <c r="D102" s="16" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E102" s="17" t="inlineStr">
         <is>
-          <t>vo_g3_prompt</t>
+          <t>vo_g2_correct</t>
         </is>
       </c>
       <c r="F102" s="19" t="inlineStr">
         <is>
-          <t>46 में से 28 घटाइए।</t>
+          <t>शाबाश! 53 घटा 14 बराबर 39।</t>
         </is>
       </c>
       <c r="G102" s="18" t="inlineStr">
         <is>
-          <t>page instruction</t>
+          <t>correct answer</t>
         </is>
       </c>
       <c r="H102" s="18" t="inlineStr">
         <is>
-          <t>as the page opens (the speaker replays it)</t>
+          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
         </is>
       </c>
       <c r="I102" s="18" t="inlineStr"/>
       <c r="J102" s="16" t="n">
-        <v>2.72</v>
+        <v>4.48</v>
       </c>
       <c r="K102" s="17" t="inlineStr">
         <is>
@@ -5408,40 +5408,40 @@
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 6</t>
         </is>
       </c>
       <c r="C103" s="14" t="inlineStr">
         <is>
-          <t>G3 · PV_SUB  (46 − 28)</t>
+          <t>G2 · PV_SUB  (53 − 14)</t>
         </is>
       </c>
       <c r="D103" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E103" s="13" t="inlineStr">
         <is>
-          <t>vo_g3_sub</t>
+          <t>vo_g2_correct_late</t>
         </is>
       </c>
       <c r="F103" s="15" t="inlineStr">
         <is>
-          <t>और अब इसमें से 28 घटाइए।</t>
+          <t>53 घटा 14 बराबर 39।</t>
         </is>
       </c>
       <c r="G103" s="14" t="inlineStr">
         <is>
-          <t>what is taken away</t>
+          <t>correct answer after a wrong one</t>
         </is>
       </c>
       <c r="H103" s="14" t="inlineStr">
         <is>
-          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
+          <t>the same as the correct line, without «शाबाश» (only a first-try answer gets it)</t>
         </is>
       </c>
       <c r="I103" s="14" t="inlineStr"/>
       <c r="J103" s="12" t="n">
-        <v>2.67</v>
+        <v>3.88</v>
       </c>
       <c r="K103" s="13" t="inlineStr">
         <is>
@@ -5464,35 +5464,31 @@
         </is>
       </c>
       <c r="D104" s="16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E104" s="17" t="inlineStr">
         <is>
-          <t>vo_idle_open</t>
+          <t>vo_g3_prompt</t>
         </is>
       </c>
       <c r="F104" s="19" t="inlineStr">
         <is>
-          <t>अब 1 दहाई को इकाई में लाइए।</t>
+          <t>46 में से 28 घटाइए।</t>
         </is>
       </c>
       <c r="G104" s="18" t="inlineStr">
         <is>
-          <t>inactivity reminder - open a ten</t>
+          <t>page instruction</t>
         </is>
       </c>
       <c r="H104" s="18" t="inlineStr">
         <is>
-          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
-        </is>
-      </c>
-      <c r="I104" s="18" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>as the page opens (the speaker replays it)</t>
+        </is>
+      </c>
+      <c r="I104" s="18" t="inlineStr"/>
       <c r="J104" s="16" t="n">
-        <v>3.16</v>
+        <v>2.72</v>
       </c>
       <c r="K104" s="17" t="inlineStr">
         <is>
@@ -5515,31 +5511,31 @@
         </is>
       </c>
       <c r="D105" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>vo_g3_rm_ones</t>
+          <t>vo_g3_sub</t>
         </is>
       </c>
       <c r="F105" s="15" t="inlineStr">
         <is>
-          <t>इसमें से 8 इकाई को हटाइए।</t>
+          <t>और अब इसमें से 28 घटाइए।</t>
         </is>
       </c>
       <c r="G105" s="14" t="inlineStr">
         <is>
-          <t>take-away step - the ones</t>
+          <t>what is taken away</t>
         </is>
       </c>
       <c r="H105" s="14" t="inlineStr">
         <is>
-          <t>after the ten is opened; the ones column beats on «इकाई»</t>
+          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
         </is>
       </c>
       <c r="I105" s="14" t="inlineStr"/>
       <c r="J105" s="12" t="n">
-        <v>3.03</v>
+        <v>2.67</v>
       </c>
       <c r="K105" s="13" t="inlineStr">
         <is>
@@ -5562,31 +5558,35 @@
         </is>
       </c>
       <c r="D106" s="16" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E106" s="17" t="inlineStr">
         <is>
-          <t>vo_g3_rm_tens</t>
+          <t>vo_idle_open</t>
         </is>
       </c>
       <c r="F106" s="19" t="inlineStr">
         <is>
-          <t>अब दहाइयाँ हटाइए।</t>
+          <t>अब 1 दहाई को इकाई में लाइए।</t>
         </is>
       </c>
       <c r="G106" s="18" t="inlineStr">
         <is>
-          <t>take-away step - the tens</t>
+          <t>inactivity reminder - open a ten</t>
         </is>
       </c>
       <c r="H106" s="18" t="inlineStr">
         <is>
-          <t>when the ones are done; the tens column beats</t>
-        </is>
-      </c>
-      <c r="I106" s="18" t="inlineStr"/>
+          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
+        </is>
+      </c>
+      <c r="I106" s="18" t="inlineStr">
+        <is>
+          <t>Page 5, Page 6, Page 8, Page 9</t>
+        </is>
+      </c>
       <c r="J106" s="16" t="n">
-        <v>2.47</v>
+        <v>3.16</v>
       </c>
       <c r="K106" s="17" t="inlineStr">
         <is>
@@ -5609,35 +5609,31 @@
         </is>
       </c>
       <c r="D107" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
-          <t>vo_idle_rm_o</t>
+          <t>vo_g3_rm_ones</t>
         </is>
       </c>
       <c r="F107" s="15" t="inlineStr">
         <is>
-          <t>अब इकाई हटाइए।</t>
+          <t>इसमें से 8 इकाई को हटाइए।</t>
         </is>
       </c>
       <c r="G107" s="14" t="inlineStr">
         <is>
-          <t>inactivity reminder - taking away</t>
+          <t>take-away step - the ones</t>
         </is>
       </c>
       <c r="H107" s="14" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I107" s="14" t="inlineStr">
-        <is>
-          <t>Page 4, Page 5, Page 6, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>after the ten is opened; the ones column beats on «इकाई»</t>
+        </is>
+      </c>
+      <c r="I107" s="14" t="inlineStr"/>
       <c r="J107" s="12" t="n">
-        <v>2.21</v>
+        <v>3.03</v>
       </c>
       <c r="K107" s="13" t="inlineStr">
         <is>
@@ -5660,35 +5656,31 @@
         </is>
       </c>
       <c r="D108" s="16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E108" s="17" t="inlineStr">
         <is>
-          <t>vo_idle_rm_t</t>
+          <t>vo_g3_rm_tens</t>
         </is>
       </c>
       <c r="F108" s="19" t="inlineStr">
         <is>
-          <t>अब दहाई हटाइए।</t>
+          <t>अब दहाइयाँ हटाइए।</t>
         </is>
       </c>
       <c r="G108" s="18" t="inlineStr">
         <is>
-          <t>inactivity reminder - taking away</t>
+          <t>take-away step - the tens</t>
         </is>
       </c>
       <c r="H108" s="18" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I108" s="18" t="inlineStr">
-        <is>
-          <t>Page 4, Page 5, Page 6, Page 8, Page 9</t>
-        </is>
-      </c>
+          <t>when the ones are done; the tens column beats</t>
+        </is>
+      </c>
+      <c r="I108" s="18" t="inlineStr"/>
       <c r="J108" s="16" t="n">
-        <v>2.27</v>
+        <v>2.47</v>
       </c>
       <c r="K108" s="17" t="inlineStr">
         <is>
@@ -5711,35 +5703,35 @@
         </is>
       </c>
       <c r="D109" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E109" s="13" t="inlineStr">
         <is>
-          <t>vo_rm_tens_more</t>
+          <t>vo_idle_rm_o</t>
         </is>
       </c>
       <c r="F109" s="15" t="inlineStr">
         <is>
-          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
+          <t>अब इकाई हटाइए।</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
         <is>
-          <t>take-away mistake - 1st time</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H109" s="14" t="inlineStr">
         <is>
-          <t>a ten too many taken: the tens go back, this line</t>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
         </is>
       </c>
       <c r="I109" s="14" t="inlineStr">
         <is>
-          <t>Page 5, Page 6, Page 8, Page 9</t>
+          <t>Page 4, Page 5, Page 6, Page 8, Page 9</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
-        <v>4.05</v>
+        <v>2.21</v>
       </c>
       <c r="K109" s="13" t="inlineStr">
         <is>
@@ -5762,35 +5754,35 @@
         </is>
       </c>
       <c r="D110" s="16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E110" s="17" t="inlineStr">
         <is>
-          <t>vo_rm_guide</t>
+          <t>vo_idle_rm_t</t>
         </is>
       </c>
       <c r="F110" s="19" t="inlineStr">
         <is>
-          <t>इनमें से इतने हटाइए।</t>
+          <t>अब दहाई हटाइए।</t>
         </is>
       </c>
       <c r="G110" s="18" t="inlineStr">
         <is>
-          <t>take-away mistake - 2nd time</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H110" s="18" t="inlineStr">
         <is>
-          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
         </is>
       </c>
       <c r="I110" s="18" t="inlineStr">
         <is>
-          <t>Page 5, Page 6, Page 8, Page 9</t>
+          <t>Page 4, Page 5, Page 6, Page 8, Page 9</t>
         </is>
       </c>
       <c r="J110" s="16" t="n">
-        <v>2.09</v>
+        <v>2.27</v>
       </c>
       <c r="K110" s="17" t="inlineStr">
         <is>
@@ -5813,35 +5805,35 @@
         </is>
       </c>
       <c r="D111" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E111" s="13" t="inlineStr">
         <is>
-          <t>vo_ask_pick</t>
+          <t>vo_rm_tens_more</t>
         </is>
       </c>
       <c r="F111" s="15" t="inlineStr">
         <is>
-          <t>अब कितने बचे? सही संख्या चुनिए।</t>
+          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
         </is>
       </c>
       <c r="G111" s="14" t="inlineStr">
         <is>
-          <t>the answer question</t>
+          <t>take-away mistake - 1st time</t>
         </is>
       </c>
       <c r="H111" s="14" t="inlineStr">
         <is>
-          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
+          <t>a ten too many taken: the tens go back, this line</t>
         </is>
       </c>
       <c r="I111" s="14" t="inlineStr">
         <is>
-          <t>Page 5, Page 6</t>
+          <t>Page 5, Page 6, Page 8, Page 9</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
-        <v>3.2</v>
+        <v>4.05</v>
       </c>
       <c r="K111" s="13" t="inlineStr">
         <is>
@@ -5864,26 +5856,26 @@
         </is>
       </c>
       <c r="D112" s="16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E112" s="17" t="inlineStr">
         <is>
-          <t>vo_h_recount</t>
+          <t>vo_rm_guide</t>
         </is>
       </c>
       <c r="F112" s="19" t="inlineStr">
         <is>
-          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
+          <t>इनमें से इतने हटाइए।</t>
         </is>
       </c>
       <c r="G112" s="18" t="inlineStr">
         <is>
-          <t>Hint 1 (1st wrong answer)</t>
+          <t>take-away mistake - 2nd time</t>
         </is>
       </c>
       <c r="H112" s="18" t="inlineStr">
         <is>
-          <t>the columns beat on «दहाई» / «इकाई»</t>
+          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
         </is>
       </c>
       <c r="I112" s="18" t="inlineStr">
@@ -5892,7 +5884,7 @@
         </is>
       </c>
       <c r="J112" s="16" t="n">
-        <v>3.31</v>
+        <v>2.09</v>
       </c>
       <c r="K112" s="17" t="inlineStr">
         <is>
@@ -5915,31 +5907,35 @@
         </is>
       </c>
       <c r="D113" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
-          <t>vo_g3_h2</t>
+          <t>vo_ask_pick</t>
         </is>
       </c>
       <c r="F113" s="15" t="inlineStr">
         <is>
-          <t>46 में से 28 घटाने पर, 1 दहाई और 8 इकाई बचती हैं।</t>
+          <t>अब कितने बचे? सही संख्या चुनिए।</t>
         </is>
       </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
-          <t>Hint 2 (2nd wrong answer)</t>
+          <t>the answer question</t>
         </is>
       </c>
       <c r="H113" s="14" t="inlineStr">
         <is>
-          <t>the numbers light; the tens and ones left beat on their words</t>
-        </is>
-      </c>
-      <c r="I113" s="14" t="inlineStr"/>
+          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
+        </is>
+      </c>
+      <c r="I113" s="14" t="inlineStr">
+        <is>
+          <t>Page 5, Page 6</t>
+        </is>
+      </c>
       <c r="J113" s="12" t="n">
-        <v>5.55</v>
+        <v>3.2</v>
       </c>
       <c r="K113" s="13" t="inlineStr">
         <is>
@@ -5962,31 +5958,35 @@
         </is>
       </c>
       <c r="D114" s="16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E114" s="17" t="inlineStr">
         <is>
-          <t>vo_g3_reveal</t>
+          <t>vo_h_recount</t>
         </is>
       </c>
       <c r="F114" s="19" t="inlineStr">
         <is>
-          <t>46 में से 28 घटाने पर 18 बचता है। तो सही संख्या यह है।</t>
+          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
         </is>
       </c>
       <c r="G114" s="18" t="inlineStr">
         <is>
-          <t>Hint 3 (3rd wrong answer)</t>
+          <t>Hint 1 (1st wrong answer)</t>
         </is>
       </c>
       <c r="H114" s="18" t="inlineStr">
         <is>
-          <t>the right card / the right keys lit (one key at a time), the others off</t>
-        </is>
-      </c>
-      <c r="I114" s="18" t="inlineStr"/>
+          <t>the columns beat on «दहाई» / «इकाई»</t>
+        </is>
+      </c>
+      <c r="I114" s="18" t="inlineStr">
+        <is>
+          <t>Page 5, Page 6, Page 8, Page 9</t>
+        </is>
+      </c>
       <c r="J114" s="16" t="n">
-        <v>5.75</v>
+        <v>3.31</v>
       </c>
       <c r="K114" s="17" t="inlineStr">
         <is>
@@ -6009,31 +6009,31 @@
         </is>
       </c>
       <c r="D115" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E115" s="13" t="inlineStr">
         <is>
-          <t>vo_g3_correct</t>
+          <t>vo_g3_h2</t>
         </is>
       </c>
       <c r="F115" s="15" t="inlineStr">
         <is>
-          <t>शाबाश! 46 घटा 28 बराबर 18।</t>
+          <t>46 में से 28 घटाने पर, 1 दहाई और 8 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="G115" s="14" t="inlineStr">
         <is>
-          <t>correct answer</t>
+          <t>Hint 2 (2nd wrong answer)</t>
         </is>
       </c>
       <c r="H115" s="14" t="inlineStr">
         <is>
-          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
+          <t>the numbers light; the tens and ones left beat on their words</t>
         </is>
       </c>
       <c r="I115" s="14" t="inlineStr"/>
       <c r="J115" s="12" t="n">
-        <v>4.99</v>
+        <v>5.55</v>
       </c>
       <c r="K115" s="13" t="inlineStr">
         <is>
@@ -6042,49 +6042,49 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="8" t="n">
+      <c r="A116" s="16" t="n">
         <v>112</v>
       </c>
-      <c r="B116" s="9" t="inlineStr">
-        <is>
-          <t>Transition 3</t>
-        </is>
-      </c>
-      <c r="C116" s="10" t="inlineStr">
-        <is>
-          <t>before page 8</t>
-        </is>
-      </c>
-      <c r="D116" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" s="9" t="inlineStr">
-        <is>
-          <t>vo_pt_practice</t>
-        </is>
-      </c>
-      <c r="F116" s="11" t="inlineStr">
-        <is>
-          <t>वाह! अब आपकी बारी।</t>
-        </is>
-      </c>
-      <c r="G116" s="10" t="inlineStr">
-        <is>
-          <t>transition line</t>
-        </is>
-      </c>
-      <c r="H116" s="10" t="inlineStr">
-        <is>
-          <t>Swiftee rises talking; «अब आपकी बारी!» wipes in as it is said</t>
-        </is>
-      </c>
-      <c r="I116" s="10" t="inlineStr"/>
-      <c r="J116" s="8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="K116" s="9" t="inlineStr">
-        <is>
-          <t>Copied (HI02H11, recorded voice)</t>
+      <c r="B116" s="17" t="inlineStr">
+        <is>
+          <t>Page 7</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="inlineStr">
+        <is>
+          <t>G3 · PV_SUB  (46 − 28)</t>
+        </is>
+      </c>
+      <c r="D116" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="E116" s="17" t="inlineStr">
+        <is>
+          <t>vo_g3_reveal</t>
+        </is>
+      </c>
+      <c r="F116" s="19" t="inlineStr">
+        <is>
+          <t>46 में से 28 घटाने पर 18 बचता है। तो सही संख्या यह है।</t>
+        </is>
+      </c>
+      <c r="G116" s="18" t="inlineStr">
+        <is>
+          <t>Hint 3 (3rd wrong answer)</t>
+        </is>
+      </c>
+      <c r="H116" s="18" t="inlineStr">
+        <is>
+          <t>the right card / the right keys lit (one key at a time), the others off</t>
+        </is>
+      </c>
+      <c r="I116" s="18" t="inlineStr"/>
+      <c r="J116" s="16" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K116" s="17" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
         </is>
       </c>
     </row>
@@ -6094,40 +6094,40 @@
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>G3 · PV_SUB  (46 − 28)</t>
         </is>
       </c>
       <c r="D117" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E117" s="13" t="inlineStr">
         <is>
-          <t>vo_p1_prompt</t>
+          <t>vo_g3_correct</t>
         </is>
       </c>
       <c r="F117" s="15" t="inlineStr">
         <is>
-          <t>74 में से 58 घटाइए।</t>
+          <t>शाबाश! 46 घटा 28 बराबर 18।</t>
         </is>
       </c>
       <c r="G117" s="14" t="inlineStr">
         <is>
-          <t>page instruction</t>
+          <t>correct answer</t>
         </is>
       </c>
       <c r="H117" s="14" t="inlineStr">
         <is>
-          <t>as the page opens (the speaker replays it)</t>
+          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
         </is>
       </c>
       <c r="I117" s="14" t="inlineStr"/>
       <c r="J117" s="12" t="n">
-        <v>2.5</v>
+        <v>4.99</v>
       </c>
       <c r="K117" s="13" t="inlineStr">
         <is>
@@ -6141,40 +6141,40 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="C118" s="18" t="inlineStr">
         <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
+          <t>G3 · PV_SUB  (46 − 28)</t>
         </is>
       </c>
       <c r="D118" s="16" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E118" s="17" t="inlineStr">
         <is>
-          <t>vo_p1_sub</t>
+          <t>vo_g3_correct_late</t>
         </is>
       </c>
       <c r="F118" s="19" t="inlineStr">
         <is>
-          <t>और अब इसमें से 58 घटाते हैं।</t>
+          <t>46 घटा 28 बराबर 18।</t>
         </is>
       </c>
       <c r="G118" s="18" t="inlineStr">
         <is>
-          <t>what is taken away</t>
+          <t>correct answer after a wrong one</t>
         </is>
       </c>
       <c r="H118" s="18" t="inlineStr">
         <is>
-          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
+          <t>the same as the correct line, without «शाबाश» (only a first-try answer gets it)</t>
         </is>
       </c>
       <c r="I118" s="18" t="inlineStr"/>
       <c r="J118" s="16" t="n">
-        <v>3.69</v>
+        <v>3.78</v>
       </c>
       <c r="K118" s="17" t="inlineStr">
         <is>
@@ -6183,53 +6183,49 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="12" t="n">
+      <c r="A119" s="8" t="n">
         <v>115</v>
       </c>
-      <c r="B119" s="13" t="inlineStr">
-        <is>
-          <t>Page 8</t>
-        </is>
-      </c>
-      <c r="C119" s="14" t="inlineStr">
-        <is>
-          <t>P1 · PV_SUB  (74 − 58)</t>
-        </is>
-      </c>
-      <c r="D119" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E119" s="13" t="inlineStr">
-        <is>
-          <t>vo_idle_open</t>
-        </is>
-      </c>
-      <c r="F119" s="15" t="inlineStr">
-        <is>
-          <t>अब 1 दहाई को इकाई में लाइए।</t>
-        </is>
-      </c>
-      <c r="G119" s="14" t="inlineStr">
-        <is>
-          <t>inactivity reminder - open a ten</t>
-        </is>
-      </c>
-      <c r="H119" s="14" t="inlineStr">
-        <is>
-          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
-        </is>
-      </c>
-      <c r="I119" s="14" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 7, Page 9</t>
-        </is>
-      </c>
-      <c r="J119" s="12" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="K119" s="13" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
+      <c r="B119" s="9" t="inlineStr">
+        <is>
+          <t>Transition 3</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>before page 8</t>
+        </is>
+      </c>
+      <c r="D119" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E119" s="9" t="inlineStr">
+        <is>
+          <t>vo_pt_practice</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>वाह! अब आपकी बारी।</t>
+        </is>
+      </c>
+      <c r="G119" s="10" t="inlineStr">
+        <is>
+          <t>transition line</t>
+        </is>
+      </c>
+      <c r="H119" s="10" t="inlineStr">
+        <is>
+          <t>Swiftee rises talking; «अब आपकी बारी!» wipes in as it is said</t>
+        </is>
+      </c>
+      <c r="I119" s="10" t="inlineStr"/>
+      <c r="J119" s="8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="K119" s="9" t="inlineStr">
+        <is>
+          <t>Copied (HI02H11, recorded voice)</t>
         </is>
       </c>
     </row>
@@ -6248,31 +6244,31 @@
         </is>
       </c>
       <c r="D120" s="16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t>vo_p1_rm_ones</t>
+          <t>vo_p1_prompt</t>
         </is>
       </c>
       <c r="F120" s="19" t="inlineStr">
         <is>
-          <t>14 इकाई में से 8 इकाई हटाइए।</t>
+          <t>74 में से 58 घटाइए।</t>
         </is>
       </c>
       <c r="G120" s="18" t="inlineStr">
         <is>
-          <t>take-away step - the ones</t>
+          <t>page instruction</t>
         </is>
       </c>
       <c r="H120" s="18" t="inlineStr">
         <is>
-          <t>after the ten is opened; the ones column beats on «इकाई»</t>
+          <t>as the page opens (the speaker replays it)</t>
         </is>
       </c>
       <c r="I120" s="18" t="inlineStr"/>
       <c r="J120" s="16" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="K120" s="17" t="inlineStr">
         <is>
@@ -6295,31 +6291,31 @@
         </is>
       </c>
       <c r="D121" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>vo_p1_rm_tens</t>
+          <t>vo_p1_sub</t>
         </is>
       </c>
       <c r="F121" s="15" t="inlineStr">
         <is>
-          <t>अब दहाइयाँ घटाइए।</t>
+          <t>और अब इसमें से 58 घटाते हैं।</t>
         </is>
       </c>
       <c r="G121" s="14" t="inlineStr">
         <is>
-          <t>take-away step - the tens</t>
+          <t>what is taken away</t>
         </is>
       </c>
       <c r="H121" s="14" t="inlineStr">
         <is>
-          <t>when the ones are done; the tens column beats</t>
+          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
         </is>
       </c>
       <c r="I121" s="14" t="inlineStr"/>
       <c r="J121" s="12" t="n">
-        <v>2.63</v>
+        <v>3.69</v>
       </c>
       <c r="K121" s="13" t="inlineStr">
         <is>
@@ -6342,35 +6338,35 @@
         </is>
       </c>
       <c r="D122" s="16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E122" s="17" t="inlineStr">
         <is>
-          <t>vo_idle_rm_o</t>
+          <t>vo_idle_open</t>
         </is>
       </c>
       <c r="F122" s="19" t="inlineStr">
         <is>
-          <t>अब इकाई हटाइए।</t>
+          <t>अब 1 दहाई को इकाई में लाइए।</t>
         </is>
       </c>
       <c r="G122" s="18" t="inlineStr">
         <is>
-          <t>inactivity reminder - taking away</t>
+          <t>inactivity reminder - open a ten</t>
         </is>
       </c>
       <c r="H122" s="18" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
+          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
         </is>
       </c>
       <c r="I122" s="18" t="inlineStr">
         <is>
-          <t>Page 4, Page 5, Page 6, Page 7, Page 9</t>
+          <t>Page 5, Page 6, Page 7, Page 9</t>
         </is>
       </c>
       <c r="J122" s="16" t="n">
-        <v>2.21</v>
+        <v>3.16</v>
       </c>
       <c r="K122" s="17" t="inlineStr">
         <is>
@@ -6393,35 +6389,31 @@
         </is>
       </c>
       <c r="D123" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E123" s="13" t="inlineStr">
         <is>
-          <t>vo_idle_rm_t</t>
+          <t>vo_p1_rm_ones</t>
         </is>
       </c>
       <c r="F123" s="15" t="inlineStr">
         <is>
-          <t>अब दहाई हटाइए।</t>
+          <t>14 इकाई में से 8 इकाई हटाइए।</t>
         </is>
       </c>
       <c r="G123" s="14" t="inlineStr">
         <is>
-          <t>inactivity reminder - taking away</t>
+          <t>take-away step - the ones</t>
         </is>
       </c>
       <c r="H123" s="14" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I123" s="14" t="inlineStr">
-        <is>
-          <t>Page 4, Page 5, Page 6, Page 7, Page 9</t>
-        </is>
-      </c>
+          <t>after the ten is opened; the ones column beats on «इकाई»</t>
+        </is>
+      </c>
+      <c r="I123" s="14" t="inlineStr"/>
       <c r="J123" s="12" t="n">
-        <v>2.27</v>
+        <v>3.33</v>
       </c>
       <c r="K123" s="13" t="inlineStr">
         <is>
@@ -6444,35 +6436,31 @@
         </is>
       </c>
       <c r="D124" s="16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E124" s="17" t="inlineStr">
         <is>
-          <t>vo_rm_tens_more</t>
+          <t>vo_p1_rm_tens</t>
         </is>
       </c>
       <c r="F124" s="19" t="inlineStr">
         <is>
-          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
+          <t>अब दहाइयाँ घटाइए।</t>
         </is>
       </c>
       <c r="G124" s="18" t="inlineStr">
         <is>
-          <t>take-away mistake - 1st time</t>
+          <t>take-away step - the tens</t>
         </is>
       </c>
       <c r="H124" s="18" t="inlineStr">
         <is>
-          <t>a ten too many taken: the tens go back, this line</t>
-        </is>
-      </c>
-      <c r="I124" s="18" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 7, Page 9</t>
-        </is>
-      </c>
+          <t>when the ones are done; the tens column beats</t>
+        </is>
+      </c>
+      <c r="I124" s="18" t="inlineStr"/>
       <c r="J124" s="16" t="n">
-        <v>4.05</v>
+        <v>2.63</v>
       </c>
       <c r="K124" s="17" t="inlineStr">
         <is>
@@ -6495,35 +6483,35 @@
         </is>
       </c>
       <c r="D125" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E125" s="13" t="inlineStr">
         <is>
-          <t>vo_rm_guide</t>
+          <t>vo_idle_rm_o</t>
         </is>
       </c>
       <c r="F125" s="15" t="inlineStr">
         <is>
-          <t>इनमें से इतने हटाइए।</t>
+          <t>अब इकाई हटाइए।</t>
         </is>
       </c>
       <c r="G125" s="14" t="inlineStr">
         <is>
-          <t>take-away mistake - 2nd time</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H125" s="14" t="inlineStr">
         <is>
-          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
         </is>
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>Page 5, Page 6, Page 7, Page 9</t>
+          <t>Page 4, Page 5, Page 6, Page 7, Page 9</t>
         </is>
       </c>
       <c r="J125" s="12" t="n">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="K125" s="13" t="inlineStr">
         <is>
@@ -6546,35 +6534,35 @@
         </is>
       </c>
       <c r="D126" s="16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E126" s="17" t="inlineStr">
         <is>
-          <t>vo_p1_ask</t>
+          <t>vo_idle_rm_t</t>
         </is>
       </c>
       <c r="F126" s="19" t="inlineStr">
         <is>
-          <t>अब कितने बचे? नीचे डिब्बे पर टैप करके सही संख्या लिखिए।</t>
+          <t>अब दहाई हटाइए।</t>
         </is>
       </c>
       <c r="G126" s="18" t="inlineStr">
         <is>
-          <t>the answer question</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H126" s="18" t="inlineStr">
         <is>
-          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
         </is>
       </c>
       <c r="I126" s="18" t="inlineStr">
         <is>
-          <t>Page 9</t>
+          <t>Page 4, Page 5, Page 6, Page 7, Page 9</t>
         </is>
       </c>
       <c r="J126" s="16" t="n">
-        <v>4.39</v>
+        <v>2.27</v>
       </c>
       <c r="K126" s="17" t="inlineStr">
         <is>
@@ -6597,26 +6585,26 @@
         </is>
       </c>
       <c r="D127" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>vo_h_recount</t>
+          <t>vo_rm_tens_more</t>
         </is>
       </c>
       <c r="F127" s="15" t="inlineStr">
         <is>
-          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
+          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
         </is>
       </c>
       <c r="G127" s="14" t="inlineStr">
         <is>
-          <t>Hint 1 (1st wrong answer)</t>
+          <t>take-away mistake - 1st time</t>
         </is>
       </c>
       <c r="H127" s="14" t="inlineStr">
         <is>
-          <t>the columns beat on «दहाई» / «इकाई»</t>
+          <t>a ten too many taken: the tens go back, this line</t>
         </is>
       </c>
       <c r="I127" s="14" t="inlineStr">
@@ -6625,7 +6613,7 @@
         </is>
       </c>
       <c r="J127" s="12" t="n">
-        <v>3.31</v>
+        <v>4.05</v>
       </c>
       <c r="K127" s="13" t="inlineStr">
         <is>
@@ -6648,31 +6636,35 @@
         </is>
       </c>
       <c r="D128" s="16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E128" s="17" t="inlineStr">
         <is>
-          <t>vo_p1_h2</t>
+          <t>vo_rm_guide</t>
         </is>
       </c>
       <c r="F128" s="19" t="inlineStr">
         <is>
-          <t>74 में से 58 घटाने पर, 1 दहाई और 6 इकाई बचती हैं।</t>
+          <t>इनमें से इतने हटाइए।</t>
         </is>
       </c>
       <c r="G128" s="18" t="inlineStr">
         <is>
-          <t>Hint 2 (2nd wrong answer)</t>
+          <t>take-away mistake - 2nd time</t>
         </is>
       </c>
       <c r="H128" s="18" t="inlineStr">
         <is>
-          <t>the numbers light; the tens and ones left beat on their words</t>
-        </is>
-      </c>
-      <c r="I128" s="18" t="inlineStr"/>
+          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
+        </is>
+      </c>
+      <c r="I128" s="18" t="inlineStr">
+        <is>
+          <t>Page 5, Page 6, Page 7, Page 9</t>
+        </is>
+      </c>
       <c r="J128" s="16" t="n">
-        <v>5.45</v>
+        <v>2.09</v>
       </c>
       <c r="K128" s="17" t="inlineStr">
         <is>
@@ -6695,31 +6687,35 @@
         </is>
       </c>
       <c r="D129" s="12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>vo_p1_reveal</t>
+          <t>vo_p1_ask</t>
         </is>
       </c>
       <c r="F129" s="15" t="inlineStr">
         <is>
-          <t>74 में से 58 घटाने पर 16 बचता है। तो सही संख्या यह है।</t>
+          <t>अब कितने बचे? नीचे डिब्बे पर टैप करके सही संख्या लिखिए।</t>
         </is>
       </c>
       <c r="G129" s="14" t="inlineStr">
         <is>
-          <t>Hint 3 (3rd wrong answer)</t>
+          <t>the answer question</t>
         </is>
       </c>
       <c r="H129" s="14" t="inlineStr">
         <is>
-          <t>the right card / the right keys lit (one key at a time), the others off</t>
-        </is>
-      </c>
-      <c r="I129" s="14" t="inlineStr"/>
+          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
+        </is>
+      </c>
+      <c r="I129" s="14" t="inlineStr">
+        <is>
+          <t>Page 9</t>
+        </is>
+      </c>
       <c r="J129" s="12" t="n">
-        <v>5.69</v>
+        <v>4.39</v>
       </c>
       <c r="K129" s="13" t="inlineStr">
         <is>
@@ -6742,31 +6738,35 @@
         </is>
       </c>
       <c r="D130" s="16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E130" s="17" t="inlineStr">
         <is>
-          <t>vo_p1_correct</t>
+          <t>vo_h_recount</t>
         </is>
       </c>
       <c r="F130" s="19" t="inlineStr">
         <is>
-          <t>शाबाश! 74 में से 58 घटाने पर हमें मिला 16।</t>
+          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
         </is>
       </c>
       <c r="G130" s="18" t="inlineStr">
         <is>
-          <t>correct answer</t>
+          <t>Hint 1 (1st wrong answer)</t>
         </is>
       </c>
       <c r="H130" s="18" t="inlineStr">
         <is>
-          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
-        </is>
-      </c>
-      <c r="I130" s="18" t="inlineStr"/>
+          <t>the columns beat on «दहाई» / «इकाई»</t>
+        </is>
+      </c>
+      <c r="I130" s="18" t="inlineStr">
+        <is>
+          <t>Page 5, Page 6, Page 7, Page 9</t>
+        </is>
+      </c>
       <c r="J130" s="16" t="n">
-        <v>5.01</v>
+        <v>3.31</v>
       </c>
       <c r="K130" s="17" t="inlineStr">
         <is>
@@ -6780,40 +6780,40 @@
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>Page 9</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C131" s="14" t="inlineStr">
         <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D131" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
-          <t>vo_p2_prompt</t>
+          <t>vo_p1_h2</t>
         </is>
       </c>
       <c r="F131" s="15" t="inlineStr">
         <is>
-          <t>61 में से 35 घटाइए।</t>
+          <t>74 में से 58 घटाने पर, 1 दहाई और 6 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="G131" s="14" t="inlineStr">
         <is>
-          <t>page instruction</t>
+          <t>Hint 2 (2nd wrong answer)</t>
         </is>
       </c>
       <c r="H131" s="14" t="inlineStr">
         <is>
-          <t>as the page opens (the speaker replays it)</t>
+          <t>the numbers light; the tens and ones left beat on their words</t>
         </is>
       </c>
       <c r="I131" s="14" t="inlineStr"/>
       <c r="J131" s="12" t="n">
-        <v>2.48</v>
+        <v>5.45</v>
       </c>
       <c r="K131" s="13" t="inlineStr">
         <is>
@@ -6827,40 +6827,40 @@
       </c>
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>Page 9</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C132" s="18" t="inlineStr">
         <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D132" s="16" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E132" s="17" t="inlineStr">
         <is>
-          <t>vo_p2_sub</t>
+          <t>vo_p1_reveal</t>
         </is>
       </c>
       <c r="F132" s="19" t="inlineStr">
         <is>
-          <t>और अब इसमें से 35 घटाते हैं।</t>
+          <t>74 में से 58 घटाने पर 16 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="G132" s="18" t="inlineStr">
         <is>
-          <t>what is taken away</t>
+          <t>Hint 3 (3rd wrong answer)</t>
         </is>
       </c>
       <c r="H132" s="18" t="inlineStr">
         <is>
-          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
+          <t>the right card / the right keys lit (one key at a time), the others off</t>
         </is>
       </c>
       <c r="I132" s="18" t="inlineStr"/>
       <c r="J132" s="16" t="n">
-        <v>2.86</v>
+        <v>5.69</v>
       </c>
       <c r="K132" s="17" t="inlineStr">
         <is>
@@ -6874,44 +6874,40 @@
       </c>
       <c r="B133" s="13" t="inlineStr">
         <is>
-          <t>Page 9</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C133" s="14" t="inlineStr">
         <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D133" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
-          <t>vo_idle_open</t>
+          <t>vo_p1_correct</t>
         </is>
       </c>
       <c r="F133" s="15" t="inlineStr">
         <is>
-          <t>अब 1 दहाई को इकाई में लाइए।</t>
+          <t>शाबाश! 74 में से 58 घटाने पर हमें मिला 16।</t>
         </is>
       </c>
       <c r="G133" s="14" t="inlineStr">
         <is>
-          <t>inactivity reminder - open a ten</t>
+          <t>correct answer</t>
         </is>
       </c>
       <c r="H133" s="14" t="inlineStr">
         <is>
-          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
-        </is>
-      </c>
-      <c r="I133" s="14" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 7, Page 8</t>
-        </is>
-      </c>
+          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
+        </is>
+      </c>
+      <c r="I133" s="14" t="inlineStr"/>
       <c r="J133" s="12" t="n">
-        <v>3.16</v>
+        <v>5.01</v>
       </c>
       <c r="K133" s="13" t="inlineStr">
         <is>
@@ -6925,40 +6921,40 @@
       </c>
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>Page 9</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="C134" s="18" t="inlineStr">
         <is>
-          <t>P2 · PV_SUB  (61 − 35)</t>
+          <t>P1 · PV_SUB  (74 − 58)</t>
         </is>
       </c>
       <c r="D134" s="16" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E134" s="17" t="inlineStr">
         <is>
-          <t>vo_p2_rm_ones</t>
+          <t>vo_p1_correct_late</t>
         </is>
       </c>
       <c r="F134" s="19" t="inlineStr">
         <is>
-          <t>इकाई हटाइए।</t>
+          <t>74 में से 58 घटाने पर हमें मिला 16।</t>
         </is>
       </c>
       <c r="G134" s="18" t="inlineStr">
         <is>
-          <t>take-away step - the ones</t>
+          <t>correct answer after a wrong one</t>
         </is>
       </c>
       <c r="H134" s="18" t="inlineStr">
         <is>
-          <t>after the ten is opened; the ones column beats on «इकाई»</t>
+          <t>the same as the correct line, without «शाबाश» (only a first-try answer gets it)</t>
         </is>
       </c>
       <c r="I134" s="18" t="inlineStr"/>
       <c r="J134" s="16" t="n">
-        <v>1.81</v>
+        <v>3.93</v>
       </c>
       <c r="K134" s="17" t="inlineStr">
         <is>
@@ -6981,31 +6977,31 @@
         </is>
       </c>
       <c r="D135" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>
-          <t>vo_p2_rm_tens</t>
+          <t>vo_p2_prompt</t>
         </is>
       </c>
       <c r="F135" s="15" t="inlineStr">
         <is>
-          <t>अब दहाइयाँ हटाइए।</t>
+          <t>61 में से 35 घटाइए।</t>
         </is>
       </c>
       <c r="G135" s="14" t="inlineStr">
         <is>
-          <t>take-away step - the tens</t>
+          <t>page instruction</t>
         </is>
       </c>
       <c r="H135" s="14" t="inlineStr">
         <is>
-          <t>when the ones are done; the tens column beats</t>
+          <t>as the page opens (the speaker replays it)</t>
         </is>
       </c>
       <c r="I135" s="14" t="inlineStr"/>
       <c r="J135" s="12" t="n">
-        <v>1.95</v>
+        <v>2.48</v>
       </c>
       <c r="K135" s="13" t="inlineStr">
         <is>
@@ -7028,35 +7024,31 @@
         </is>
       </c>
       <c r="D136" s="16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E136" s="17" t="inlineStr">
         <is>
-          <t>vo_idle_rm_o</t>
+          <t>vo_p2_sub</t>
         </is>
       </c>
       <c r="F136" s="19" t="inlineStr">
         <is>
-          <t>अब इकाई हटाइए।</t>
+          <t>और अब इसमें से 35 घटाते हैं।</t>
         </is>
       </c>
       <c r="G136" s="18" t="inlineStr">
         <is>
-          <t>inactivity reminder - taking away</t>
+          <t>what is taken away</t>
         </is>
       </c>
       <c r="H136" s="18" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
-        </is>
-      </c>
-      <c r="I136" s="18" t="inlineStr">
-        <is>
-          <t>Page 4, Page 5, Page 6, Page 7, Page 8</t>
-        </is>
-      </c>
+          <t>after the build: the number pops, its digits light on «… दहाई» / «… इकाई»; on «इसमें» the whole table lights</t>
+        </is>
+      </c>
+      <c r="I136" s="18" t="inlineStr"/>
       <c r="J136" s="16" t="n">
-        <v>2.21</v>
+        <v>2.86</v>
       </c>
       <c r="K136" s="17" t="inlineStr">
         <is>
@@ -7079,35 +7071,35 @@
         </is>
       </c>
       <c r="D137" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E137" s="13" t="inlineStr">
         <is>
-          <t>vo_idle_rm_t</t>
+          <t>vo_idle_open</t>
         </is>
       </c>
       <c r="F137" s="15" t="inlineStr">
         <is>
-          <t>अब दहाई हटाइए।</t>
+          <t>अब 1 दहाई को इकाई में लाइए।</t>
         </is>
       </c>
       <c r="G137" s="14" t="inlineStr">
         <is>
-          <t>inactivity reminder - taking away</t>
+          <t>inactivity reminder - open a ten</t>
         </is>
       </c>
       <c r="H137" s="14" t="inlineStr">
         <is>
-          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
+          <t>the rods pulse until the child taps one; after 7s with no tap this line, again every 7s</t>
         </is>
       </c>
       <c r="I137" s="14" t="inlineStr">
         <is>
-          <t>Page 4, Page 5, Page 6, Page 7, Page 8</t>
+          <t>Page 5, Page 6, Page 7, Page 8</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
-        <v>2.27</v>
+        <v>3.16</v>
       </c>
       <c r="K137" s="13" t="inlineStr">
         <is>
@@ -7130,35 +7122,31 @@
         </is>
       </c>
       <c r="D138" s="16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E138" s="17" t="inlineStr">
         <is>
-          <t>vo_rm_tens_more</t>
+          <t>vo_p2_rm_ones</t>
         </is>
       </c>
       <c r="F138" s="19" t="inlineStr">
         <is>
-          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
+          <t>इकाई हटाइए।</t>
         </is>
       </c>
       <c r="G138" s="18" t="inlineStr">
         <is>
-          <t>take-away mistake - 1st time</t>
+          <t>take-away step - the ones</t>
         </is>
       </c>
       <c r="H138" s="18" t="inlineStr">
         <is>
-          <t>a ten too many taken: the tens go back, this line</t>
-        </is>
-      </c>
-      <c r="I138" s="18" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 7, Page 8</t>
-        </is>
-      </c>
+          <t>after the ten is opened; the ones column beats on «इकाई»</t>
+        </is>
+      </c>
+      <c r="I138" s="18" t="inlineStr"/>
       <c r="J138" s="16" t="n">
-        <v>4.05</v>
+        <v>1.81</v>
       </c>
       <c r="K138" s="17" t="inlineStr">
         <is>
@@ -7181,35 +7169,31 @@
         </is>
       </c>
       <c r="D139" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>vo_rm_guide</t>
+          <t>vo_p2_rm_tens</t>
         </is>
       </c>
       <c r="F139" s="15" t="inlineStr">
         <is>
-          <t>इनमें से इतने हटाइए।</t>
+          <t>अब दहाइयाँ हटाइए।</t>
         </is>
       </c>
       <c r="G139" s="14" t="inlineStr">
         <is>
-          <t>take-away mistake - 2nd time</t>
+          <t>take-away step - the tens</t>
         </is>
       </c>
       <c r="H139" s="14" t="inlineStr">
         <is>
-          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
-        </is>
-      </c>
-      <c r="I139" s="14" t="inlineStr">
-        <is>
-          <t>Page 5, Page 6, Page 7, Page 8</t>
-        </is>
-      </c>
+          <t>when the ones are done; the tens column beats</t>
+        </is>
+      </c>
+      <c r="I139" s="14" t="inlineStr"/>
       <c r="J139" s="12" t="n">
-        <v>2.09</v>
+        <v>1.95</v>
       </c>
       <c r="K139" s="13" t="inlineStr">
         <is>
@@ -7232,35 +7216,35 @@
         </is>
       </c>
       <c r="D140" s="16" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E140" s="17" t="inlineStr">
         <is>
-          <t>vo_p1_ask</t>
+          <t>vo_idle_rm_o</t>
         </is>
       </c>
       <c r="F140" s="19" t="inlineStr">
         <is>
-          <t>अब कितने बचे? नीचे डिब्बे पर टैप करके सही संख्या लिखिए।</t>
+          <t>अब इकाई हटाइए।</t>
         </is>
       </c>
       <c r="G140" s="18" t="inlineStr">
         <is>
-          <t>the answer question</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H140" s="18" t="inlineStr">
         <is>
-          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
         </is>
       </c>
       <c r="I140" s="18" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 4, Page 5, Page 6, Page 7, Page 8</t>
         </is>
       </c>
       <c r="J140" s="16" t="n">
-        <v>4.39</v>
+        <v>2.21</v>
       </c>
       <c r="K140" s="17" t="inlineStr">
         <is>
@@ -7283,35 +7267,35 @@
         </is>
       </c>
       <c r="D141" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E141" s="13" t="inlineStr">
         <is>
-          <t>vo_h_recount</t>
+          <t>vo_idle_rm_t</t>
         </is>
       </c>
       <c r="F141" s="15" t="inlineStr">
         <is>
-          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
+          <t>अब दहाई हटाइए।</t>
         </is>
       </c>
       <c r="G141" s="14" t="inlineStr">
         <is>
-          <t>Hint 1 (1st wrong answer)</t>
+          <t>inactivity reminder - taking away</t>
         </is>
       </c>
       <c r="H141" s="14" t="inlineStr">
         <is>
-          <t>the columns beat on «दहाई» / «इकाई»</t>
+          <t>after 7s with no tap at the take-away step, again every 7s while idle</t>
         </is>
       </c>
       <c r="I141" s="14" t="inlineStr">
         <is>
-          <t>Page 5, Page 6, Page 7, Page 8</t>
+          <t>Page 4, Page 5, Page 6, Page 7, Page 8</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
-        <v>3.31</v>
+        <v>2.27</v>
       </c>
       <c r="K141" s="13" t="inlineStr">
         <is>
@@ -7334,31 +7318,35 @@
         </is>
       </c>
       <c r="D142" s="16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E142" s="17" t="inlineStr">
         <is>
-          <t>vo_p2_h2</t>
+          <t>vo_rm_tens_more</t>
         </is>
       </c>
       <c r="F142" s="19" t="inlineStr">
         <is>
-          <t>61 में से 35 घटाने पर, 2 दहाई और 6 इकाई बचती हैं।</t>
+          <t>आपने दहाई में ज़्यादा हटाए हैं। दोबारा कोशिश करिए।</t>
         </is>
       </c>
       <c r="G142" s="18" t="inlineStr">
         <is>
-          <t>Hint 2 (2nd wrong answer)</t>
+          <t>take-away mistake - 1st time</t>
         </is>
       </c>
       <c r="H142" s="18" t="inlineStr">
         <is>
-          <t>the numbers light; the tens and ones left beat on their words</t>
-        </is>
-      </c>
-      <c r="I142" s="18" t="inlineStr"/>
+          <t>a ten too many taken: the tens go back, this line</t>
+        </is>
+      </c>
+      <c r="I142" s="18" t="inlineStr">
+        <is>
+          <t>Page 5, Page 6, Page 7, Page 8</t>
+        </is>
+      </c>
       <c r="J142" s="16" t="n">
-        <v>5.81</v>
+        <v>4.05</v>
       </c>
       <c r="K142" s="17" t="inlineStr">
         <is>
@@ -7381,31 +7369,35 @@
         </is>
       </c>
       <c r="D143" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E143" s="13" t="inlineStr">
         <is>
-          <t>vo_p2_reveal</t>
+          <t>vo_rm_guide</t>
         </is>
       </c>
       <c r="F143" s="15" t="inlineStr">
         <is>
-          <t>61 में से 35 घटाने पर 26 बचता है। तो सही संख्या यह है।</t>
+          <t>इनमें से इतने हटाइए।</t>
         </is>
       </c>
       <c r="G143" s="14" t="inlineStr">
         <is>
-          <t>Hint 3 (3rd wrong answer)</t>
+          <t>take-away mistake - 2nd time</t>
         </is>
       </c>
       <c r="H143" s="14" t="inlineStr">
         <is>
-          <t>the right card / the right keys lit (one key at a time), the others off</t>
-        </is>
-      </c>
-      <c r="I143" s="14" t="inlineStr"/>
+          <t>the tens go back; only the tens to take stay live, the others dimmed</t>
+        </is>
+      </c>
+      <c r="I143" s="14" t="inlineStr">
+        <is>
+          <t>Page 5, Page 6, Page 7, Page 8</t>
+        </is>
+      </c>
       <c r="J143" s="12" t="n">
-        <v>4.64</v>
+        <v>2.09</v>
       </c>
       <c r="K143" s="13" t="inlineStr">
         <is>
@@ -7428,31 +7420,35 @@
         </is>
       </c>
       <c r="D144" s="16" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E144" s="17" t="inlineStr">
         <is>
-          <t>vo_p2_correct</t>
+          <t>vo_p1_ask</t>
         </is>
       </c>
       <c r="F144" s="19" t="inlineStr">
         <is>
-          <t>शाबाश! 61 में से 35 घटाने पर हमें मिला 26।</t>
+          <t>अब कितने बचे? नीचे डिब्बे पर टैप करके सही संख्या लिखिए।</t>
         </is>
       </c>
       <c r="G144" s="18" t="inlineStr">
         <is>
-          <t>correct answer</t>
+          <t>the answer question</t>
         </is>
       </c>
       <c r="H144" s="18" t="inlineStr">
         <is>
-          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
-        </is>
-      </c>
-      <c r="I144" s="18" t="inlineStr"/>
+          <t>when the take-away is done; the cards / the keypad come in (said again after 7s idle)</t>
+        </is>
+      </c>
+      <c r="I144" s="18" t="inlineStr">
+        <is>
+          <t>Page 8</t>
+        </is>
+      </c>
       <c r="J144" s="16" t="n">
-        <v>5.21</v>
+        <v>4.39</v>
       </c>
       <c r="K144" s="17" t="inlineStr">
         <is>
@@ -7466,40 +7462,44 @@
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>Page 10</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C145" s="14" t="inlineStr">
         <is>
-          <t>P3 · MENTAL_SUB  (84 − 46)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D145" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E145" s="13" t="inlineStr">
         <is>
-          <t>vo_p3_prompt</t>
+          <t>vo_h_recount</t>
         </is>
       </c>
       <c r="F145" s="15" t="inlineStr">
         <is>
-          <t>84 में से 46 घटाइए और सही संख्या चुनिए।</t>
+          <t>बची हुई दहाई और इकाई को दोबारा गिनिए।</t>
         </is>
       </c>
       <c r="G145" s="14" t="inlineStr">
         <is>
-          <t>page instruction</t>
+          <t>Hint 1 (1st wrong answer)</t>
         </is>
       </c>
       <c r="H145" s="14" t="inlineStr">
         <is>
-          <t>as the page opens (the speaker replays it)</t>
-        </is>
-      </c>
-      <c r="I145" s="14" t="inlineStr"/>
+          <t>the columns beat on «दहाई» / «इकाई»</t>
+        </is>
+      </c>
+      <c r="I145" s="14" t="inlineStr">
+        <is>
+          <t>Page 5, Page 6, Page 7, Page 8</t>
+        </is>
+      </c>
       <c r="J145" s="12" t="n">
-        <v>4.51</v>
+        <v>3.31</v>
       </c>
       <c r="K145" s="13" t="inlineStr">
         <is>
@@ -7513,44 +7513,40 @@
       </c>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>Page 10</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C146" s="18" t="inlineStr">
         <is>
-          <t>P3 · MENTAL_SUB  (84 − 46)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D146" s="16" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E146" s="17" t="inlineStr">
         <is>
-          <t>vo_h_order</t>
+          <t>vo_p2_h2</t>
         </is>
       </c>
       <c r="F146" s="19" t="inlineStr">
         <is>
-          <t>संख्याओं में से पहले इकाई घटाइए, फिर दहाई घटाइए।</t>
+          <t>61 में से 35 घटाने पर, 2 दहाई और 6 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="G146" s="18" t="inlineStr">
         <is>
-          <t>Hint 1 (1st wrong answer)</t>
+          <t>Hint 2 (2nd wrong answer)</t>
         </is>
       </c>
       <c r="H146" s="18" t="inlineStr">
         <is>
-          <t>the ones digits light on «इकाई», the tens digits on «दहाई»</t>
-        </is>
-      </c>
-      <c r="I146" s="18" t="inlineStr">
-        <is>
-          <t>Page 11</t>
-        </is>
-      </c>
+          <t>the numbers light; the tens and ones left beat on their words</t>
+        </is>
+      </c>
+      <c r="I146" s="18" t="inlineStr"/>
       <c r="J146" s="16" t="n">
-        <v>4.45</v>
+        <v>5.81</v>
       </c>
       <c r="K146" s="17" t="inlineStr">
         <is>
@@ -7564,40 +7560,40 @@
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>Page 10</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C147" s="14" t="inlineStr">
         <is>
-          <t>P3 · MENTAL_SUB  (84 − 46)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D147" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>vo_p3_h2</t>
+          <t>vo_p2_reveal</t>
         </is>
       </c>
       <c r="F147" s="15" t="inlineStr">
         <is>
-          <t>84 में से 46 घटाने पर, 3 दहाई और 8 इकाई बचती हैं।</t>
+          <t>61 में से 35 घटाने पर 26 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="G147" s="14" t="inlineStr">
         <is>
-          <t>Hint 2 (2nd wrong answer)</t>
+          <t>Hint 3 (3rd wrong answer)</t>
         </is>
       </c>
       <c r="H147" s="14" t="inlineStr">
         <is>
-          <t>the table comes in with the first number's blocks; the second number is taken away as it is said</t>
+          <t>the right card / the right keys lit (one key at a time), the others off</t>
         </is>
       </c>
       <c r="I147" s="14" t="inlineStr"/>
       <c r="J147" s="12" t="n">
-        <v>5.47</v>
+        <v>4.64</v>
       </c>
       <c r="K147" s="13" t="inlineStr">
         <is>
@@ -7611,40 +7607,40 @@
       </c>
       <c r="B148" s="17" t="inlineStr">
         <is>
-          <t>Page 10</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C148" s="18" t="inlineStr">
         <is>
-          <t>P3 · MENTAL_SUB  (84 − 46)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D148" s="16" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E148" s="17" t="inlineStr">
         <is>
-          <t>vo_p3_reveal</t>
+          <t>vo_p2_correct</t>
         </is>
       </c>
       <c r="F148" s="19" t="inlineStr">
         <is>
-          <t>84 में से 46 घटाने पर 38 बचता है। तो सही संख्या यह है।</t>
+          <t>शाबाश! 61 में से 35 घटाने पर हमें मिला 26।</t>
         </is>
       </c>
       <c r="G148" s="18" t="inlineStr">
         <is>
-          <t>Hint 3 (3rd wrong answer)</t>
+          <t>correct answer</t>
         </is>
       </c>
       <c r="H148" s="18" t="inlineStr">
         <is>
-          <t>the right card / the right keys lit (one key at a time), the others off</t>
+          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
         </is>
       </c>
       <c r="I148" s="18" t="inlineStr"/>
       <c r="J148" s="16" t="n">
-        <v>5.52</v>
+        <v>5.21</v>
       </c>
       <c r="K148" s="17" t="inlineStr">
         <is>
@@ -7658,40 +7654,40 @@
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>Page 10</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="C149" s="14" t="inlineStr">
         <is>
-          <t>P3 · MENTAL_SUB  (84 − 46)</t>
+          <t>P2 · PV_SUB  (61 − 35)</t>
         </is>
       </c>
       <c r="D149" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>vo_p3_correct</t>
+          <t>vo_p2_correct_late</t>
         </is>
       </c>
       <c r="F149" s="15" t="inlineStr">
         <is>
-          <t>शाबाश! आपने सही संख्या चुन ली। 84 घटा 46 बराबर 38।</t>
+          <t>61 में से 35 घटाने पर हमें मिला 26।</t>
         </is>
       </c>
       <c r="G149" s="14" t="inlineStr">
         <is>
-          <t>correct answer</t>
+          <t>correct answer after a wrong one</t>
         </is>
       </c>
       <c r="H149" s="14" t="inlineStr">
         <is>
-          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
+          <t>the same as the correct line, without «शाबाश» (only a first-try answer gets it)</t>
         </is>
       </c>
       <c r="I149" s="14" t="inlineStr"/>
       <c r="J149" s="12" t="n">
-        <v>6.91</v>
+        <v>3.94</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -7705,12 +7701,12 @@
       </c>
       <c r="B150" s="17" t="inlineStr">
         <is>
-          <t>Page 11</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="C150" s="18" t="inlineStr">
         <is>
-          <t>P4 · MENTAL_SUB  (91 − 14)</t>
+          <t>P3 · MENTAL_SUB  (84 − 46)</t>
         </is>
       </c>
       <c r="D150" s="16" t="n">
@@ -7718,12 +7714,12 @@
       </c>
       <c r="E150" s="17" t="inlineStr">
         <is>
-          <t>vo_p4_prompt</t>
+          <t>vo_p3_prompt</t>
         </is>
       </c>
       <c r="F150" s="19" t="inlineStr">
         <is>
-          <t>91 में से 14 घटाइए और सही संख्या चुनिए।</t>
+          <t>84 में से 46 घटाइए और सही संख्या चुनिए।</t>
         </is>
       </c>
       <c r="G150" s="18" t="inlineStr">
@@ -7738,7 +7734,7 @@
       </c>
       <c r="I150" s="18" t="inlineStr"/>
       <c r="J150" s="16" t="n">
-        <v>3.57</v>
+        <v>4.51</v>
       </c>
       <c r="K150" s="17" t="inlineStr">
         <is>
@@ -7752,12 +7748,12 @@
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>Page 11</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="C151" s="14" t="inlineStr">
         <is>
-          <t>P4 · MENTAL_SUB  (91 − 14)</t>
+          <t>P3 · MENTAL_SUB  (84 − 46)</t>
         </is>
       </c>
       <c r="D151" s="12" t="n">
@@ -7785,7 +7781,7 @@
       </c>
       <c r="I151" s="14" t="inlineStr">
         <is>
-          <t>Page 10</t>
+          <t>Page 11</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
@@ -7803,12 +7799,12 @@
       </c>
       <c r="B152" s="17" t="inlineStr">
         <is>
-          <t>Page 11</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="C152" s="18" t="inlineStr">
         <is>
-          <t>P4 · MENTAL_SUB  (91 − 14)</t>
+          <t>P3 · MENTAL_SUB  (84 − 46)</t>
         </is>
       </c>
       <c r="D152" s="16" t="n">
@@ -7816,12 +7812,12 @@
       </c>
       <c r="E152" s="17" t="inlineStr">
         <is>
-          <t>vo_p4_h2</t>
+          <t>vo_p3_h2</t>
         </is>
       </c>
       <c r="F152" s="19" t="inlineStr">
         <is>
-          <t>91 में से 14 घटाने पर, 7 दहाई और 7 इकाई बचती हैं।</t>
+          <t>84 में से 46 घटाने पर, 3 दहाई और 8 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="G152" s="18" t="inlineStr">
@@ -7836,7 +7832,7 @@
       </c>
       <c r="I152" s="18" t="inlineStr"/>
       <c r="J152" s="16" t="n">
-        <v>5.17</v>
+        <v>5.47</v>
       </c>
       <c r="K152" s="17" t="inlineStr">
         <is>
@@ -7850,12 +7846,12 @@
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>Page 11</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="C153" s="14" t="inlineStr">
         <is>
-          <t>P4 · MENTAL_SUB  (91 − 14)</t>
+          <t>P3 · MENTAL_SUB  (84 − 46)</t>
         </is>
       </c>
       <c r="D153" s="12" t="n">
@@ -7863,12 +7859,12 @@
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>vo_p4_reveal</t>
+          <t>vo_p3_reveal</t>
         </is>
       </c>
       <c r="F153" s="15" t="inlineStr">
         <is>
-          <t>91 में से 14 घटाने पर 77 बचता है। तो सही संख्या यह है।</t>
+          <t>84 में से 46 घटाने पर 38 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="G153" s="14" t="inlineStr">
@@ -7883,7 +7879,7 @@
       </c>
       <c r="I153" s="14" t="inlineStr"/>
       <c r="J153" s="12" t="n">
-        <v>6.49</v>
+        <v>5.52</v>
       </c>
       <c r="K153" s="13" t="inlineStr">
         <is>
@@ -7897,12 +7893,12 @@
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>Page 11</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="C154" s="18" t="inlineStr">
         <is>
-          <t>P4 · MENTAL_SUB  (91 − 14)</t>
+          <t>P3 · MENTAL_SUB  (84 − 46)</t>
         </is>
       </c>
       <c r="D154" s="16" t="n">
@@ -7910,12 +7906,12 @@
       </c>
       <c r="E154" s="17" t="inlineStr">
         <is>
-          <t>vo_p4_correct</t>
+          <t>vo_p3_correct</t>
         </is>
       </c>
       <c r="F154" s="19" t="inlineStr">
         <is>
-          <t>शाबाश! आपने सही संख्या चुन ली। 91 घटा 14 बराबर 77।</t>
+          <t>शाबाश! आपने सही संख्या चुन ली। 84 घटा 46 बराबर 38।</t>
         </is>
       </c>
       <c r="G154" s="18" t="inlineStr">
@@ -7930,56 +7926,389 @@
       </c>
       <c r="I154" s="18" t="inlineStr"/>
       <c r="J154" s="16" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="K154" s="17" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="12" t="n">
+        <v>151</v>
+      </c>
+      <c r="B155" s="13" t="inlineStr">
+        <is>
+          <t>Page 10</t>
+        </is>
+      </c>
+      <c r="C155" s="14" t="inlineStr">
+        <is>
+          <t>P3 · MENTAL_SUB  (84 − 46)</t>
+        </is>
+      </c>
+      <c r="D155" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E155" s="13" t="inlineStr">
+        <is>
+          <t>vo_p3_correct_late</t>
+        </is>
+      </c>
+      <c r="F155" s="15" t="inlineStr">
+        <is>
+          <t>आपने सही संख्या चुन ली। 84 घटा 46 बराबर 38।</t>
+        </is>
+      </c>
+      <c r="G155" s="14" t="inlineStr">
+        <is>
+          <t>correct answer after a wrong one</t>
+        </is>
+      </c>
+      <c r="H155" s="14" t="inlineStr">
+        <is>
+          <t>the same as the correct line, without «शाबाश» (only a first-try answer gets it)</t>
+        </is>
+      </c>
+      <c r="I155" s="14" t="inlineStr"/>
+      <c r="J155" s="12" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="K155" s="13" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="16" t="n">
+        <v>152</v>
+      </c>
+      <c r="B156" s="17" t="inlineStr">
+        <is>
+          <t>Page 11</t>
+        </is>
+      </c>
+      <c r="C156" s="18" t="inlineStr">
+        <is>
+          <t>P4 · MENTAL_SUB  (91 − 14)</t>
+        </is>
+      </c>
+      <c r="D156" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" s="17" t="inlineStr">
+        <is>
+          <t>vo_p4_prompt</t>
+        </is>
+      </c>
+      <c r="F156" s="19" t="inlineStr">
+        <is>
+          <t>91 में से 14 घटाइए और सही संख्या चुनिए।</t>
+        </is>
+      </c>
+      <c r="G156" s="18" t="inlineStr">
+        <is>
+          <t>page instruction</t>
+        </is>
+      </c>
+      <c r="H156" s="18" t="inlineStr">
+        <is>
+          <t>as the page opens (the speaker replays it)</t>
+        </is>
+      </c>
+      <c r="I156" s="18" t="inlineStr"/>
+      <c r="J156" s="16" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="K156" s="17" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="12" t="n">
+        <v>153</v>
+      </c>
+      <c r="B157" s="13" t="inlineStr">
+        <is>
+          <t>Page 11</t>
+        </is>
+      </c>
+      <c r="C157" s="14" t="inlineStr">
+        <is>
+          <t>P4 · MENTAL_SUB  (91 − 14)</t>
+        </is>
+      </c>
+      <c r="D157" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E157" s="13" t="inlineStr">
+        <is>
+          <t>vo_h_order</t>
+        </is>
+      </c>
+      <c r="F157" s="15" t="inlineStr">
+        <is>
+          <t>संख्याओं में से पहले इकाई घटाइए, फिर दहाई घटाइए।</t>
+        </is>
+      </c>
+      <c r="G157" s="14" t="inlineStr">
+        <is>
+          <t>Hint 1 (1st wrong answer)</t>
+        </is>
+      </c>
+      <c r="H157" s="14" t="inlineStr">
+        <is>
+          <t>the ones digits light on «इकाई», the tens digits on «दहाई»</t>
+        </is>
+      </c>
+      <c r="I157" s="14" t="inlineStr">
+        <is>
+          <t>Page 10</t>
+        </is>
+      </c>
+      <c r="J157" s="12" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="K157" s="13" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="16" t="n">
+        <v>154</v>
+      </c>
+      <c r="B158" s="17" t="inlineStr">
+        <is>
+          <t>Page 11</t>
+        </is>
+      </c>
+      <c r="C158" s="18" t="inlineStr">
+        <is>
+          <t>P4 · MENTAL_SUB  (91 − 14)</t>
+        </is>
+      </c>
+      <c r="D158" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E158" s="17" t="inlineStr">
+        <is>
+          <t>vo_p4_h2</t>
+        </is>
+      </c>
+      <c r="F158" s="19" t="inlineStr">
+        <is>
+          <t>91 में से 14 घटाने पर, 7 दहाई और 7 इकाई बचती हैं।</t>
+        </is>
+      </c>
+      <c r="G158" s="18" t="inlineStr">
+        <is>
+          <t>Hint 2 (2nd wrong answer)</t>
+        </is>
+      </c>
+      <c r="H158" s="18" t="inlineStr">
+        <is>
+          <t>the table comes in with the first number's blocks; the second number is taken away as it is said</t>
+        </is>
+      </c>
+      <c r="I158" s="18" t="inlineStr"/>
+      <c r="J158" s="16" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="K158" s="17" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="12" t="n">
+        <v>155</v>
+      </c>
+      <c r="B159" s="13" t="inlineStr">
+        <is>
+          <t>Page 11</t>
+        </is>
+      </c>
+      <c r="C159" s="14" t="inlineStr">
+        <is>
+          <t>P4 · MENTAL_SUB  (91 − 14)</t>
+        </is>
+      </c>
+      <c r="D159" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E159" s="13" t="inlineStr">
+        <is>
+          <t>vo_p4_reveal</t>
+        </is>
+      </c>
+      <c r="F159" s="15" t="inlineStr">
+        <is>
+          <t>91 में से 14 घटाने पर 77 बचता है। तो सही संख्या यह है।</t>
+        </is>
+      </c>
+      <c r="G159" s="14" t="inlineStr">
+        <is>
+          <t>Hint 3 (3rd wrong answer)</t>
+        </is>
+      </c>
+      <c r="H159" s="14" t="inlineStr">
+        <is>
+          <t>the right card / the right keys lit (one key at a time), the others off</t>
+        </is>
+      </c>
+      <c r="I159" s="14" t="inlineStr"/>
+      <c r="J159" s="12" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="K159" s="13" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="16" t="n">
+        <v>156</v>
+      </c>
+      <c r="B160" s="17" t="inlineStr">
+        <is>
+          <t>Page 11</t>
+        </is>
+      </c>
+      <c r="C160" s="18" t="inlineStr">
+        <is>
+          <t>P4 · MENTAL_SUB  (91 − 14)</t>
+        </is>
+      </c>
+      <c r="D160" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E160" s="17" t="inlineStr">
+        <is>
+          <t>vo_p4_correct</t>
+        </is>
+      </c>
+      <c r="F160" s="19" t="inlineStr">
+        <is>
+          <t>शाबाश! आपने सही संख्या चुन ली। 91 घटा 14 बराबर 77।</t>
+        </is>
+      </c>
+      <c r="G160" s="18" t="inlineStr">
+        <is>
+          <t>correct answer</t>
+        </is>
+      </c>
+      <c r="H160" s="18" t="inlineStr">
+        <is>
+          <t>the answer goes into the ?; confetti (a line with «… घटा … बराबर …» lights each part as it is said)</t>
+        </is>
+      </c>
+      <c r="I160" s="18" t="inlineStr"/>
+      <c r="J160" s="16" t="n">
         <v>7.04</v>
       </c>
-      <c r="K154" s="17" t="inlineStr">
-        <is>
-          <t>TTS (Gemini, Kore)</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="20" t="n">
-        <v>151</v>
-      </c>
-      <c r="B155" s="21" t="inlineStr">
+      <c r="K160" s="17" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="12" t="n">
+        <v>157</v>
+      </c>
+      <c r="B161" s="13" t="inlineStr">
+        <is>
+          <t>Page 11</t>
+        </is>
+      </c>
+      <c r="C161" s="14" t="inlineStr">
+        <is>
+          <t>P4 · MENTAL_SUB  (91 − 14)</t>
+        </is>
+      </c>
+      <c r="D161" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E161" s="13" t="inlineStr">
+        <is>
+          <t>vo_p4_correct_late</t>
+        </is>
+      </c>
+      <c r="F161" s="15" t="inlineStr">
+        <is>
+          <t>आपने सही संख्या चुन ली। 91 घटा 14 बराबर 77।</t>
+        </is>
+      </c>
+      <c r="G161" s="14" t="inlineStr">
+        <is>
+          <t>correct answer after a wrong one</t>
+        </is>
+      </c>
+      <c r="H161" s="14" t="inlineStr">
+        <is>
+          <t>the same as the correct line, without «शाबाश» (only a first-try answer gets it)</t>
+        </is>
+      </c>
+      <c r="I161" s="14" t="inlineStr"/>
+      <c r="J161" s="12" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="K161" s="13" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="20" t="n">
+        <v>158</v>
+      </c>
+      <c r="B162" s="21" t="inlineStr">
         <is>
           <t>Celebration</t>
         </is>
       </c>
-      <c r="C155" s="22" t="inlineStr">
+      <c r="C162" s="22" t="inlineStr">
         <is>
           <t>CEL · CELEBRATION</t>
         </is>
       </c>
-      <c r="D155" s="20" t="n">
+      <c r="D162" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E155" s="21" t="inlineStr">
+      <c r="E162" s="21" t="inlineStr">
         <is>
           <t>vo_cel</t>
         </is>
       </c>
-      <c r="F155" s="23" t="inlineStr">
+      <c r="F162" s="23" t="inlineStr">
         <is>
           <t>शाबाश! आपने दहाई खोलकर घटाना सीख लिया!</t>
         </is>
       </c>
-      <c r="G155" s="22" t="inlineStr">
+      <c r="G162" s="22" t="inlineStr">
         <is>
           <t>celebration</t>
         </is>
       </c>
-      <c r="H155" s="22" t="inlineStr">
+      <c r="H162" s="22" t="inlineStr">
         <is>
           <t>the celebration screen: Swiftee jumps on «शाबाश», then says the line lip-synced</t>
         </is>
       </c>
-      <c r="I155" s="22" t="inlineStr"/>
-      <c r="J155" s="20" t="n">
+      <c r="I162" s="22" t="inlineStr"/>
+      <c r="J162" s="20" t="n">
         <v>3.93</v>
       </c>
-      <c r="K155" s="21" t="inlineStr">
+      <c r="K162" s="21" t="inlineStr">
         <is>
           <t>TTS (Gemini, Kore)</t>
         </is>
@@ -7996,7 +8325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G116"/>
+  <dimension ref="A1:G123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -8018,7 +8347,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>112 recordings. Record each once; the file name is the Audio ID + .ogg, in assets/voiceover/.</t>
+          <t>119 recordings. Record each once; the file name is the Audio ID + .ogg, in assets/voiceover/.</t>
         </is>
       </c>
     </row>
@@ -10375,17 +10704,17 @@
       </c>
       <c r="B75" s="25" t="inlineStr">
         <is>
-          <t>vo_g1_eq</t>
+          <t>vo_g1_correct_late</t>
         </is>
       </c>
       <c r="C75" s="25" t="inlineStr">
         <is>
-          <t>vo_g1_eq.ogg</t>
+          <t>vo_g1_correct_late.ogg</t>
         </is>
       </c>
       <c r="D75" s="26" t="inlineStr">
         <is>
-          <t>इसलिए 42 घटा 27 बराबर 15।</t>
+          <t>42 में से 27 घटाने पर हमें मिलीं 1 दहाई और 5 इकाई, यानी 15।</t>
         </is>
       </c>
       <c r="E75" s="27" t="inlineStr">
@@ -10394,7 +10723,7 @@
         </is>
       </c>
       <c r="F75" s="24" t="n">
-        <v>4.26</v>
+        <v>6.47</v>
       </c>
       <c r="G75" s="25" t="inlineStr">
         <is>
@@ -10408,26 +10737,26 @@
       </c>
       <c r="B76" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_prompt</t>
+          <t>vo_g1_eq</t>
         </is>
       </c>
       <c r="C76" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_prompt.ogg</t>
+          <t>vo_g1_eq.ogg</t>
         </is>
       </c>
       <c r="D76" s="26" t="inlineStr">
         <is>
-          <t>53 में से 14 घटाइए।</t>
+          <t>इसलिए 42 घटा 27 बराबर 15।</t>
         </is>
       </c>
       <c r="E76" s="27" t="inlineStr">
         <is>
-          <t>Page 6</t>
+          <t>Page 5</t>
         </is>
       </c>
       <c r="F76" s="24" t="n">
-        <v>2.56</v>
+        <v>4.26</v>
       </c>
       <c r="G76" s="25" t="inlineStr">
         <is>
@@ -10441,17 +10770,17 @@
       </c>
       <c r="B77" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_build</t>
+          <t>vo_g2_prompt</t>
         </is>
       </c>
       <c r="C77" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_build.ogg</t>
+          <t>vo_g2_prompt.ogg</t>
         </is>
       </c>
       <c r="D77" s="26" t="inlineStr">
         <is>
-          <t>सबसे पहले ब्लॉक्स की सहायता से 53 बनाइए।</t>
+          <t>53 में से 14 घटाइए।</t>
         </is>
       </c>
       <c r="E77" s="27" t="inlineStr">
@@ -10460,7 +10789,7 @@
         </is>
       </c>
       <c r="F77" s="24" t="n">
-        <v>4.23</v>
+        <v>2.56</v>
       </c>
       <c r="G77" s="25" t="inlineStr">
         <is>
@@ -10474,17 +10803,17 @@
       </c>
       <c r="B78" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_sub</t>
+          <t>vo_g2_build</t>
         </is>
       </c>
       <c r="C78" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_sub.ogg</t>
+          <t>vo_g2_build.ogg</t>
         </is>
       </c>
       <c r="D78" s="26" t="inlineStr">
         <is>
-          <t>और अब इसमें से 14 घटाइए।</t>
+          <t>सबसे पहले ब्लॉक्स की सहायता से 53 बनाइए।</t>
         </is>
       </c>
       <c r="E78" s="27" t="inlineStr">
@@ -10493,7 +10822,7 @@
         </is>
       </c>
       <c r="F78" s="24" t="n">
-        <v>2.32</v>
+        <v>4.23</v>
       </c>
       <c r="G78" s="25" t="inlineStr">
         <is>
@@ -10507,17 +10836,17 @@
       </c>
       <c r="B79" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_rm_ones</t>
+          <t>vo_g2_sub</t>
         </is>
       </c>
       <c r="C79" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_rm_ones.ogg</t>
+          <t>vo_g2_sub.ogg</t>
         </is>
       </c>
       <c r="D79" s="26" t="inlineStr">
         <is>
-          <t>इसमें से 4 इकाई को हटाइए।</t>
+          <t>और अब इसमें से 14 घटाइए।</t>
         </is>
       </c>
       <c r="E79" s="27" t="inlineStr">
@@ -10526,7 +10855,7 @@
         </is>
       </c>
       <c r="F79" s="24" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="G79" s="25" t="inlineStr">
         <is>
@@ -10540,17 +10869,17 @@
       </c>
       <c r="B80" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_rm_tens</t>
+          <t>vo_g2_rm_ones</t>
         </is>
       </c>
       <c r="C80" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_rm_tens.ogg</t>
+          <t>vo_g2_rm_ones.ogg</t>
         </is>
       </c>
       <c r="D80" s="26" t="inlineStr">
         <is>
-          <t>अब दहाइयाँ घटाइए।</t>
+          <t>इसमें से 4 इकाई को हटाइए।</t>
         </is>
       </c>
       <c r="E80" s="27" t="inlineStr">
@@ -10559,7 +10888,7 @@
         </is>
       </c>
       <c r="F80" s="24" t="n">
-        <v>2.16</v>
+        <v>2.58</v>
       </c>
       <c r="G80" s="25" t="inlineStr">
         <is>
@@ -10573,17 +10902,17 @@
       </c>
       <c r="B81" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_h2</t>
+          <t>vo_g2_rm_tens</t>
         </is>
       </c>
       <c r="C81" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_h2.ogg</t>
+          <t>vo_g2_rm_tens.ogg</t>
         </is>
       </c>
       <c r="D81" s="26" t="inlineStr">
         <is>
-          <t>53 में से 14 घटाने पर, 3 दहाई और 9 इकाई बचती हैं।</t>
+          <t>अब दहाइयाँ घटाइए।</t>
         </is>
       </c>
       <c r="E81" s="27" t="inlineStr">
@@ -10592,7 +10921,7 @@
         </is>
       </c>
       <c r="F81" s="24" t="n">
-        <v>4.71</v>
+        <v>2.16</v>
       </c>
       <c r="G81" s="25" t="inlineStr">
         <is>
@@ -10606,17 +10935,17 @@
       </c>
       <c r="B82" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_reveal</t>
+          <t>vo_g2_h2</t>
         </is>
       </c>
       <c r="C82" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_reveal.ogg</t>
+          <t>vo_g2_h2.ogg</t>
         </is>
       </c>
       <c r="D82" s="26" t="inlineStr">
         <is>
-          <t>53 में से 14 घटाने पर 39 बचता है। तो सही संख्या यह है।</t>
+          <t>53 में से 14 घटाने पर, 3 दहाई और 9 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="E82" s="27" t="inlineStr">
@@ -10625,7 +10954,7 @@
         </is>
       </c>
       <c r="F82" s="24" t="n">
-        <v>5.8</v>
+        <v>4.71</v>
       </c>
       <c r="G82" s="25" t="inlineStr">
         <is>
@@ -10639,17 +10968,17 @@
       </c>
       <c r="B83" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_correct</t>
+          <t>vo_g2_reveal</t>
         </is>
       </c>
       <c r="C83" s="25" t="inlineStr">
         <is>
-          <t>vo_g2_correct.ogg</t>
+          <t>vo_g2_reveal.ogg</t>
         </is>
       </c>
       <c r="D83" s="26" t="inlineStr">
         <is>
-          <t>शाबाश! 53 घटा 14 बराबर 39।</t>
+          <t>53 में से 14 घटाने पर 39 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="E83" s="27" t="inlineStr">
@@ -10658,7 +10987,7 @@
         </is>
       </c>
       <c r="F83" s="24" t="n">
-        <v>4.48</v>
+        <v>5.8</v>
       </c>
       <c r="G83" s="25" t="inlineStr">
         <is>
@@ -10672,26 +11001,26 @@
       </c>
       <c r="B84" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_prompt</t>
+          <t>vo_g2_correct</t>
         </is>
       </c>
       <c r="C84" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_prompt.ogg</t>
+          <t>vo_g2_correct.ogg</t>
         </is>
       </c>
       <c r="D84" s="26" t="inlineStr">
         <is>
-          <t>46 में से 28 घटाइए।</t>
+          <t>शाबाश! 53 घटा 14 बराबर 39।</t>
         </is>
       </c>
       <c r="E84" s="27" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 6</t>
         </is>
       </c>
       <c r="F84" s="24" t="n">
-        <v>2.72</v>
+        <v>4.48</v>
       </c>
       <c r="G84" s="25" t="inlineStr">
         <is>
@@ -10705,26 +11034,26 @@
       </c>
       <c r="B85" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_sub</t>
+          <t>vo_g2_correct_late</t>
         </is>
       </c>
       <c r="C85" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_sub.ogg</t>
+          <t>vo_g2_correct_late.ogg</t>
         </is>
       </c>
       <c r="D85" s="26" t="inlineStr">
         <is>
-          <t>और अब इसमें से 28 घटाइए।</t>
+          <t>53 घटा 14 बराबर 39।</t>
         </is>
       </c>
       <c r="E85" s="27" t="inlineStr">
         <is>
-          <t>Page 7</t>
+          <t>Page 6</t>
         </is>
       </c>
       <c r="F85" s="24" t="n">
-        <v>2.67</v>
+        <v>3.88</v>
       </c>
       <c r="G85" s="25" t="inlineStr">
         <is>
@@ -10738,17 +11067,17 @@
       </c>
       <c r="B86" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_rm_ones</t>
+          <t>vo_g3_prompt</t>
         </is>
       </c>
       <c r="C86" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_rm_ones.ogg</t>
+          <t>vo_g3_prompt.ogg</t>
         </is>
       </c>
       <c r="D86" s="26" t="inlineStr">
         <is>
-          <t>इसमें से 8 इकाई को हटाइए।</t>
+          <t>46 में से 28 घटाइए।</t>
         </is>
       </c>
       <c r="E86" s="27" t="inlineStr">
@@ -10757,7 +11086,7 @@
         </is>
       </c>
       <c r="F86" s="24" t="n">
-        <v>3.03</v>
+        <v>2.72</v>
       </c>
       <c r="G86" s="25" t="inlineStr">
         <is>
@@ -10771,17 +11100,17 @@
       </c>
       <c r="B87" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_rm_tens</t>
+          <t>vo_g3_sub</t>
         </is>
       </c>
       <c r="C87" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_rm_tens.ogg</t>
+          <t>vo_g3_sub.ogg</t>
         </is>
       </c>
       <c r="D87" s="26" t="inlineStr">
         <is>
-          <t>अब दहाइयाँ हटाइए।</t>
+          <t>और अब इसमें से 28 घटाइए।</t>
         </is>
       </c>
       <c r="E87" s="27" t="inlineStr">
@@ -10790,7 +11119,7 @@
         </is>
       </c>
       <c r="F87" s="24" t="n">
-        <v>2.47</v>
+        <v>2.67</v>
       </c>
       <c r="G87" s="25" t="inlineStr">
         <is>
@@ -10804,17 +11133,17 @@
       </c>
       <c r="B88" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_h2</t>
+          <t>vo_g3_rm_ones</t>
         </is>
       </c>
       <c r="C88" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_h2.ogg</t>
+          <t>vo_g3_rm_ones.ogg</t>
         </is>
       </c>
       <c r="D88" s="26" t="inlineStr">
         <is>
-          <t>46 में से 28 घटाने पर, 1 दहाई और 8 इकाई बचती हैं।</t>
+          <t>इसमें से 8 इकाई को हटाइए।</t>
         </is>
       </c>
       <c r="E88" s="27" t="inlineStr">
@@ -10823,7 +11152,7 @@
         </is>
       </c>
       <c r="F88" s="24" t="n">
-        <v>5.55</v>
+        <v>3.03</v>
       </c>
       <c r="G88" s="25" t="inlineStr">
         <is>
@@ -10837,17 +11166,17 @@
       </c>
       <c r="B89" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_reveal</t>
+          <t>vo_g3_rm_tens</t>
         </is>
       </c>
       <c r="C89" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_reveal.ogg</t>
+          <t>vo_g3_rm_tens.ogg</t>
         </is>
       </c>
       <c r="D89" s="26" t="inlineStr">
         <is>
-          <t>46 में से 28 घटाने पर 18 बचता है। तो सही संख्या यह है।</t>
+          <t>अब दहाइयाँ हटाइए।</t>
         </is>
       </c>
       <c r="E89" s="27" t="inlineStr">
@@ -10856,7 +11185,7 @@
         </is>
       </c>
       <c r="F89" s="24" t="n">
-        <v>5.75</v>
+        <v>2.47</v>
       </c>
       <c r="G89" s="25" t="inlineStr">
         <is>
@@ -10870,17 +11199,17 @@
       </c>
       <c r="B90" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_correct</t>
+          <t>vo_g3_h2</t>
         </is>
       </c>
       <c r="C90" s="25" t="inlineStr">
         <is>
-          <t>vo_g3_correct.ogg</t>
+          <t>vo_g3_h2.ogg</t>
         </is>
       </c>
       <c r="D90" s="26" t="inlineStr">
         <is>
-          <t>शाबाश! 46 घटा 28 बराबर 18।</t>
+          <t>46 में से 28 घटाने पर, 1 दहाई और 8 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="E90" s="27" t="inlineStr">
@@ -10889,7 +11218,7 @@
         </is>
       </c>
       <c r="F90" s="24" t="n">
-        <v>4.99</v>
+        <v>5.55</v>
       </c>
       <c r="G90" s="25" t="inlineStr">
         <is>
@@ -10903,30 +11232,30 @@
       </c>
       <c r="B91" s="25" t="inlineStr">
         <is>
-          <t>vo_pt_practice</t>
+          <t>vo_g3_reveal</t>
         </is>
       </c>
       <c r="C91" s="25" t="inlineStr">
         <is>
-          <t>vo_pt_practice.ogg</t>
+          <t>vo_g3_reveal.ogg</t>
         </is>
       </c>
       <c r="D91" s="26" t="inlineStr">
         <is>
-          <t>वाह! अब आपकी बारी।</t>
+          <t>46 में से 28 घटाने पर 18 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="E91" s="27" t="inlineStr">
         <is>
-          <t>Transition 3</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="F91" s="24" t="n">
-        <v>1.87</v>
+        <v>5.75</v>
       </c>
       <c r="G91" s="25" t="inlineStr">
         <is>
-          <t>Copied (HI02H11, recorded voice)</t>
+          <t>TTS (Gemini, Kore)</t>
         </is>
       </c>
     </row>
@@ -10936,26 +11265,26 @@
       </c>
       <c r="B92" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_prompt</t>
+          <t>vo_g3_correct</t>
         </is>
       </c>
       <c r="C92" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_prompt.ogg</t>
+          <t>vo_g3_correct.ogg</t>
         </is>
       </c>
       <c r="D92" s="26" t="inlineStr">
         <is>
-          <t>74 में से 58 घटाइए।</t>
+          <t>शाबाश! 46 घटा 28 बराबर 18।</t>
         </is>
       </c>
       <c r="E92" s="27" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="F92" s="24" t="n">
-        <v>2.5</v>
+        <v>4.99</v>
       </c>
       <c r="G92" s="25" t="inlineStr">
         <is>
@@ -10969,26 +11298,26 @@
       </c>
       <c r="B93" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_sub</t>
+          <t>vo_g3_correct_late</t>
         </is>
       </c>
       <c r="C93" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_sub.ogg</t>
+          <t>vo_g3_correct_late.ogg</t>
         </is>
       </c>
       <c r="D93" s="26" t="inlineStr">
         <is>
-          <t>और अब इसमें से 58 घटाते हैं।</t>
+          <t>46 घटा 28 बराबर 18।</t>
         </is>
       </c>
       <c r="E93" s="27" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 7</t>
         </is>
       </c>
       <c r="F93" s="24" t="n">
-        <v>3.69</v>
+        <v>3.78</v>
       </c>
       <c r="G93" s="25" t="inlineStr">
         <is>
@@ -11002,30 +11331,30 @@
       </c>
       <c r="B94" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_rm_ones</t>
+          <t>vo_pt_practice</t>
         </is>
       </c>
       <c r="C94" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_rm_ones.ogg</t>
+          <t>vo_pt_practice.ogg</t>
         </is>
       </c>
       <c r="D94" s="26" t="inlineStr">
         <is>
-          <t>14 इकाई में से 8 इकाई हटाइए।</t>
+          <t>वाह! अब आपकी बारी।</t>
         </is>
       </c>
       <c r="E94" s="27" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Transition 3</t>
         </is>
       </c>
       <c r="F94" s="24" t="n">
-        <v>3.33</v>
+        <v>1.87</v>
       </c>
       <c r="G94" s="25" t="inlineStr">
         <is>
-          <t>TTS (Gemini, Kore)</t>
+          <t>Copied (HI02H11, recorded voice)</t>
         </is>
       </c>
     </row>
@@ -11035,17 +11364,17 @@
       </c>
       <c r="B95" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_rm_tens</t>
+          <t>vo_p1_prompt</t>
         </is>
       </c>
       <c r="C95" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_rm_tens.ogg</t>
+          <t>vo_p1_prompt.ogg</t>
         </is>
       </c>
       <c r="D95" s="26" t="inlineStr">
         <is>
-          <t>अब दहाइयाँ घटाइए।</t>
+          <t>74 में से 58 घटाइए।</t>
         </is>
       </c>
       <c r="E95" s="27" t="inlineStr">
@@ -11054,7 +11383,7 @@
         </is>
       </c>
       <c r="F95" s="24" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="G95" s="25" t="inlineStr">
         <is>
@@ -11068,26 +11397,26 @@
       </c>
       <c r="B96" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_ask</t>
+          <t>vo_p1_sub</t>
         </is>
       </c>
       <c r="C96" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_ask.ogg</t>
+          <t>vo_p1_sub.ogg</t>
         </is>
       </c>
       <c r="D96" s="26" t="inlineStr">
         <is>
-          <t>अब कितने बचे? नीचे डिब्बे पर टैप करके सही संख्या लिखिए।</t>
+          <t>और अब इसमें से 58 घटाते हैं।</t>
         </is>
       </c>
       <c r="E96" s="27" t="inlineStr">
         <is>
-          <t>Page 8, Page 9</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="F96" s="24" t="n">
-        <v>4.39</v>
+        <v>3.69</v>
       </c>
       <c r="G96" s="25" t="inlineStr">
         <is>
@@ -11101,17 +11430,17 @@
       </c>
       <c r="B97" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_h2</t>
+          <t>vo_p1_rm_ones</t>
         </is>
       </c>
       <c r="C97" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_h2.ogg</t>
+          <t>vo_p1_rm_ones.ogg</t>
         </is>
       </c>
       <c r="D97" s="26" t="inlineStr">
         <is>
-          <t>74 में से 58 घटाने पर, 1 दहाई और 6 इकाई बचती हैं।</t>
+          <t>14 इकाई में से 8 इकाई हटाइए।</t>
         </is>
       </c>
       <c r="E97" s="27" t="inlineStr">
@@ -11120,7 +11449,7 @@
         </is>
       </c>
       <c r="F97" s="24" t="n">
-        <v>5.45</v>
+        <v>3.33</v>
       </c>
       <c r="G97" s="25" t="inlineStr">
         <is>
@@ -11134,17 +11463,17 @@
       </c>
       <c r="B98" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_reveal</t>
+          <t>vo_p1_rm_tens</t>
         </is>
       </c>
       <c r="C98" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_reveal.ogg</t>
+          <t>vo_p1_rm_tens.ogg</t>
         </is>
       </c>
       <c r="D98" s="26" t="inlineStr">
         <is>
-          <t>74 में से 58 घटाने पर 16 बचता है। तो सही संख्या यह है।</t>
+          <t>अब दहाइयाँ घटाइए।</t>
         </is>
       </c>
       <c r="E98" s="27" t="inlineStr">
@@ -11153,7 +11482,7 @@
         </is>
       </c>
       <c r="F98" s="24" t="n">
-        <v>5.69</v>
+        <v>2.63</v>
       </c>
       <c r="G98" s="25" t="inlineStr">
         <is>
@@ -11167,26 +11496,26 @@
       </c>
       <c r="B99" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_correct</t>
+          <t>vo_p1_ask</t>
         </is>
       </c>
       <c r="C99" s="25" t="inlineStr">
         <is>
-          <t>vo_p1_correct.ogg</t>
+          <t>vo_p1_ask.ogg</t>
         </is>
       </c>
       <c r="D99" s="26" t="inlineStr">
         <is>
-          <t>शाबाश! 74 में से 58 घटाने पर हमें मिला 16।</t>
+          <t>अब कितने बचे? नीचे डिब्बे पर टैप करके सही संख्या लिखिए।</t>
         </is>
       </c>
       <c r="E99" s="27" t="inlineStr">
         <is>
-          <t>Page 8</t>
+          <t>Page 8, Page 9</t>
         </is>
       </c>
       <c r="F99" s="24" t="n">
-        <v>5.01</v>
+        <v>4.39</v>
       </c>
       <c r="G99" s="25" t="inlineStr">
         <is>
@@ -11200,26 +11529,26 @@
       </c>
       <c r="B100" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_prompt</t>
+          <t>vo_p1_h2</t>
         </is>
       </c>
       <c r="C100" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_prompt.ogg</t>
+          <t>vo_p1_h2.ogg</t>
         </is>
       </c>
       <c r="D100" s="26" t="inlineStr">
         <is>
-          <t>61 में से 35 घटाइए।</t>
+          <t>74 में से 58 घटाने पर, 1 दहाई और 6 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="E100" s="27" t="inlineStr">
         <is>
-          <t>Page 9</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="F100" s="24" t="n">
-        <v>2.48</v>
+        <v>5.45</v>
       </c>
       <c r="G100" s="25" t="inlineStr">
         <is>
@@ -11233,26 +11562,26 @@
       </c>
       <c r="B101" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_sub</t>
+          <t>vo_p1_reveal</t>
         </is>
       </c>
       <c r="C101" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_sub.ogg</t>
+          <t>vo_p1_reveal.ogg</t>
         </is>
       </c>
       <c r="D101" s="26" t="inlineStr">
         <is>
-          <t>और अब इसमें से 35 घटाते हैं।</t>
+          <t>74 में से 58 घटाने पर 16 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="E101" s="27" t="inlineStr">
         <is>
-          <t>Page 9</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="F101" s="24" t="n">
-        <v>2.86</v>
+        <v>5.69</v>
       </c>
       <c r="G101" s="25" t="inlineStr">
         <is>
@@ -11266,26 +11595,26 @@
       </c>
       <c r="B102" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_rm_ones</t>
+          <t>vo_p1_correct</t>
         </is>
       </c>
       <c r="C102" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_rm_ones.ogg</t>
+          <t>vo_p1_correct.ogg</t>
         </is>
       </c>
       <c r="D102" s="26" t="inlineStr">
         <is>
-          <t>इकाई हटाइए।</t>
+          <t>शाबाश! 74 में से 58 घटाने पर हमें मिला 16।</t>
         </is>
       </c>
       <c r="E102" s="27" t="inlineStr">
         <is>
-          <t>Page 9</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="F102" s="24" t="n">
-        <v>1.81</v>
+        <v>5.01</v>
       </c>
       <c r="G102" s="25" t="inlineStr">
         <is>
@@ -11299,26 +11628,26 @@
       </c>
       <c r="B103" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_rm_tens</t>
+          <t>vo_p1_correct_late</t>
         </is>
       </c>
       <c r="C103" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_rm_tens.ogg</t>
+          <t>vo_p1_correct_late.ogg</t>
         </is>
       </c>
       <c r="D103" s="26" t="inlineStr">
         <is>
-          <t>अब दहाइयाँ हटाइए।</t>
+          <t>74 में से 58 घटाने पर हमें मिला 16।</t>
         </is>
       </c>
       <c r="E103" s="27" t="inlineStr">
         <is>
-          <t>Page 9</t>
+          <t>Page 8</t>
         </is>
       </c>
       <c r="F103" s="24" t="n">
-        <v>1.95</v>
+        <v>3.93</v>
       </c>
       <c r="G103" s="25" t="inlineStr">
         <is>
@@ -11332,17 +11661,17 @@
       </c>
       <c r="B104" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_h2</t>
+          <t>vo_p2_prompt</t>
         </is>
       </c>
       <c r="C104" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_h2.ogg</t>
+          <t>vo_p2_prompt.ogg</t>
         </is>
       </c>
       <c r="D104" s="26" t="inlineStr">
         <is>
-          <t>61 में से 35 घटाने पर, 2 दहाई और 6 इकाई बचती हैं।</t>
+          <t>61 में से 35 घटाइए।</t>
         </is>
       </c>
       <c r="E104" s="27" t="inlineStr">
@@ -11351,7 +11680,7 @@
         </is>
       </c>
       <c r="F104" s="24" t="n">
-        <v>5.81</v>
+        <v>2.48</v>
       </c>
       <c r="G104" s="25" t="inlineStr">
         <is>
@@ -11365,17 +11694,17 @@
       </c>
       <c r="B105" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_reveal</t>
+          <t>vo_p2_sub</t>
         </is>
       </c>
       <c r="C105" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_reveal.ogg</t>
+          <t>vo_p2_sub.ogg</t>
         </is>
       </c>
       <c r="D105" s="26" t="inlineStr">
         <is>
-          <t>61 में से 35 घटाने पर 26 बचता है। तो सही संख्या यह है।</t>
+          <t>और अब इसमें से 35 घटाते हैं।</t>
         </is>
       </c>
       <c r="E105" s="27" t="inlineStr">
@@ -11384,7 +11713,7 @@
         </is>
       </c>
       <c r="F105" s="24" t="n">
-        <v>4.64</v>
+        <v>2.86</v>
       </c>
       <c r="G105" s="25" t="inlineStr">
         <is>
@@ -11398,17 +11727,17 @@
       </c>
       <c r="B106" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_correct</t>
+          <t>vo_p2_rm_ones</t>
         </is>
       </c>
       <c r="C106" s="25" t="inlineStr">
         <is>
-          <t>vo_p2_correct.ogg</t>
+          <t>vo_p2_rm_ones.ogg</t>
         </is>
       </c>
       <c r="D106" s="26" t="inlineStr">
         <is>
-          <t>शाबाश! 61 में से 35 घटाने पर हमें मिला 26।</t>
+          <t>इकाई हटाइए।</t>
         </is>
       </c>
       <c r="E106" s="27" t="inlineStr">
@@ -11417,7 +11746,7 @@
         </is>
       </c>
       <c r="F106" s="24" t="n">
-        <v>5.21</v>
+        <v>1.81</v>
       </c>
       <c r="G106" s="25" t="inlineStr">
         <is>
@@ -11431,26 +11760,26 @@
       </c>
       <c r="B107" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_prompt</t>
+          <t>vo_p2_rm_tens</t>
         </is>
       </c>
       <c r="C107" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_prompt.ogg</t>
+          <t>vo_p2_rm_tens.ogg</t>
         </is>
       </c>
       <c r="D107" s="26" t="inlineStr">
         <is>
-          <t>84 में से 46 घटाइए और सही संख्या चुनिए।</t>
+          <t>अब दहाइयाँ हटाइए।</t>
         </is>
       </c>
       <c r="E107" s="27" t="inlineStr">
         <is>
-          <t>Page 10</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="F107" s="24" t="n">
-        <v>4.51</v>
+        <v>1.95</v>
       </c>
       <c r="G107" s="25" t="inlineStr">
         <is>
@@ -11464,26 +11793,26 @@
       </c>
       <c r="B108" s="25" t="inlineStr">
         <is>
-          <t>vo_h_order</t>
+          <t>vo_p2_h2</t>
         </is>
       </c>
       <c r="C108" s="25" t="inlineStr">
         <is>
-          <t>vo_h_order.ogg</t>
+          <t>vo_p2_h2.ogg</t>
         </is>
       </c>
       <c r="D108" s="26" t="inlineStr">
         <is>
-          <t>संख्याओं में से पहले इकाई घटाइए, फिर दहाई घटाइए।</t>
+          <t>61 में से 35 घटाने पर, 2 दहाई और 6 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="E108" s="27" t="inlineStr">
         <is>
-          <t>Page 10, Page 11</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="F108" s="24" t="n">
-        <v>4.45</v>
+        <v>5.81</v>
       </c>
       <c r="G108" s="25" t="inlineStr">
         <is>
@@ -11497,26 +11826,26 @@
       </c>
       <c r="B109" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_h2</t>
+          <t>vo_p2_reveal</t>
         </is>
       </c>
       <c r="C109" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_h2.ogg</t>
+          <t>vo_p2_reveal.ogg</t>
         </is>
       </c>
       <c r="D109" s="26" t="inlineStr">
         <is>
-          <t>84 में से 46 घटाने पर, 3 दहाई और 8 इकाई बचती हैं।</t>
+          <t>61 में से 35 घटाने पर 26 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="E109" s="27" t="inlineStr">
         <is>
-          <t>Page 10</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="F109" s="24" t="n">
-        <v>5.47</v>
+        <v>4.64</v>
       </c>
       <c r="G109" s="25" t="inlineStr">
         <is>
@@ -11530,26 +11859,26 @@
       </c>
       <c r="B110" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_reveal</t>
+          <t>vo_p2_correct</t>
         </is>
       </c>
       <c r="C110" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_reveal.ogg</t>
+          <t>vo_p2_correct.ogg</t>
         </is>
       </c>
       <c r="D110" s="26" t="inlineStr">
         <is>
-          <t>84 में से 46 घटाने पर 38 बचता है। तो सही संख्या यह है।</t>
+          <t>शाबाश! 61 में से 35 घटाने पर हमें मिला 26।</t>
         </is>
       </c>
       <c r="E110" s="27" t="inlineStr">
         <is>
-          <t>Page 10</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="F110" s="24" t="n">
-        <v>5.52</v>
+        <v>5.21</v>
       </c>
       <c r="G110" s="25" t="inlineStr">
         <is>
@@ -11563,26 +11892,26 @@
       </c>
       <c r="B111" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_correct</t>
+          <t>vo_p2_correct_late</t>
         </is>
       </c>
       <c r="C111" s="25" t="inlineStr">
         <is>
-          <t>vo_p3_correct.ogg</t>
+          <t>vo_p2_correct_late.ogg</t>
         </is>
       </c>
       <c r="D111" s="26" t="inlineStr">
         <is>
-          <t>शाबाश! आपने सही संख्या चुन ली। 84 घटा 46 बराबर 38।</t>
+          <t>61 में से 35 घटाने पर हमें मिला 26।</t>
         </is>
       </c>
       <c r="E111" s="27" t="inlineStr">
         <is>
-          <t>Page 10</t>
+          <t>Page 9</t>
         </is>
       </c>
       <c r="F111" s="24" t="n">
-        <v>6.91</v>
+        <v>3.94</v>
       </c>
       <c r="G111" s="25" t="inlineStr">
         <is>
@@ -11596,26 +11925,26 @@
       </c>
       <c r="B112" s="25" t="inlineStr">
         <is>
-          <t>vo_p4_prompt</t>
+          <t>vo_p3_prompt</t>
         </is>
       </c>
       <c r="C112" s="25" t="inlineStr">
         <is>
-          <t>vo_p4_prompt.ogg</t>
+          <t>vo_p3_prompt.ogg</t>
         </is>
       </c>
       <c r="D112" s="26" t="inlineStr">
         <is>
-          <t>91 में से 14 घटाइए और सही संख्या चुनिए।</t>
+          <t>84 में से 46 घटाइए और सही संख्या चुनिए।</t>
         </is>
       </c>
       <c r="E112" s="27" t="inlineStr">
         <is>
-          <t>Page 11</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="F112" s="24" t="n">
-        <v>3.57</v>
+        <v>4.51</v>
       </c>
       <c r="G112" s="25" t="inlineStr">
         <is>
@@ -11629,26 +11958,26 @@
       </c>
       <c r="B113" s="25" t="inlineStr">
         <is>
-          <t>vo_p4_h2</t>
+          <t>vo_h_order</t>
         </is>
       </c>
       <c r="C113" s="25" t="inlineStr">
         <is>
-          <t>vo_p4_h2.ogg</t>
+          <t>vo_h_order.ogg</t>
         </is>
       </c>
       <c r="D113" s="26" t="inlineStr">
         <is>
-          <t>91 में से 14 घटाने पर, 7 दहाई और 7 इकाई बचती हैं।</t>
+          <t>संख्याओं में से पहले इकाई घटाइए, फिर दहाई घटाइए।</t>
         </is>
       </c>
       <c r="E113" s="27" t="inlineStr">
         <is>
-          <t>Page 11</t>
+          <t>Page 10, Page 11</t>
         </is>
       </c>
       <c r="F113" s="24" t="n">
-        <v>5.17</v>
+        <v>4.45</v>
       </c>
       <c r="G113" s="25" t="inlineStr">
         <is>
@@ -11662,26 +11991,26 @@
       </c>
       <c r="B114" s="25" t="inlineStr">
         <is>
-          <t>vo_p4_reveal</t>
+          <t>vo_p3_h2</t>
         </is>
       </c>
       <c r="C114" s="25" t="inlineStr">
         <is>
-          <t>vo_p4_reveal.ogg</t>
+          <t>vo_p3_h2.ogg</t>
         </is>
       </c>
       <c r="D114" s="26" t="inlineStr">
         <is>
-          <t>91 में से 14 घटाने पर 77 बचता है। तो सही संख्या यह है।</t>
+          <t>84 में से 46 घटाने पर, 3 दहाई और 8 इकाई बचती हैं।</t>
         </is>
       </c>
       <c r="E114" s="27" t="inlineStr">
         <is>
-          <t>Page 11</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="F114" s="24" t="n">
-        <v>6.49</v>
+        <v>5.47</v>
       </c>
       <c r="G114" s="25" t="inlineStr">
         <is>
@@ -11695,26 +12024,26 @@
       </c>
       <c r="B115" s="25" t="inlineStr">
         <is>
-          <t>vo_p4_correct</t>
+          <t>vo_p3_reveal</t>
         </is>
       </c>
       <c r="C115" s="25" t="inlineStr">
         <is>
-          <t>vo_p4_correct.ogg</t>
+          <t>vo_p3_reveal.ogg</t>
         </is>
       </c>
       <c r="D115" s="26" t="inlineStr">
         <is>
-          <t>शाबाश! आपने सही संख्या चुन ली। 91 घटा 14 बराबर 77।</t>
+          <t>84 में से 46 घटाने पर 38 बचता है। तो सही संख्या यह है।</t>
         </is>
       </c>
       <c r="E115" s="27" t="inlineStr">
         <is>
-          <t>Page 11</t>
+          <t>Page 10</t>
         </is>
       </c>
       <c r="F115" s="24" t="n">
-        <v>7.04</v>
+        <v>5.52</v>
       </c>
       <c r="G115" s="25" t="inlineStr">
         <is>
@@ -11728,28 +12057,259 @@
       </c>
       <c r="B116" s="25" t="inlineStr">
         <is>
+          <t>vo_p3_correct</t>
+        </is>
+      </c>
+      <c r="C116" s="25" t="inlineStr">
+        <is>
+          <t>vo_p3_correct.ogg</t>
+        </is>
+      </c>
+      <c r="D116" s="26" t="inlineStr">
+        <is>
+          <t>शाबाश! आपने सही संख्या चुन ली। 84 घटा 46 बराबर 38।</t>
+        </is>
+      </c>
+      <c r="E116" s="27" t="inlineStr">
+        <is>
+          <t>Page 10</t>
+        </is>
+      </c>
+      <c r="F116" s="24" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="G116" s="25" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="24" t="n">
+        <v>113</v>
+      </c>
+      <c r="B117" s="25" t="inlineStr">
+        <is>
+          <t>vo_p3_correct_late</t>
+        </is>
+      </c>
+      <c r="C117" s="25" t="inlineStr">
+        <is>
+          <t>vo_p3_correct_late.ogg</t>
+        </is>
+      </c>
+      <c r="D117" s="26" t="inlineStr">
+        <is>
+          <t>आपने सही संख्या चुन ली। 84 घटा 46 बराबर 38।</t>
+        </is>
+      </c>
+      <c r="E117" s="27" t="inlineStr">
+        <is>
+          <t>Page 10</t>
+        </is>
+      </c>
+      <c r="F117" s="24" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="G117" s="25" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="24" t="n">
+        <v>114</v>
+      </c>
+      <c r="B118" s="25" t="inlineStr">
+        <is>
+          <t>vo_p4_prompt</t>
+        </is>
+      </c>
+      <c r="C118" s="25" t="inlineStr">
+        <is>
+          <t>vo_p4_prompt.ogg</t>
+        </is>
+      </c>
+      <c r="D118" s="26" t="inlineStr">
+        <is>
+          <t>91 में से 14 घटाइए और सही संख्या चुनिए।</t>
+        </is>
+      </c>
+      <c r="E118" s="27" t="inlineStr">
+        <is>
+          <t>Page 11</t>
+        </is>
+      </c>
+      <c r="F118" s="24" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="G118" s="25" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="24" t="n">
+        <v>115</v>
+      </c>
+      <c r="B119" s="25" t="inlineStr">
+        <is>
+          <t>vo_p4_h2</t>
+        </is>
+      </c>
+      <c r="C119" s="25" t="inlineStr">
+        <is>
+          <t>vo_p4_h2.ogg</t>
+        </is>
+      </c>
+      <c r="D119" s="26" t="inlineStr">
+        <is>
+          <t>91 में से 14 घटाने पर, 7 दहाई और 7 इकाई बचती हैं।</t>
+        </is>
+      </c>
+      <c r="E119" s="27" t="inlineStr">
+        <is>
+          <t>Page 11</t>
+        </is>
+      </c>
+      <c r="F119" s="24" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="G119" s="25" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="24" t="n">
+        <v>116</v>
+      </c>
+      <c r="B120" s="25" t="inlineStr">
+        <is>
+          <t>vo_p4_reveal</t>
+        </is>
+      </c>
+      <c r="C120" s="25" t="inlineStr">
+        <is>
+          <t>vo_p4_reveal.ogg</t>
+        </is>
+      </c>
+      <c r="D120" s="26" t="inlineStr">
+        <is>
+          <t>91 में से 14 घटाने पर 77 बचता है। तो सही संख्या यह है।</t>
+        </is>
+      </c>
+      <c r="E120" s="27" t="inlineStr">
+        <is>
+          <t>Page 11</t>
+        </is>
+      </c>
+      <c r="F120" s="24" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="G120" s="25" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="24" t="n">
+        <v>117</v>
+      </c>
+      <c r="B121" s="25" t="inlineStr">
+        <is>
+          <t>vo_p4_correct</t>
+        </is>
+      </c>
+      <c r="C121" s="25" t="inlineStr">
+        <is>
+          <t>vo_p4_correct.ogg</t>
+        </is>
+      </c>
+      <c r="D121" s="26" t="inlineStr">
+        <is>
+          <t>शाबाश! आपने सही संख्या चुन ली। 91 घटा 14 बराबर 77।</t>
+        </is>
+      </c>
+      <c r="E121" s="27" t="inlineStr">
+        <is>
+          <t>Page 11</t>
+        </is>
+      </c>
+      <c r="F121" s="24" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="G121" s="25" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="24" t="n">
+        <v>118</v>
+      </c>
+      <c r="B122" s="25" t="inlineStr">
+        <is>
+          <t>vo_p4_correct_late</t>
+        </is>
+      </c>
+      <c r="C122" s="25" t="inlineStr">
+        <is>
+          <t>vo_p4_correct_late.ogg</t>
+        </is>
+      </c>
+      <c r="D122" s="26" t="inlineStr">
+        <is>
+          <t>आपने सही संख्या चुन ली। 91 घटा 14 बराबर 77।</t>
+        </is>
+      </c>
+      <c r="E122" s="27" t="inlineStr">
+        <is>
+          <t>Page 11</t>
+        </is>
+      </c>
+      <c r="F122" s="24" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="G122" s="25" t="inlineStr">
+        <is>
+          <t>TTS (Gemini, Kore)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="24" t="n">
+        <v>119</v>
+      </c>
+      <c r="B123" s="25" t="inlineStr">
+        <is>
           <t>vo_cel</t>
         </is>
       </c>
-      <c r="C116" s="25" t="inlineStr">
+      <c r="C123" s="25" t="inlineStr">
         <is>
           <t>vo_cel.ogg</t>
         </is>
       </c>
-      <c r="D116" s="26" t="inlineStr">
+      <c r="D123" s="26" t="inlineStr">
         <is>
           <t>शाबाश! आपने दहाई खोलकर घटाना सीख लिया!</t>
         </is>
       </c>
-      <c r="E116" s="27" t="inlineStr">
+      <c r="E123" s="27" t="inlineStr">
         <is>
           <t>Celebration</t>
         </is>
       </c>
-      <c r="F116" s="24" t="n">
+      <c r="F123" s="24" t="n">
         <v>3.93</v>
       </c>
-      <c r="G116" s="25" t="inlineStr">
+      <c r="G123" s="25" t="inlineStr">
         <is>
           <t>TTS (Gemini, Kore)</t>
         </is>
@@ -12127,7 +12687,7 @@
       </c>
       <c r="B5" s="30" t="inlineStr">
         <is>
-          <t>151 rows, 112 distinct recordings (see 'Recording list'). In the card but not heard in this build (not listed): vo_rm_ones_less, vo_rm_ones_more.</t>
+          <t>158 rows, 119 distinct recordings (see 'Recording list'). In the card but not heard in this build (not listed): vo_rm_ones_less, vo_rm_ones_more.</t>
         </is>
       </c>
     </row>

--- a/lesson_vo_manifest.xlsx
+++ b/lesson_vo_manifest.xlsx
@@ -703,7 +703,7 @@
       </c>
       <c r="I5" s="6" t="inlineStr"/>
       <c r="J5" s="4" t="n">
-        <v>5.32</v>
+        <v>5.61</v>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="I6" s="10" t="inlineStr"/>
       <c r="J6" s="8" t="n">
-        <v>4.32</v>
+        <v>4.99</v>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
       </c>
       <c r="I7" s="14" t="inlineStr"/>
       <c r="J7" s="12" t="n">
-        <v>2.76</v>
+        <v>3.43</v>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
@@ -844,7 +844,7 @@
       </c>
       <c r="I8" s="18" t="inlineStr"/>
       <c r="J8" s="16" t="n">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="K8" s="17" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
       </c>
       <c r="I9" s="14" t="inlineStr"/>
       <c r="J9" s="12" t="n">
-        <v>4.13</v>
+        <v>4.82</v>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
       </c>
       <c r="I10" s="18" t="inlineStr"/>
       <c r="J10" s="16" t="n">
-        <v>6.53</v>
+        <v>6.45</v>
       </c>
       <c r="K10" s="17" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
       </c>
       <c r="I11" s="14" t="inlineStr"/>
       <c r="J11" s="12" t="n">
-        <v>3.81</v>
+        <v>4.08</v>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="I12" s="18" t="inlineStr"/>
       <c r="J12" s="16" t="n">
-        <v>3.15</v>
+        <v>4.23</v>
       </c>
       <c r="K12" s="17" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="I13" s="14" t="inlineStr"/>
       <c r="J13" s="12" t="n">
-        <v>3.18</v>
+        <v>3.04</v>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
       </c>
       <c r="I14" s="18" t="inlineStr"/>
       <c r="J14" s="16" t="n">
-        <v>3.97</v>
+        <v>3.38</v>
       </c>
       <c r="K14" s="17" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="I15" s="14" t="inlineStr"/>
       <c r="J15" s="12" t="n">
-        <v>2.97</v>
+        <v>3.54</v>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="I16" s="18" t="inlineStr"/>
       <c r="J16" s="16" t="n">
-        <v>5.18</v>
+        <v>4.98</v>
       </c>
       <c r="K16" s="17" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="I17" s="14" t="inlineStr"/>
       <c r="J17" s="12" t="n">
-        <v>6.25</v>
+        <v>6.85</v>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I18" s="18" t="inlineStr"/>
       <c r="J18" s="16" t="n">
-        <v>7.22</v>
+        <v>6.75</v>
       </c>
       <c r="K18" s="17" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="I19" s="14" t="inlineStr"/>
       <c r="J19" s="12" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="I20" s="18" t="inlineStr"/>
       <c r="J20" s="16" t="n">
-        <v>2.95</v>
+        <v>3.38</v>
       </c>
       <c r="K20" s="17" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="J21" s="12" t="n">
-        <v>1.32</v>
+        <v>1</v>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
         </is>
       </c>
       <c r="J22" s="16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="K22" s="17" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="J24" s="16" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="K24" s="17" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="J25" s="12" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="J26" s="16" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="K26" s="17" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I27" s="14" t="inlineStr"/>
       <c r="J27" s="12" t="n">
-        <v>5.51</v>
+        <v>5.46</v>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>तो, अब यहाँ 1 दहाई और 9 इकाई बचीं।</t>
+          <t>अब यहाँ 1 दहाई और 9 इकाई बचीं।</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="I29" s="14" t="inlineStr"/>
       <c r="J29" s="12" t="n">
-        <v>4.04</v>
+        <v>3.54</v>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="I30" s="18" t="inlineStr"/>
       <c r="J30" s="16" t="n">
-        <v>6.96</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="K30" s="17" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="I31" s="14" t="inlineStr"/>
       <c r="J31" s="12" t="n">
-        <v>4.54</v>
+        <v>4.85</v>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="I32" s="18" t="inlineStr"/>
       <c r="J32" s="16" t="n">
-        <v>2.83</v>
+        <v>2.42</v>
       </c>
       <c r="K32" s="17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>यानी माधव के पास कुल 19 ब्लॉक्स बचे।</t>
+          <t>यानी माधव के पास 19 ब्लॉक्स बचे।</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="I33" s="14" t="inlineStr"/>
       <c r="J33" s="12" t="n">
-        <v>3.81</v>
+        <v>3.43</v>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="I34" s="18" t="inlineStr"/>
       <c r="J34" s="16" t="n">
-        <v>5.2</v>
+        <v>5.48</v>
       </c>
       <c r="K34" s="17" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="I35" s="14" t="inlineStr"/>
       <c r="J35" s="12" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="I36" s="18" t="inlineStr"/>
       <c r="J36" s="16" t="n">
-        <v>4.03</v>
+        <v>4.61</v>
       </c>
       <c r="K36" s="17" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="I37" s="14" t="inlineStr"/>
       <c r="J37" s="12" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="I38" s="18" t="inlineStr"/>
       <c r="J38" s="16" t="n">
-        <v>3.72</v>
+        <v>3.91</v>
       </c>
       <c r="K38" s="17" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
       </c>
       <c r="I39" s="14" t="inlineStr"/>
       <c r="J39" s="12" t="n">
-        <v>3.75</v>
+        <v>4.17</v>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="I40" s="18" t="inlineStr"/>
       <c r="J40" s="16" t="n">
-        <v>2.27</v>
+        <v>2.48</v>
       </c>
       <c r="K40" s="17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="I42" s="18" t="inlineStr"/>
       <c r="J42" s="16" t="n">
-        <v>3.04</v>
+        <v>3.97</v>
       </c>
       <c r="K42" s="17" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="I43" s="14" t="inlineStr"/>
       <c r="J43" s="12" t="n">
-        <v>5.29</v>
+        <v>5.19</v>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
       </c>
       <c r="I44" s="18" t="inlineStr"/>
       <c r="J44" s="16" t="n">
-        <v>8.949999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K44" s="17" t="inlineStr">
         <is>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="F45" s="15" t="inlineStr">
         <is>
-          <t>अब इसमें से 7 इकाई को हटाइए।</t>
+          <t>अब इसमें से 7 इकाई को आप हटाइए।</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="I45" s="14" t="inlineStr"/>
       <c r="J45" s="12" t="n">
-        <v>2.71</v>
+        <v>3.37</v>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
         </is>
       </c>
       <c r="J46" s="16" t="n">
-        <v>1.32</v>
+        <v>1</v>
       </c>
       <c r="K46" s="17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="J47" s="12" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="J49" s="12" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="J50" s="16" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="K50" s="17" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="J51" s="12" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="I52" s="18" t="inlineStr"/>
       <c r="J52" s="16" t="n">
-        <v>1.45</v>
+        <v>1.11</v>
       </c>
       <c r="K52" s="17" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="J53" s="12" t="n">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="I54" s="18" t="inlineStr"/>
       <c r="J54" s="16" t="n">
-        <v>4.99</v>
+        <v>4.83</v>
       </c>
       <c r="K54" s="17" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="F55" s="15" t="inlineStr">
         <is>
-          <t>अब आप दहाइयाँ घटाइए। 2 दहाई में से 1 दहाई हटाइए।</t>
+          <t>अब आप दहाई घटाइए। 2 दहाई में से 1 दहाई हटाइए।</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="I55" s="14" t="inlineStr"/>
       <c r="J55" s="12" t="n">
-        <v>4.8</v>
+        <v>5.18</v>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="J56" s="16" t="n">
-        <v>2.27</v>
+        <v>1.89</v>
       </c>
       <c r="K56" s="17" t="inlineStr">
         <is>
@@ -3207,7 +3207,7 @@
       </c>
       <c r="I57" s="14" t="inlineStr"/>
       <c r="J57" s="12" t="n">
-        <v>5.47</v>
+        <v>6.05</v>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="I58" s="18" t="inlineStr"/>
       <c r="J58" s="16" t="n">
-        <v>6.98</v>
+        <v>6.8</v>
       </c>
       <c r="K58" s="17" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="I59" s="14" t="inlineStr"/>
       <c r="J59" s="12" t="n">
-        <v>4.9</v>
+        <v>4.96</v>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="I60" s="18" t="inlineStr"/>
       <c r="J60" s="16" t="n">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="K60" s="17" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="F61" s="15" t="inlineStr">
         <is>
-          <t>यानी माधव के पास कुल 13 ब्लॉक्स बचे।</t>
+          <t>यानी माधव के पास 13 ब्लॉक्स बचे।</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="I61" s="14" t="inlineStr"/>
       <c r="J61" s="12" t="n">
-        <v>3.59</v>
+        <v>3.64</v>
       </c>
       <c r="K61" s="13" t="inlineStr">
         <is>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="I62" s="10" t="inlineStr"/>
       <c r="J62" s="8" t="n">
-        <v>5.01</v>
+        <v>5.55</v>
       </c>
       <c r="K62" s="9" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="I63" s="14" t="inlineStr"/>
       <c r="J63" s="12" t="n">
-        <v>2.48</v>
+        <v>2.97</v>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="I64" s="18" t="inlineStr"/>
       <c r="J64" s="16" t="n">
-        <v>7.18</v>
+        <v>7.02</v>
       </c>
       <c r="K64" s="17" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="J66" s="16" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="K66" s="17" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="I67" s="14" t="inlineStr"/>
       <c r="J67" s="12" t="n">
-        <v>5.56</v>
+        <v>5.55</v>
       </c>
       <c r="K67" s="13" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I68" s="18" t="inlineStr"/>
       <c r="J68" s="16" t="n">
-        <v>7.55</v>
+        <v>7.84</v>
       </c>
       <c r="K68" s="17" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         </is>
       </c>
       <c r="J69" s="12" t="n">
-        <v>3.16</v>
+        <v>3.38</v>
       </c>
       <c r="K69" s="13" t="inlineStr">
         <is>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="I70" s="18" t="inlineStr"/>
       <c r="J70" s="16" t="n">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="K70" s="17" t="inlineStr">
         <is>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="I71" s="14" t="inlineStr"/>
       <c r="J71" s="12" t="n">
-        <v>2.31</v>
+        <v>2.73</v>
       </c>
       <c r="K71" s="13" t="inlineStr">
         <is>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="I72" s="18" t="inlineStr"/>
       <c r="J72" s="16" t="n">
-        <v>4.48</v>
+        <v>4.33</v>
       </c>
       <c r="K72" s="17" t="inlineStr">
         <is>
@@ -3971,7 +3971,7 @@
       </c>
       <c r="I73" s="14" t="inlineStr"/>
       <c r="J73" s="12" t="n">
-        <v>4.92</v>
+        <v>5.48</v>
       </c>
       <c r="K73" s="13" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
       </c>
       <c r="I74" s="18" t="inlineStr"/>
       <c r="J74" s="16" t="n">
-        <v>5.49</v>
+        <v>4.81</v>
       </c>
       <c r="K74" s="17" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         </is>
       </c>
       <c r="J75" s="12" t="n">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="K75" s="13" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="J76" s="16" t="n">
-        <v>2.27</v>
+        <v>1.89</v>
       </c>
       <c r="K76" s="17" t="inlineStr">
         <is>
@@ -4171,7 +4171,7 @@
         </is>
       </c>
       <c r="J77" s="12" t="n">
-        <v>4.05</v>
+        <v>4.19</v>
       </c>
       <c r="K77" s="13" t="inlineStr">
         <is>
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="J78" s="16" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="K78" s="17" t="inlineStr">
         <is>
@@ -4273,7 +4273,7 @@
         </is>
       </c>
       <c r="J79" s="12" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="K79" s="13" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="J80" s="16" t="n">
-        <v>3.31</v>
+        <v>3.9</v>
       </c>
       <c r="K80" s="17" t="inlineStr">
         <is>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="I81" s="14" t="inlineStr"/>
       <c r="J81" s="12" t="n">
-        <v>5.72</v>
+        <v>5.61</v>
       </c>
       <c r="K81" s="13" t="inlineStr">
         <is>
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I82" s="18" t="inlineStr"/>
       <c r="J82" s="16" t="n">
-        <v>5.02</v>
+        <v>5.6</v>
       </c>
       <c r="K82" s="17" t="inlineStr">
         <is>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="I83" s="14" t="inlineStr"/>
       <c r="J83" s="12" t="n">
-        <v>7.35</v>
+        <v>7.8</v>
       </c>
       <c r="K83" s="13" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="I84" s="18" t="inlineStr"/>
       <c r="J84" s="16" t="n">
-        <v>6.47</v>
+        <v>7.05</v>
       </c>
       <c r="K84" s="17" t="inlineStr">
         <is>
@@ -4559,7 +4559,7 @@
       </c>
       <c r="I85" s="14" t="inlineStr"/>
       <c r="J85" s="12" t="n">
-        <v>4.26</v>
+        <v>5.25</v>
       </c>
       <c r="K85" s="13" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="I86" s="18" t="inlineStr"/>
       <c r="J86" s="16" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="K86" s="17" t="inlineStr">
         <is>
@@ -4653,7 +4653,7 @@
       </c>
       <c r="I87" s="14" t="inlineStr"/>
       <c r="J87" s="12" t="n">
-        <v>4.23</v>
+        <v>4.06</v>
       </c>
       <c r="K87" s="13" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         </is>
       </c>
       <c r="J89" s="12" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="K89" s="13" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="I90" s="18" t="inlineStr"/>
       <c r="J90" s="16" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="K90" s="17" t="inlineStr">
         <is>
@@ -4853,7 +4853,7 @@
         </is>
       </c>
       <c r="J91" s="12" t="n">
-        <v>3.16</v>
+        <v>3.38</v>
       </c>
       <c r="K91" s="13" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
       </c>
       <c r="I92" s="18" t="inlineStr"/>
       <c r="J92" s="16" t="n">
-        <v>2.58</v>
+        <v>3.08</v>
       </c>
       <c r="K92" s="17" t="inlineStr">
         <is>
@@ -4947,7 +4947,7 @@
       </c>
       <c r="I93" s="14" t="inlineStr"/>
       <c r="J93" s="12" t="n">
-        <v>2.16</v>
+        <v>2.49</v>
       </c>
       <c r="K93" s="13" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="J94" s="16" t="n">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="K94" s="17" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="J95" s="12" t="n">
-        <v>2.27</v>
+        <v>1.89</v>
       </c>
       <c r="K95" s="13" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         </is>
       </c>
       <c r="J96" s="16" t="n">
-        <v>4.05</v>
+        <v>4.19</v>
       </c>
       <c r="K96" s="17" t="inlineStr">
         <is>
@@ -5151,7 +5151,7 @@
         </is>
       </c>
       <c r="J97" s="12" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="K97" s="13" t="inlineStr">
         <is>
@@ -5202,7 +5202,7 @@
         </is>
       </c>
       <c r="J98" s="16" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="K98" s="17" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="J99" s="12" t="n">
-        <v>3.31</v>
+        <v>3.9</v>
       </c>
       <c r="K99" s="13" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="I100" s="18" t="inlineStr"/>
       <c r="J100" s="16" t="n">
-        <v>4.71</v>
+        <v>5.24</v>
       </c>
       <c r="K100" s="17" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="I101" s="14" t="inlineStr"/>
       <c r="J101" s="12" t="n">
-        <v>5.8</v>
+        <v>5.49</v>
       </c>
       <c r="K101" s="13" t="inlineStr">
         <is>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="I102" s="18" t="inlineStr"/>
       <c r="J102" s="16" t="n">
-        <v>4.48</v>
+        <v>4.81</v>
       </c>
       <c r="K102" s="17" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="I103" s="14" t="inlineStr"/>
       <c r="J103" s="12" t="n">
-        <v>3.88</v>
+        <v>5.46</v>
       </c>
       <c r="K103" s="13" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="I104" s="18" t="inlineStr"/>
       <c r="J104" s="16" t="n">
-        <v>2.72</v>
+        <v>2.89</v>
       </c>
       <c r="K104" s="17" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="I105" s="14" t="inlineStr"/>
       <c r="J105" s="12" t="n">
-        <v>2.67</v>
+        <v>3.09</v>
       </c>
       <c r="K105" s="13" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="J106" s="16" t="n">
-        <v>3.16</v>
+        <v>3.38</v>
       </c>
       <c r="K106" s="17" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="I107" s="14" t="inlineStr"/>
       <c r="J107" s="12" t="n">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="K107" s="13" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
       </c>
       <c r="I108" s="18" t="inlineStr"/>
       <c r="J108" s="16" t="n">
-        <v>2.47</v>
+        <v>2.12</v>
       </c>
       <c r="K108" s="17" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="J109" s="12" t="n">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="K109" s="13" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="J110" s="16" t="n">
-        <v>2.27</v>
+        <v>1.89</v>
       </c>
       <c r="K110" s="17" t="inlineStr">
         <is>
@@ -5833,7 +5833,7 @@
         </is>
       </c>
       <c r="J111" s="12" t="n">
-        <v>4.05</v>
+        <v>4.19</v>
       </c>
       <c r="K111" s="13" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="J112" s="16" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="K112" s="17" t="inlineStr">
         <is>
@@ -5935,7 +5935,7 @@
         </is>
       </c>
       <c r="J113" s="12" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="K113" s="13" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="J114" s="16" t="n">
-        <v>3.31</v>
+        <v>3.9</v>
       </c>
       <c r="K114" s="17" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
       </c>
       <c r="I115" s="14" t="inlineStr"/>
       <c r="J115" s="12" t="n">
-        <v>5.55</v>
+        <v>6.3</v>
       </c>
       <c r="K115" s="13" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="I116" s="18" t="inlineStr"/>
       <c r="J116" s="16" t="n">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="K116" s="17" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
       </c>
       <c r="I117" s="14" t="inlineStr"/>
       <c r="J117" s="12" t="n">
-        <v>4.99</v>
+        <v>4.92</v>
       </c>
       <c r="K117" s="13" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
       </c>
       <c r="I118" s="18" t="inlineStr"/>
       <c r="J118" s="16" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="K118" s="17" t="inlineStr">
         <is>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="I119" s="10" t="inlineStr"/>
       <c r="J119" s="8" t="n">
-        <v>1.87</v>
+        <v>2.37</v>
       </c>
       <c r="K119" s="9" t="inlineStr">
         <is>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="I120" s="18" t="inlineStr"/>
       <c r="J120" s="16" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="K120" s="17" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="I121" s="14" t="inlineStr"/>
       <c r="J121" s="12" t="n">
-        <v>3.69</v>
+        <v>2.88</v>
       </c>
       <c r="K121" s="13" t="inlineStr">
         <is>
@@ -6366,7 +6366,7 @@
         </is>
       </c>
       <c r="J122" s="16" t="n">
-        <v>3.16</v>
+        <v>3.38</v>
       </c>
       <c r="K122" s="17" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="I123" s="14" t="inlineStr"/>
       <c r="J123" s="12" t="n">
-        <v>3.33</v>
+        <v>3.51</v>
       </c>
       <c r="K123" s="13" t="inlineStr">
         <is>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="I124" s="18" t="inlineStr"/>
       <c r="J124" s="16" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="K124" s="17" t="inlineStr">
         <is>
@@ -6511,7 +6511,7 @@
         </is>
       </c>
       <c r="J125" s="12" t="n">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="K125" s="13" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c r="J126" s="16" t="n">
-        <v>2.27</v>
+        <v>1.89</v>
       </c>
       <c r="K126" s="17" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="J127" s="12" t="n">
-        <v>4.05</v>
+        <v>4.19</v>
       </c>
       <c r="K127" s="13" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         </is>
       </c>
       <c r="J128" s="16" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="K128" s="17" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         </is>
       </c>
       <c r="J129" s="12" t="n">
-        <v>4.39</v>
+        <v>5.27</v>
       </c>
       <c r="K129" s="13" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="J130" s="16" t="n">
-        <v>3.31</v>
+        <v>3.9</v>
       </c>
       <c r="K130" s="17" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="I131" s="14" t="inlineStr"/>
       <c r="J131" s="12" t="n">
-        <v>5.45</v>
+        <v>6.01</v>
       </c>
       <c r="K131" s="13" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="I132" s="18" t="inlineStr"/>
       <c r="J132" s="16" t="n">
-        <v>5.69</v>
+        <v>5.58</v>
       </c>
       <c r="K132" s="17" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="I133" s="14" t="inlineStr"/>
       <c r="J133" s="12" t="n">
-        <v>5.01</v>
+        <v>5.55</v>
       </c>
       <c r="K133" s="13" t="inlineStr">
         <is>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="I134" s="18" t="inlineStr"/>
       <c r="J134" s="16" t="n">
-        <v>3.93</v>
+        <v>4.45</v>
       </c>
       <c r="K134" s="17" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
       </c>
       <c r="I135" s="14" t="inlineStr"/>
       <c r="J135" s="12" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="K135" s="13" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
       </c>
       <c r="I136" s="18" t="inlineStr"/>
       <c r="J136" s="16" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="K136" s="17" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="J137" s="12" t="n">
-        <v>3.16</v>
+        <v>3.38</v>
       </c>
       <c r="K137" s="13" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="I138" s="18" t="inlineStr"/>
       <c r="J138" s="16" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="K138" s="17" t="inlineStr">
         <is>
@@ -7193,7 +7193,7 @@
       </c>
       <c r="I139" s="14" t="inlineStr"/>
       <c r="J139" s="12" t="n">
-        <v>1.95</v>
+        <v>2.46</v>
       </c>
       <c r="K139" s="13" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         </is>
       </c>
       <c r="J140" s="16" t="n">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="K140" s="17" t="inlineStr">
         <is>
@@ -7295,7 +7295,7 @@
         </is>
       </c>
       <c r="J141" s="12" t="n">
-        <v>2.27</v>
+        <v>1.89</v>
       </c>
       <c r="K141" s="13" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         </is>
       </c>
       <c r="J142" s="16" t="n">
-        <v>4.05</v>
+        <v>4.19</v>
       </c>
       <c r="K142" s="17" t="inlineStr">
         <is>
@@ -7397,7 +7397,7 @@
         </is>
       </c>
       <c r="J143" s="12" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="K143" s="13" t="inlineStr">
         <is>
@@ -7448,7 +7448,7 @@
         </is>
       </c>
       <c r="J144" s="16" t="n">
-        <v>4.39</v>
+        <v>5.27</v>
       </c>
       <c r="K144" s="17" t="inlineStr">
         <is>
@@ -7499,7 +7499,7 @@
         </is>
       </c>
       <c r="J145" s="12" t="n">
-        <v>3.31</v>
+        <v>3.9</v>
       </c>
       <c r="K145" s="13" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="I146" s="18" t="inlineStr"/>
       <c r="J146" s="16" t="n">
-        <v>5.81</v>
+        <v>5.52</v>
       </c>
       <c r="K146" s="17" t="inlineStr">
         <is>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="I147" s="14" t="inlineStr"/>
       <c r="J147" s="12" t="n">
-        <v>4.64</v>
+        <v>5.55</v>
       </c>
       <c r="K147" s="13" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
       </c>
       <c r="I148" s="18" t="inlineStr"/>
       <c r="J148" s="16" t="n">
-        <v>5.21</v>
+        <v>5.53</v>
       </c>
       <c r="K148" s="17" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
       </c>
       <c r="I149" s="14" t="inlineStr"/>
       <c r="J149" s="12" t="n">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="K149" s="13" t="inlineStr">
         <is>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="I150" s="18" t="inlineStr"/>
       <c r="J150" s="16" t="n">
-        <v>4.51</v>
+        <v>4.57</v>
       </c>
       <c r="K150" s="17" t="inlineStr">
         <is>
@@ -7785,7 +7785,7 @@
         </is>
       </c>
       <c r="J151" s="12" t="n">
-        <v>4.45</v>
+        <v>4.46</v>
       </c>
       <c r="K151" s="13" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="I152" s="18" t="inlineStr"/>
       <c r="J152" s="16" t="n">
-        <v>5.47</v>
+        <v>5.85</v>
       </c>
       <c r="K152" s="17" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
       </c>
       <c r="I153" s="14" t="inlineStr"/>
       <c r="J153" s="12" t="n">
-        <v>5.52</v>
+        <v>6.25</v>
       </c>
       <c r="K153" s="13" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
       </c>
       <c r="I154" s="18" t="inlineStr"/>
       <c r="J154" s="16" t="n">
-        <v>6.91</v>
+        <v>6.93</v>
       </c>
       <c r="K154" s="17" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
       </c>
       <c r="I155" s="14" t="inlineStr"/>
       <c r="J155" s="12" t="n">
-        <v>5.67</v>
+        <v>6.35</v>
       </c>
       <c r="K155" s="13" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
       </c>
       <c r="I156" s="18" t="inlineStr"/>
       <c r="J156" s="16" t="n">
-        <v>3.57</v>
+        <v>4.47</v>
       </c>
       <c r="K156" s="17" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="J157" s="12" t="n">
-        <v>4.45</v>
+        <v>4.46</v>
       </c>
       <c r="K157" s="13" t="inlineStr">
         <is>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="I158" s="18" t="inlineStr"/>
       <c r="J158" s="16" t="n">
-        <v>5.17</v>
+        <v>5.86</v>
       </c>
       <c r="K158" s="17" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
       </c>
       <c r="I159" s="14" t="inlineStr"/>
       <c r="J159" s="12" t="n">
-        <v>6.49</v>
+        <v>6.16</v>
       </c>
       <c r="K159" s="13" t="inlineStr">
         <is>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="I160" s="18" t="inlineStr"/>
       <c r="J160" s="16" t="n">
-        <v>7.04</v>
+        <v>7.41</v>
       </c>
       <c r="K160" s="17" t="inlineStr">
         <is>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="I161" s="14" t="inlineStr"/>
       <c r="J161" s="12" t="n">
-        <v>5.79</v>
+        <v>5.28</v>
       </c>
       <c r="K161" s="13" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
       </c>
       <c r="I162" s="22" t="inlineStr"/>
       <c r="J162" s="20" t="n">
-        <v>3.93</v>
+        <v>4.67</v>
       </c>
       <c r="K162" s="21" t="inlineStr">
         <is>
@@ -8413,7 +8413,7 @@
         </is>
       </c>
       <c r="F5" s="24" t="n">
-        <v>5.32</v>
+        <v>5.61</v>
       </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="F6" s="24" t="n">
-        <v>4.32</v>
+        <v>4.99</v>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
         </is>
       </c>
       <c r="F7" s="24" t="n">
-        <v>2.76</v>
+        <v>3.43</v>
       </c>
       <c r="G7" s="25" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
         </is>
       </c>
       <c r="F8" s="24" t="n">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
@@ -8545,7 +8545,7 @@
         </is>
       </c>
       <c r="F9" s="24" t="n">
-        <v>4.13</v>
+        <v>4.82</v>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="F10" s="24" t="n">
-        <v>6.53</v>
+        <v>6.45</v>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="F11" s="24" t="n">
-        <v>3.81</v>
+        <v>4.08</v>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         </is>
       </c>
       <c r="F12" s="24" t="n">
-        <v>3.15</v>
+        <v>4.23</v>
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         </is>
       </c>
       <c r="F13" s="24" t="n">
-        <v>3.18</v>
+        <v>3.04</v>
       </c>
       <c r="G13" s="25" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         </is>
       </c>
       <c r="F14" s="24" t="n">
-        <v>3.97</v>
+        <v>3.38</v>
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="F15" s="24" t="n">
-        <v>2.97</v>
+        <v>3.54</v>
       </c>
       <c r="G15" s="25" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         </is>
       </c>
       <c r="F16" s="24" t="n">
-        <v>5.18</v>
+        <v>4.98</v>
       </c>
       <c r="G16" s="25" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         </is>
       </c>
       <c r="F17" s="24" t="n">
-        <v>6.25</v>
+        <v>6.85</v>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
@@ -8842,7 +8842,7 @@
         </is>
       </c>
       <c r="F18" s="24" t="n">
-        <v>7.22</v>
+        <v>6.75</v>
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="F19" s="24" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         </is>
       </c>
       <c r="F20" s="24" t="n">
-        <v>2.95</v>
+        <v>3.38</v>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         </is>
       </c>
       <c r="F21" s="24" t="n">
-        <v>1.32</v>
+        <v>1</v>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         </is>
       </c>
       <c r="F22" s="24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="G22" s="25" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         </is>
       </c>
       <c r="F24" s="24" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="F25" s="24" t="n">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="G25" s="25" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         </is>
       </c>
       <c r="F26" s="24" t="n">
-        <v>1.19</v>
+        <v>1.05</v>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         </is>
       </c>
       <c r="F27" s="24" t="n">
-        <v>5.51</v>
+        <v>5.46</v>
       </c>
       <c r="G27" s="25" t="inlineStr">
         <is>
@@ -9196,7 +9196,7 @@
       </c>
       <c r="D29" s="26" t="inlineStr">
         <is>
-          <t>तो, अब यहाँ 1 दहाई और 9 इकाई बचीं।</t>
+          <t>अब यहाँ 1 दहाई और 9 इकाई बचीं।</t>
         </is>
       </c>
       <c r="E29" s="27" t="inlineStr">
@@ -9205,7 +9205,7 @@
         </is>
       </c>
       <c r="F29" s="24" t="n">
-        <v>4.04</v>
+        <v>3.54</v>
       </c>
       <c r="G29" s="25" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         </is>
       </c>
       <c r="F30" s="24" t="n">
-        <v>6.96</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         </is>
       </c>
       <c r="F31" s="24" t="n">
-        <v>4.54</v>
+        <v>4.85</v>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         </is>
       </c>
       <c r="F32" s="24" t="n">
-        <v>2.83</v>
+        <v>2.42</v>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
       </c>
       <c r="D33" s="26" t="inlineStr">
         <is>
-          <t>यानी माधव के पास कुल 19 ब्लॉक्स बचे।</t>
+          <t>यानी माधव के पास 19 ब्लॉक्स बचे।</t>
         </is>
       </c>
       <c r="E33" s="27" t="inlineStr">
@@ -9337,7 +9337,7 @@
         </is>
       </c>
       <c r="F33" s="24" t="n">
-        <v>3.81</v>
+        <v>3.43</v>
       </c>
       <c r="G33" s="25" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="F34" s="24" t="n">
-        <v>5.2</v>
+        <v>5.48</v>
       </c>
       <c r="G34" s="25" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         </is>
       </c>
       <c r="F35" s="24" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="F36" s="24" t="n">
-        <v>4.03</v>
+        <v>4.61</v>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
@@ -9469,7 +9469,7 @@
         </is>
       </c>
       <c r="F37" s="24" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="G37" s="25" t="inlineStr">
         <is>
@@ -9502,7 +9502,7 @@
         </is>
       </c>
       <c r="F38" s="24" t="n">
-        <v>3.72</v>
+        <v>3.91</v>
       </c>
       <c r="G38" s="25" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         </is>
       </c>
       <c r="F39" s="24" t="n">
-        <v>3.75</v>
+        <v>4.17</v>
       </c>
       <c r="G39" s="25" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="F40" s="24" t="n">
-        <v>2.27</v>
+        <v>2.48</v>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
@@ -9634,7 +9634,7 @@
         </is>
       </c>
       <c r="F42" s="24" t="n">
-        <v>3.04</v>
+        <v>3.97</v>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         </is>
       </c>
       <c r="F43" s="24" t="n">
-        <v>5.29</v>
+        <v>5.19</v>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         </is>
       </c>
       <c r="F44" s="24" t="n">
-        <v>8.949999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="G44" s="25" t="inlineStr">
         <is>
@@ -9724,7 +9724,7 @@
       </c>
       <c r="D45" s="26" t="inlineStr">
         <is>
-          <t>अब इसमें से 7 इकाई को हटाइए।</t>
+          <t>अब इसमें से 7 इकाई को आप हटाइए।</t>
         </is>
       </c>
       <c r="E45" s="27" t="inlineStr">
@@ -9733,7 +9733,7 @@
         </is>
       </c>
       <c r="F45" s="24" t="n">
-        <v>2.71</v>
+        <v>3.37</v>
       </c>
       <c r="G45" s="25" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         </is>
       </c>
       <c r="F46" s="24" t="n">
-        <v>1.45</v>
+        <v>1.11</v>
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="F47" s="24" t="n">
-        <v>2.21</v>
+        <v>1.88</v>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
@@ -9832,7 +9832,7 @@
         </is>
       </c>
       <c r="F48" s="24" t="n">
-        <v>4.99</v>
+        <v>4.83</v>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="D49" s="26" t="inlineStr">
         <is>
-          <t>अब आप दहाइयाँ घटाइए। 2 दहाई में से 1 दहाई हटाइए।</t>
+          <t>अब आप दहाई घटाइए। 2 दहाई में से 1 दहाई हटाइए।</t>
         </is>
       </c>
       <c r="E49" s="27" t="inlineStr">
@@ -9865,7 +9865,7 @@
         </is>
       </c>
       <c r="F49" s="24" t="n">
-        <v>4.8</v>
+        <v>5.18</v>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="F50" s="24" t="n">
-        <v>2.27</v>
+        <v>1.89</v>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         </is>
       </c>
       <c r="F51" s="24" t="n">
-        <v>5.47</v>
+        <v>6.05</v>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         </is>
       </c>
       <c r="F52" s="24" t="n">
-        <v>6.98</v>
+        <v>6.8</v>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         </is>
       </c>
       <c r="F53" s="24" t="n">
-        <v>4.9</v>
+        <v>4.96</v>
       </c>
       <c r="G53" s="25" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         </is>
       </c>
       <c r="F54" s="24" t="n">
-        <v>2.63</v>
+        <v>2.96</v>
       </c>
       <c r="G54" s="25" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
       </c>
       <c r="D55" s="26" t="inlineStr">
         <is>
-          <t>यानी माधव के पास कुल 13 ब्लॉक्स बचे।</t>
+          <t>यानी माधव के पास 13 ब्लॉक्स बचे।</t>
         </is>
       </c>
       <c r="E55" s="27" t="inlineStr">
@@ -10063,7 +10063,7 @@
         </is>
       </c>
       <c r="F55" s="24" t="n">
-        <v>3.59</v>
+        <v>3.64</v>
       </c>
       <c r="G55" s="25" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         </is>
       </c>
       <c r="F56" s="24" t="n">
-        <v>5.01</v>
+        <v>5.55</v>
       </c>
       <c r="G56" s="25" t="inlineStr">
         <is>
@@ -10129,7 +10129,7 @@
         </is>
       </c>
       <c r="F57" s="24" t="n">
-        <v>2.48</v>
+        <v>2.97</v>
       </c>
       <c r="G57" s="25" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         </is>
       </c>
       <c r="F58" s="24" t="n">
-        <v>7.18</v>
+        <v>7.02</v>
       </c>
       <c r="G58" s="25" t="inlineStr">
         <is>
@@ -10195,7 +10195,7 @@
         </is>
       </c>
       <c r="F59" s="24" t="n">
-        <v>1.85</v>
+        <v>2.03</v>
       </c>
       <c r="G59" s="25" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="F60" s="24" t="n">
-        <v>5.56</v>
+        <v>5.55</v>
       </c>
       <c r="G60" s="25" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         </is>
       </c>
       <c r="F61" s="24" t="n">
-        <v>7.55</v>
+        <v>7.84</v>
       </c>
       <c r="G61" s="25" t="inlineStr">
         <is>
@@ -10294,7 +10294,7 @@
         </is>
       </c>
       <c r="F62" s="24" t="n">
-        <v>3.16</v>
+        <v>3.38</v>
       </c>
       <c r="G62" s="25" t="inlineStr">
         <is>
@@ -10327,7 +10327,7 @@
         </is>
       </c>
       <c r="F63" s="24" t="n">
-        <v>3.19</v>
+        <v>3.31</v>
       </c>
       <c r="G63" s="25" t="inlineStr">
         <is>
@@ -10360,7 +10360,7 @@
         </is>
       </c>
       <c r="F64" s="24" t="n">
-        <v>2.31</v>
+        <v>2.73</v>
       </c>
       <c r="G64" s="25" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         </is>
       </c>
       <c r="F65" s="24" t="n">
-        <v>4.48</v>
+        <v>4.33</v>
       </c>
       <c r="G65" s="25" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         </is>
       </c>
       <c r="F66" s="24" t="n">
-        <v>4.92</v>
+        <v>5.48</v>
       </c>
       <c r="G66" s="25" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         </is>
       </c>
       <c r="F67" s="24" t="n">
-        <v>5.49</v>
+        <v>4.81</v>
       </c>
       <c r="G67" s="25" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         </is>
       </c>
       <c r="F68" s="24" t="n">
-        <v>4.05</v>
+        <v>4.19</v>
       </c>
       <c r="G68" s="25" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         </is>
       </c>
       <c r="F69" s="24" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="G69" s="25" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         </is>
       </c>
       <c r="F70" s="24" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="G70" s="25" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         </is>
       </c>
       <c r="F71" s="24" t="n">
-        <v>3.31</v>
+        <v>3.9</v>
       </c>
       <c r="G71" s="25" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         </is>
       </c>
       <c r="F72" s="24" t="n">
-        <v>5.72</v>
+        <v>5.61</v>
       </c>
       <c r="G72" s="25" t="inlineStr">
         <is>
@@ -10657,7 +10657,7 @@
         </is>
       </c>
       <c r="F73" s="24" t="n">
-        <v>5.02</v>
+        <v>5.6</v>
       </c>
       <c r="G73" s="25" t="inlineStr">
         <is>
@@ -10690,7 +10690,7 @@
         </is>
       </c>
       <c r="F74" s="24" t="n">
-        <v>7.35</v>
+        <v>7.8</v>
       </c>
       <c r="G74" s="25" t="inlineStr">
         <is>
@@ -10723,7 +10723,7 @@
         </is>
       </c>
       <c r="F75" s="24" t="n">
-        <v>6.47</v>
+        <v>7.05</v>
       </c>
       <c r="G75" s="25" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="F76" s="24" t="n">
-        <v>4.26</v>
+        <v>5.25</v>
       </c>
       <c r="G76" s="25" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         </is>
       </c>
       <c r="F77" s="24" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="G77" s="25" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="F78" s="24" t="n">
-        <v>4.23</v>
+        <v>4.06</v>
       </c>
       <c r="G78" s="25" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         </is>
       </c>
       <c r="F79" s="24" t="n">
-        <v>2.32</v>
+        <v>2.52</v>
       </c>
       <c r="G79" s="25" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         </is>
       </c>
       <c r="F80" s="24" t="n">
-        <v>2.58</v>
+        <v>3.08</v>
       </c>
       <c r="G80" s="25" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         </is>
       </c>
       <c r="F81" s="24" t="n">
-        <v>2.16</v>
+        <v>2.49</v>
       </c>
       <c r="G81" s="25" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         </is>
       </c>
       <c r="F82" s="24" t="n">
-        <v>4.71</v>
+        <v>5.24</v>
       </c>
       <c r="G82" s="25" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         </is>
       </c>
       <c r="F83" s="24" t="n">
-        <v>5.8</v>
+        <v>5.49</v>
       </c>
       <c r="G83" s="25" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         </is>
       </c>
       <c r="F84" s="24" t="n">
-        <v>4.48</v>
+        <v>4.81</v>
       </c>
       <c r="G84" s="25" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="F85" s="24" t="n">
-        <v>3.88</v>
+        <v>5.46</v>
       </c>
       <c r="G85" s="25" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         </is>
       </c>
       <c r="F86" s="24" t="n">
-        <v>2.72</v>
+        <v>2.89</v>
       </c>
       <c r="G86" s="25" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         </is>
       </c>
       <c r="F87" s="24" t="n">
-        <v>2.67</v>
+        <v>3.09</v>
       </c>
       <c r="G87" s="25" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         </is>
       </c>
       <c r="F88" s="24" t="n">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="G88" s="25" t="inlineStr">
         <is>
@@ -11185,7 +11185,7 @@
         </is>
       </c>
       <c r="F89" s="24" t="n">
-        <v>2.47</v>
+        <v>2.12</v>
       </c>
       <c r="G89" s="25" t="inlineStr">
         <is>
@@ -11218,7 +11218,7 @@
         </is>
       </c>
       <c r="F90" s="24" t="n">
-        <v>5.55</v>
+        <v>6.3</v>
       </c>
       <c r="G90" s="25" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="F91" s="24" t="n">
-        <v>5.75</v>
+        <v>5.55</v>
       </c>
       <c r="G91" s="25" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         </is>
       </c>
       <c r="F92" s="24" t="n">
-        <v>4.99</v>
+        <v>4.92</v>
       </c>
       <c r="G92" s="25" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         </is>
       </c>
       <c r="F93" s="24" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="G93" s="25" t="inlineStr">
         <is>
@@ -11350,7 +11350,7 @@
         </is>
       </c>
       <c r="F94" s="24" t="n">
-        <v>1.87</v>
+        <v>2.37</v>
       </c>
       <c r="G94" s="25" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         </is>
       </c>
       <c r="F95" s="24" t="n">
-        <v>2.5</v>
+        <v>2.68</v>
       </c>
       <c r="G95" s="25" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         </is>
       </c>
       <c r="F96" s="24" t="n">
-        <v>3.69</v>
+        <v>2.88</v>
       </c>
       <c r="G96" s="25" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         </is>
       </c>
       <c r="F97" s="24" t="n">
-        <v>3.33</v>
+        <v>3.51</v>
       </c>
       <c r="G97" s="25" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         </is>
       </c>
       <c r="F98" s="24" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="G98" s="25" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         </is>
       </c>
       <c r="F99" s="24" t="n">
-        <v>4.39</v>
+        <v>5.27</v>
       </c>
       <c r="G99" s="25" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="F100" s="24" t="n">
-        <v>5.45</v>
+        <v>6.01</v>
       </c>
       <c r="G100" s="25" t="inlineStr">
         <is>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="F101" s="24" t="n">
-        <v>5.69</v>
+        <v>5.58</v>
       </c>
       <c r="G101" s="25" t="inlineStr">
         <is>
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="F102" s="24" t="n">
-        <v>5.01</v>
+        <v>5.55</v>
       </c>
       <c r="G102" s="25" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         </is>
       </c>
       <c r="F103" s="24" t="n">
-        <v>3.93</v>
+        <v>4.45</v>
       </c>
       <c r="G103" s="25" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="F104" s="24" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G104" s="25" t="inlineStr">
         <is>
@@ -11713,7 +11713,7 @@
         </is>
       </c>
       <c r="F105" s="24" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="G105" s="25" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         </is>
       </c>
       <c r="F106" s="24" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="G106" s="25" t="inlineStr">
         <is>
@@ -11779,7 +11779,7 @@
         </is>
       </c>
       <c r="F107" s="24" t="n">
-        <v>1.95</v>
+        <v>2.46</v>
       </c>
       <c r="G107" s="25" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         </is>
       </c>
       <c r="F108" s="24" t="n">
-        <v>5.81</v>
+        <v>5.52</v>
       </c>
       <c r="G108" s="25" t="inlineStr">
         <is>
@@ -11845,7 +11845,7 @@
         </is>
       </c>
       <c r="F109" s="24" t="n">
-        <v>4.64</v>
+        <v>5.55</v>
       </c>
       <c r="G109" s="25" t="inlineStr">
         <is>
@@ -11878,7 +11878,7 @@
         </is>
       </c>
       <c r="F110" s="24" t="n">
-        <v>5.21</v>
+        <v>5.53</v>
       </c>
       <c r="G110" s="25" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         </is>
       </c>
       <c r="F111" s="24" t="n">
-        <v>3.94</v>
+        <v>3.97</v>
       </c>
       <c r="G111" s="25" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         </is>
       </c>
       <c r="F112" s="24" t="n">
-        <v>4.51</v>
+        <v>4.57</v>
       </c>
       <c r="G112" s="25" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         </is>
       </c>
       <c r="F113" s="24" t="n">
-        <v>4.45</v>
+        <v>4.46</v>
       </c>
       <c r="G113" s="25" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         </is>
       </c>
       <c r="F114" s="24" t="n">
-        <v>5.47</v>
+        <v>5.85</v>
       </c>
       <c r="G114" s="25" t="inlineStr">
         <is>
@@ -12043,7 +12043,7 @@
         </is>
       </c>
       <c r="F115" s="24" t="n">
-        <v>5.52</v>
+        <v>6.25</v>
       </c>
       <c r="G115" s="25" t="inlineStr">
         <is>
@@ -12076,7 +12076,7 @@
         </is>
       </c>
       <c r="F116" s="24" t="n">
-        <v>6.91</v>
+        <v>6.93</v>
       </c>
       <c r="G116" s="25" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         </is>
       </c>
       <c r="F117" s="24" t="n">
-        <v>5.67</v>
+        <v>6.35</v>
       </c>
       <c r="G117" s="25" t="inlineStr">
         <is>
@@ -12142,7 +12142,7 @@
         </is>
       </c>
       <c r="F118" s="24" t="n">
-        <v>3.57</v>
+        <v>4.47</v>
       </c>
       <c r="G118" s="25" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         </is>
       </c>
       <c r="F119" s="24" t="n">
-        <v>5.17</v>
+        <v>5.86</v>
       </c>
       <c r="G119" s="25" t="inlineStr">
         <is>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="F120" s="24" t="n">
-        <v>6.49</v>
+        <v>6.16</v>
       </c>
       <c r="G120" s="25" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="F121" s="24" t="n">
-        <v>7.04</v>
+        <v>7.41</v>
       </c>
       <c r="G121" s="25" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         </is>
       </c>
       <c r="F122" s="24" t="n">
-        <v>5.79</v>
+        <v>5.28</v>
       </c>
       <c r="G122" s="25" t="inlineStr">
         <is>
@@ -12307,7 +12307,7 @@
         </is>
       </c>
       <c r="F123" s="24" t="n">
-        <v>3.93</v>
+        <v>4.67</v>
       </c>
       <c r="G123" s="25" t="inlineStr">
         <is>
